--- a/traducciones/Traduccion_nahuatl_tablero.xlsx
+++ b/traducciones/Traduccion_nahuatl_tablero.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glosario" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$G$300</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$G$316</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G300"/>
+  <dimension ref="A1:G316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Inicio</t>
+          <t>Pie de página</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -1894,12 +1894,12 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Gobierno del Estado de Morelos · La tierra que nos une</t>
+          <t>Datos actualizados al {n} de octubre de {n}.</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Kaltlayekana ipan Morelos · Nin tlale tech sepaneloa</t>
+          <t>Tlapoualli yankuik ipan {n} octubre, {n} xiuitl.</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -1925,16 +1925,20 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Territorios de Paz y Buen Vivir</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Gobierno del Estado de Morelos · La tierra que nos une</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Kaltlayekana ipan Morelos · Nin tlale tech sepaneloa</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -1952,20 +1956,16 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>El programa social más importante del sexenio. Su propósito es terminar con el rezago social y garantizar que todas las personas cuenten con oportunidades reales para su desarrollo, llevando la acción coordinada del Gobierno de Morelos a las comunidades que más lo necesitan.</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>Nin tlapaleuilistle tlen ogachi ueyi ipan nin chikuasen xiuitl. Guinegui kitlamiltis iknoyotl uan kichiuas ma nochi tlatlaga kipiakaj melauak ojmej iga ueyiyaskej, iga iteguiu Kaltlayekana ipan Morelos tlen asi ipan altepetsitsin tlen ogachi guineguij.</t>
-        </is>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="n"/>
+          <t>Territorios de Paz y Buen Vivir</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -1983,12 +1983,12 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Este tablero, de la Agencia de Transformación Digital, reúne la información sociodemográfica y territorial del programa para apoyar su planeación y seguimiento.</t>
+          <t>El programa social más importante del sexenio. Su propósito es terminar con el rezago social y garantizar que todas las personas cuenten con oportunidades reales para su desarrollo, llevando la acción coordinada del Gobierno de Morelos a las comunidades que más lo necesitan.</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>Nin tlapoualli, tlen kichiua Agencia de Transformación Digital, kisentlalia tlamachilistle iga tlatlaga uan tlale tlen nin tlapaleuilistle, iga ma kipaleui kuak motlalia uan motlachilia.</t>
+          <t>Nin tlapaleuilistle tlen ogachi ueyi ipan nin chikuasen xiuitl. Guinegui kitlamiltis iknoyotl uan kichiuas ma nochi tlatlaga kipiakaj melauak ojmej iga ueyiyaskej, iga iteguiu Kaltlayekana ipan Morelos tlen asi ipan altepetsitsin tlen ogachi guineguij.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Explorar el análisis</t>
+          <t>Este tablero, de la Agencia de Transformación Digital, reúne la información sociodemográfica y territorial del programa para apoyar su planeación y seguimiento.</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Xiktlachili tlapoualli</t>
+          <t>Nin tlapoualli, tlen kichiua Agencia de Transformación Digital, kisentlalia tlamachilistle iga tlatlaga uan tlale tlen nin tlapaleuilistle, iga ma kipaleui kuak motlalia uan motlachilia.</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Datos abiertos</t>
+          <t>Explorar el análisis</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
-          <t>Tlapoualli tlapojtok</t>
+          <t>Xiktlachili tlapoualli</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Este es el programa social más importante para nosotros en estos seis años. Yo, como titular del Ejecutivo, quiero hacer una transformación en el estado, y los necesito a todos ustedes.</t>
+          <t>Datos abiertos</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Nin tlapaleuilistle tlen ogachi ueyi iga tojuantij ipan nin chikuasen xiuitl. Na, ken akin tlayekana, niknegui nikpatlas nin altepetl ueyi, uan nochi namejuantij nimechmonekiltia.</t>
+          <t>Tlapoualli tlapojtok</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>, Gobernadora del Estado de Morelos, durante la presentación del programa.</t>
+          <t>Datos actualizados al {n} de octubre de {n} · Fuentes: INEGI (Censo {n}), CONAPO y ATDEM</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
         <is>
-          <t>, Soatlayekanki ipan Morelos, kuak kiteixpantij nin tlapaleuilistle.</t>
+          <t>Tlapoualli yankuik ipan {n} octubre, {n} xiuitl · Kanin eua: INEGI (Censo {n}), CONAPO uan ATDEM</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Boletín {n}</t>
+          <t>¿Tu comunidad está en el programa?</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Tlanonotsalli {n}</t>
+          <t>¿Moaltepetsin kalaktok ipan nin tlapaleuilistle?</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>¿Cómo funciona?</t>
+          <t>Escribe el nombre de tu localidad, colonia o municipio.</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
         <is>
-          <t>¿Kenin teguiti?</t>
+          <t>Xiktlajkuilo itoga moaltepetsin, mocolonia o moaltepeu.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2200,12 +2200,12 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Diagnóstico territorial</t>
+          <t>Nombre de tu localidad, colonia o municipio</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>Tlatemolistle ipan tlale</t>
+          <t>Itoga moaltepetsin, mocolonia o moaltepeu</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2226,17 +2226,17 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Las comunidades se identifican mediante un diagnóstico realizado por la Jefatura de la Oficina de la Gubernatura, que define los polígonos de atención.</t>
+          <t>Por ejemplo: {d}</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin moixmatij iga se tlatemolistle tlen kichiua Jefatura de la Oficina de la Gubernatura, uan yejua kitlalia polígono kanin motekipanos.</t>
+          <t>Ken nin: {d}</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2262,12 +2262,12 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Promotores comunitarios</t>
+          <t>Este es el programa social más importante para nosotros en estos seis años. Yo, como titular del Ejecutivo, quiero hacer una transformación en el estado, y los necesito a todos ustedes.</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Tlapaleuianij ipan altepetsitsin</t>
+          <t>Nin tlapaleuilistle tlen ogachi ueyi iga tojuantij ipan nin chikuasen xiuitl. Na, ken akin tlayekana, niknegui nikpatlas nin altepetl ueyi, uan nochi namejuantij nimechmonekiltia.</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Promotores capacitados visitan a la población para escuchar y conocer a detalle sus necesidades básicas.</t>
+          <t>, Gobernadora del Estado de Morelos, durante la presentación del programa.</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>Tlapaleuianij tlen momachtijkej kinpaxalouaj tlatlaga iga kinkaguiskej uan kualtsin kiixmatiskej tlen kinmonekij.</t>
+          <t>, Soatlayekanki ipan Morelos, kuak kiteixpantij nin tlapaleuilistle.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Acción coordinada</t>
+          <t>Boletín {n}</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>Teguitl tlen sepan mochiua</t>
+          <t>Tlanonotsalli {n}</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Cada secretaría y organismo del Poder Ejecutivo lleva a cabo acciones coordinadas para fortalecer proyectos de mejora en las localidades.</t>
+          <t>¿Cómo funciona?</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>Nochi secretaría uan teguichiualoyan iga Kaltlayekana sepan teguitij iga kichikauaskej tlachiualmej tlen kikualtlaliaj altepetsitsin.</t>
+          <t>¿Kenin teguiti?</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Equidad y dignidad</t>
+          <t>Diagnóstico territorial</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Sepan tiuejueyij uan tlakaitalistle</t>
+          <t>Tlatemolistle ipan tlale</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>El objetivo es construir una sociedad más equitativa y justa, donde todas las personas puedan vivir con dignidad.</t>
+          <t>Las comunidades se identifican mediante un diagnóstico realizado por la Jefatura de la Oficina de la Gubernatura, que define los polígonos de atención.</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Tlen tiknegui: tikchiuaskej se altepetl kanin nochi sepan katej uan melauak, kanin nochi tlatlaga ueliskej nemiskej iga tlakaitalistle.</t>
+          <t>Altepetsitsin moixmatij iga se tlatemolistle tlen kichiua Jefatura de la Oficina de la Gubernatura, uan yejua kitlalia polígono kanin motekipanos.</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>El programa en cifras</t>
+          <t>Promotores comunitarios</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Nin tlapaleuilistle iga tlapoualli</t>
+          <t>Tlapaleuianij ipan altepetsitsin</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Localidades</t>
+          <t>Promotores capacitados visitan a la población para escuchar y conocer a detalle sus necesidades básicas.</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin</t>
+          <t>Tlapaleuianij tlen momachtijkej kinpaxalouaj tlatlaga iga kinkaguiskej uan kualtsin kiixmatiskej tlen kinmonekij.</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Polígonos</t>
+          <t>Acción coordinada</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Teguitl tlen sepan mochiua</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -2541,12 +2541,12 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Municipios</t>
+          <t>Cada secretaría y organismo del Poder Ejecutivo lleva a cabo acciones coordinadas para fortalecer proyectos de mejora en las localidades.</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Altepemej</t>
+          <t>Nochi secretaría uan teguichiualoyan iga Kaltlayekana sepan teguitij iga kichikauaskej tlachiualmej tlen kikualtlaliaj altepetsitsin.</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Habitantes</t>
+          <t>Equidad y dignidad</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Tlatlaga</t>
+          <t>Sepan tiuejueyij uan tlakaitalistle</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Escuelas con aula</t>
+          <t>El objetivo es construir una sociedad más equitativa y justa, donde todas las personas puedan vivir con dignidad.</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan iga tepostlapoualli</t>
+          <t>Tlen tiknegui: tikchiuaskej se altepetl kanin nochi sepan katej uan melauak, kanin nochi tlatlaga ueliskej nemiskej iga tlakaitalistle.</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Hitos</t>
+          <t>El programa en cifras</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Tlen ueyi omochiu</t>
+          <t>Nin tlapaleuilistle iga tlapoualli</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -2665,12 +2665,12 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>{n} de abril de {n}</t>
+          <t>Localidades</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>{n} abril, {n} xiuitl</t>
+          <t>Altepetsitsin</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Presentación del programa</t>
+          <t>Polígonos</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Teixpantilistle iga nin tlapaleuilistle</t>
+          <t>Polígono</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Arranca la primera etapa con {n} comunidades y {n} promotores comunitarios capacitados.</t>
+          <t>Municipios</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Peua achtopa tlachiualistle iga {n} altepetsitsin uan {n} tlapaleuianij tlen momachtijkej.</t>
+          <t>Altepemej</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -2758,16 +2758,20 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Diciembre {n} – enero {n}</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="n"/>
-      <c r="F71" s="4" t="n"/>
-      <c r="G71" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Habitantes</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Tlatlaga</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="n">
@@ -2785,12 +2789,12 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>La ATDEM instala aulas de cómputo en {n} escuelas de los polígonos.</t>
+          <t>Escuelas con aula</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>ATDEM kitlalia tepostlapoualli ipan {n} kaltlamachtiloyan tlen polígono.</t>
+          <t>Kaltlamachtiloyan iga tepostlapoualli</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -2816,12 +2820,12 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Delimitación vigente</t>
+          <t>Hitos</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Polígono tlen axan</t>
+          <t>Tlen ueyi omochiu</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -2847,12 +2851,12 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>{n} localidades en {n} polígonos de atención, que se analizan en este tablero.</t>
+          <t>{n} de abril de {n}</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>{n} altepetsitsin ipan {n} polígono, tlen motlachilia ipan nin tlapoualli.</t>
+          <t>{n} abril, {n} xiuitl</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -2878,12 +2882,12 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Grados de marginación</t>
+          <t>Presentación del programa</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Tlapoual iknoyotl</t>
+          <t>Teixpantilistle iga nin tlapaleuilistle</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -2909,12 +2913,12 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Localidades ({n})</t>
+          <t>Arranca la primera etapa con {n} comunidades y {n} promotores comunitarios capacitados.</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin ({n})</t>
+          <t>Peua achtopa tlachiualistle iga {n} altepetsitsin uan {n} tlapaleuianij tlen momachtijkej.</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -2940,20 +2944,16 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Comunidades prioritarias</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>Altepetsitsin tlen achtopa</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="n"/>
+          <t>Diciembre {n} – enero {n}</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="n"/>
+      <c r="F77" s="4" t="n"/>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Sin grado de marginación</t>
+          <t>La ATDEM instala aulas de cómputo en {n} escuelas de los polígonos.</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Amo kipia itlapoual iknoyotl</t>
+          <t>ATDEM kitlalia tepostlapoualli ipan {n} kaltlamachtiloyan tlen polígono.</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>¿Qué encontrarás en este tablero?</t>
+          <t>Delimitación vigente</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>¿Tlen tikajsis ipan nin tlapoualli?</t>
+          <t>Polígono tlen axan</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Indicadores de población, vivienda, tecnologías de la información, salud, educación y economía de las {n} localidades de los {n} polígonos vigentes, por localidad o por polígono completo.</t>
+          <t>{n} localidades en {n} polígonos de atención, que se analizan en este tablero.</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Tlapoualli iga tlatlaga, kalmej, tepostlapoualli uan internet, pajtilistle, temachtilistle uan tomin ipan {n} altepetsitsin tlen {n} polígono tlen axan, iga se altepetsin o iga se polígono nochi.</t>
+          <t>{n} altepetsitsin ipan {n} polígono, tlen motlachilia ipan nin tlapoualli.</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Ir a Análisis Demográfico</t>
+          <t>Grados de marginación</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Xiyau ipan Tlapoualli iga tlatlaga</t>
+          <t>Tlapoual iknoyotl</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Mapa de las {n} escuelas donde ATDEM instaló aulas de cómputo en los polígonos TPBV: computadoras, nivel educativo y ubicación de cada una.</t>
+          <t>Localidades ({n})</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Tlalamatl iga {n} kaltlamachtiloyan kanin ATDEM kitlalij tepostlapoualli ipan polígono TPBV: tepostlapoualmej, temachtilistle uan kanin katej.</t>
+          <t>Altepetsitsin ({n})</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Ir a Aulas Tecnológicas</t>
+          <t>Comunidades prioritarias</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Xiyau ipan Tlamachtiloyan iga tepostlapoualli</t>
+          <t>Altepetsitsin tlen achtopa</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Mapa de las dependencias estatales que ya cuentan con la red Wi-Fi pública y gratuita de la ATDEM: sedes, secretarías y puntos de acceso.</t>
+          <t>Sin grado de marginación</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Tlalamatl iga teguichiualoyan iga Kaltlayekana tlen ya kipiaj matlatl Wi-Fi tlapojtok uan amo iga tomin tlen ATDEM: kalmej, secretarías uan kanin mosaloua.</t>
+          <t>Amo kipia itlapoual iknoyotl</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Ir a Red La tierra que nos une</t>
+          <t>¿Qué encontrarás en este tablero?</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Xiyau ipan Matlatl Nin tlale tech sepaneloa</t>
+          <t>¿Tlen tikajsis ipan nin tlapoualli?</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Indicadores de población, vivienda, tecnologías de la información, salud, educación y economía de las {n} localidades de los {n} polígonos vigentes, por localidad o por polígono completo.</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Tepostlaketsalmej iga uejka tlanonotsalistle</t>
+          <t>Tlapoualli iga tlatlaga, kalmej, tepostlapoualli uan internet, pajtilistle, temachtilistle uan tomin ipan {n} altepetsitsin tlen {n} polígono tlen axan, iga se altepetsin o iga se polígono nochi.</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Sitios y torres de la red estatal por municipio y sector (gobierno, educación, salud y seguridad). Por seguridad se muestran solo de forma agregada.</t>
+          <t>Ir a Análisis Demográfico</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Sitios uan tepostlaketsalmej tlen imatlau Kaltlayekana, iga altepetl uan teguitl (kaltlayekana, temachtilistle, pajtilistle uan tlajpialistle). Iga tlajpialistle san monextiaj sepan.</t>
+          <t>Xiyau ipan Tlapoualli iga tlatlaga</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Ir a Telecomunicaciones</t>
+          <t>Mapa de las {n} escuelas donde ATDEM instaló aulas de cómputo en los polígonos TPBV: computadoras, nivel educativo y ubicación de cada una.</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Xiyau ipan Uejka tlanonotsalistle</t>
+          <t>Tlalamatl iga {n} kaltlamachtiloyan kanin ATDEM kitlalij tepostlapoualli ipan polígono TPBV: tepostlapoualmej, temachtilistle uan kanin katej.</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Descarga en CSV y KML las bases de datos del tablero: localidades y polígonos vigentes, Aulas Tecnológicas y límites municipales.</t>
+          <t>Ir a Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga ipan CSV uan KML itlapoual nin tablero: altepetsitsin uan polígono tlen axan, Tlamachtiloyan iga tepostlapoualli uan itlalxelol altepemej.</t>
+          <t>Xiyau ipan Tlamachtiloyan iga tepostlapoualli</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Ir a Datos Abiertos</t>
+          <t>Mapa de las dependencias estatales que ya cuentan con la red Wi-Fi pública y gratuita de la ATDEM: sedes, secretarías y puntos de acceso.</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Xiyau ipan Tlapoualli tlapojtok</t>
+          <t>Tlalamatl iga teguichiualoyan iga Kaltlayekana tlen ya kipiaj matlatl Wi-Fi tlapojtok uan amo iga tomin tlen ATDEM: kalmej, secretarías uan kanin mosaloua.</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Reportes Institucionales</t>
+          <t>Ir a Red La tierra que nos une</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Tlapoualamatl iga Kaltlayekana</t>
+          <t>Xiyau ipan Matlatl Nin tlale tech sepaneloa</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -3405,12 +3405,12 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Genera, para la localidad o el polígono que estés viendo, un documento formal con portada y todas las tablas de indicadores, listo para imprimir o exportar a PDF.</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Xikchiua, iga altepetsin o polígono tlen tikitta, se amatl iga ixko uan nochi tlapoualli, iga tiktlalis ipan amatl o ipan PDF.</t>
+          <t>Tepostlaketsalmej iga uejka tlanonotsalistle</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Ir a generar un reporte</t>
+          <t>Sitios y torres de la red estatal por municipio y sector (gobierno, educación, salud y seguridad). Por seguridad se muestran solo de forma agregada.</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Xikchiua se tlapoualamatl</t>
+          <t>Sitios uan tepostlaketsalmej tlen imatlau Kaltlayekana, iga altepetl uan teguitl (kaltlayekana, temachtilistle, pajtilistle uan tlajpialistle). Iga tlajpialistle san monextiaj sepan.</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -3467,12 +3467,12 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Cómo empezar</t>
+          <t>Ir a Telecomunicaciones</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Kenin tipeuas</t>
+          <t>Xiyau ipan Uejka tlanonotsalistle</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Filtra por polígono o localidad</t>
+          <t>Descarga en CSV y KML las bases de datos del tablero: localidades y polígonos vigentes, Aulas Tecnológicas y límites municipales.</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Xikpepena polígono o altepetsin</t>
+          <t>Xikuiga ipan CSV uan KML itlapoual nin tablero: altepetsitsin uan polígono tlen axan, Tlamachtiloyan iga tepostlapoualli uan itlalxelol altepemej.</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>En Análisis Demográfico, usa los selectores de la parte superior, o entra directo a un polígono desde el mapa o la lista de localidades.</t>
+          <t>Ir a Datos Abiertos</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Ipan Tlapoualli iga tlatlaga, xiktekiuti tlapepenalli tlen kaninpa, o xiyau nimantsin ipan se polígono iga tlalamatl o iga itlapoual altepetsitsin.</t>
+          <t>Xiyau ipan Tlapoualli tlapojtok</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -3560,12 +3560,12 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Explora los indicadores</t>
+          <t>Reportes Institucionales</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Xiktlachili tlapoualli</t>
+          <t>Tlapoualamatl iga Kaltlayekana</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Revisa las tarjetas de población, vivienda, salud, educación, economía y la pirámide poblacional, además del mapa de ubicación.</t>
+          <t>Genera, para la localidad o el polígono que estés viendo, un documento formal con portada y todas las tablas de indicadores, listo para imprimir o exportar a PDF.</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Xiktlachili tlapoualli iga tlatlaga, kalmej, pajtilistle, temachtilistle, tomin uan keski xiuitl kipiaj, uan tlalamatl kanin katej.</t>
+          <t>Xikchiua, iga altepetsin o polígono tlen tikitta, se amatl iga ixko uan nochi tlapoualli, iga tiktlalis ipan amatl o ipan PDF.</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Consulta las aulas</t>
+          <t>Ir a generar un reporte</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Xiktlachili tlamachtiloyan</t>
+          <t>Xikchiua se tlapoualamatl</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Revisa el mapa de Aulas Tecnológicas instaladas en las escuelas de los polígonos.</t>
+          <t>Cómo empezar</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Xiktlachili tlalamatl iga Tlamachtiloyan iga tepostlapoualli tlen motlalijkej ipan kaltlamachtiloyan tlen polígono.</t>
+          <t>Kenin tipeuas</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Descarga los datos</t>
+          <t>Filtra por polígono o localidad</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga tlapoualli</t>
+          <t>Xikpepena polígono o altepetsin</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>En Datos Abiertos encontrarás las bases de datos del tablero en CSV y KML.</t>
+          <t>En Análisis Demográfico, usa los selectores de la parte superior, o entra directo a un polígono desde el mapa o la lista de localidades.</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Ipan Tlapoualli tlapojtok tikajsis itlapoual nin tablero ipan CSV uan KML.</t>
+          <t>Ipan Tlapoualli iga tlatlaga, xiktekiuti tlapepenalli tlen kaninpa, o xiyau nimantsin ipan se polígono iga tlalamatl o iga itlapoual altepetsitsin.</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Genera tu reporte</t>
+          <t>Explora los indicadores</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Xikchiua motlapoualamau</t>
+          <t>Xiktlachili tlapoualli</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Usa el botón "Reporte Institucional" para exportar un documento formal en PDF de lo que estés viendo.</t>
+          <t>Revisa las tarjetas de población, vivienda, salud, educación, economía y la pirámide poblacional, además del mapa de ubicación.</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Xiktekiuti "Tlapoualamatl iga Kaltlayekana" iga tikixtis se amatl PDF iga tlen tikitta.</t>
+          <t>Xiktlachili tlapoualli iga tlatlaga, kalmej, pajtilistle, temachtilistle, tomin uan keski xiuitl kipiaj, uan tlalamatl kanin katej.</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Población Total</t>
+          <t>Consulta las aulas</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Nochi tlatlaga</t>
+          <t>Xiktlachili tlamachtiloyan</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Viviendas Totales</t>
+          <t>Revisa el mapa de Aulas Tecnológicas instaladas en las escuelas de los polígonos.</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Nochi kalmej</t>
+          <t>Xiktlachili tlalamatl iga Tlamachtiloyan iga tepostlapoualli tlen motlalijkej ipan kaltlamachtiloyan tlen polígono.</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Afiliación a Salud</t>
+          <t>Descarga los datos</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>Tlen kipiaj pajtilistle</t>
+          <t>Xikuiga tlapoualli</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -3901,12 +3901,12 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Localidades Totales</t>
+          <t>En Datos Abiertos encontrarás las bases de datos del tablero en CSV y KML.</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Nochi altepetsitsin</t>
+          <t>Ipan Tlapoualli tlapojtok tikajsis itlapoual nin tablero ipan CSV uan KML.</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Información General</t>
+          <t>Genera tu reporte</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>Tlamachilistle</t>
+          <t>Xikchiua motlapoualamau</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Municipio</t>
+          <t>Usa el botón "Reporte Institucional" para exportar un documento formal en PDF de lo que estés viendo.</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Altepetl</t>
+          <t>Xiktekiuti "Tlapoualamatl iga Kaltlayekana" iga tikixtis se amatl PDF iga tlen tikitta.</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>{n} municipios</t>
+          <t>Población Total</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>{n} altepemej</t>
+          <t>Nochi tlatlaga</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -4025,12 +4025,12 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Región</t>
+          <t>Viviendas Totales</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Tlalxeloli</t>
+          <t>Nochi kalmej</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Afiliación a Salud</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Tlen kipiaj pajtilistle</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Polígonos incluidos</t>
+          <t>Localidades Totales</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Polígono tlen kipia</t>
+          <t>Nochi altepetsitsin</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
@@ -4118,12 +4118,12 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Localidades incluidas</t>
+          <t>Información General</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin tlen kipia</t>
+          <t>Tlamachilistle</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>{n} de {n}</t>
+          <t>Municipio</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>{n} ipan {n}</t>
+          <t>Altepetl</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Grados de Marginación</t>
+          <t>{n} municipios</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>Tlapoual iknoyotl</t>
+          <t>{n} altepemej</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Todas las Localidades</t>
+          <t>Región</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>Nochi altepetsitsin</t>
+          <t>Tlalxeloli</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Ubicación Geográfica</t>
+          <t>Polígono</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>Kanin katej</t>
+          <t>Polígono</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Localidad</t>
+          <t>Polígonos incluidos</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>Altepetsin</t>
+          <t>Polígono tlen kipia</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
@@ -4304,16 +4304,20 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Polígono TPBV</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="n"/>
-      <c r="F121" s="4" t="n"/>
-      <c r="G121" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Localidades incluidas</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>Altepetsitsin tlen kipia</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="n">
@@ -4326,17 +4330,17 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Zoom in</t>
+          <t>{n} de {n}</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Xikueyichiua</t>
+          <t>{n} ipan {n}</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
@@ -4357,17 +4361,17 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Zoom out</t>
+          <t>Grados de Marginación</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>Xiktepitonchiua</t>
+          <t>Tlapoual iknoyotl</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
@@ -4393,12 +4397,12 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>{n} de {n} localidades no tienen coincidencia en el Censo INEGI {n} (suelen ser colonias/barrios dentro de una cabecera urbana). Su población sí está incluida en el total (vía la Lista TPBV {n}), pero vivienda, salud, educación y economía no — esos indicadores solo suman las localidades con coincidencia censal. Revísalas en la lista de localidades.</t>
+          <t>Todas las Localidades</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>{n} ipan {n} altepetsitsin amo monextiaj ipan Censo INEGI {n} (miakpa colonias o barrios ipan se ueyi altepetl). Intlatlaga motlapouaj ipan nochi (iga Lista TPBV {n}), san kalmej, pajtilistle, temachtilistle uan tomin amo — nin tlapoualli san kinsentlalia altepetsitsin tlen monextiaj ipan censo. Xikintlachili ipan itlapoual altepetsitsin.</t>
+          <t>Nochi altepetsitsin</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
@@ -4424,12 +4428,12 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Demografía</t>
+          <t>Ubicación Geográfica</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>Tlatlaga iga tlapoualli</t>
+          <t>Kanin katej</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
@@ -4455,12 +4459,12 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Población</t>
+          <t>Localidad</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>Tlatlaga</t>
+          <t>Altepetsin</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
@@ -4486,20 +4490,16 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Mujeres</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="inlineStr">
-        <is>
-          <t>Soamej</t>
-        </is>
-      </c>
-      <c r="F127" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G127" s="4" t="n"/>
+          <t>Polígono TPBV</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="n"/>
+      <c r="F127" s="4" t="n"/>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="n">
@@ -4512,17 +4512,17 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Hombres</t>
+          <t>Zoom in</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>Tlagamej</t>
+          <t>Xikueyichiua</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -4543,17 +4543,17 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Población Indígena y Afromexicana</t>
+          <t>Zoom out</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>Maseualmej uan afromexikanojmej</t>
+          <t>Xiktepitonchiua</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Habla Lengua Indígena</t>
+          <t>{n} de {n} localidades no tienen coincidencia en el Censo INEGI {n} (suelen ser colonias/barrios dentro de una cabecera urbana). Su población sí está incluida en el total (vía la Lista TPBV {n}), pero vivienda, salud, educación y economía no — esos indicadores solo suman las localidades con coincidencia censal. Revísalas en la lista de localidades.</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>Kitlajtouaj maseualtlajtolli</t>
+          <t>{n} ipan {n} altepetsitsin amo monextiaj ipan Censo INEGI {n} (miakpa colonias o barrios ipan se ueyi altepetl). Intlatlaga motlapouaj ipan nochi (iga Lista TPBV {n}), san kalmej, pajtilistle, temachtilistle uan tomin amo — nin tlapoualli san kinsentlalia altepetsitsin tlen monextiaj ipan censo. Xikintlachili ipan itlapoual altepetsitsin.</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
@@ -4610,12 +4610,12 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Monolingüe (no habla español)</t>
+          <t>Demografía</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>San se tlajtolli (amo kitlajtouaj kaxtilan tlajtolli)</t>
+          <t>Tlatlaga iga tlapoualli</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Hogares Censales Indígenas</t>
+          <t>Población</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Kalmej kanin chantij maseualmej</t>
+          <t>Tlatlaga</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Pob. Afromexicana</t>
+          <t>Mujeres</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>Afromexikanojmej</t>
+          <t>Soamej</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Estructura de Población por Edad y Sexo</t>
+          <t>Hombres</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Tlatlaga iga ixiuiu, soamej uan tlagamej</t>
+          <t>Tlagamej</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
@@ -4729,17 +4729,17 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>{n}+ años · Mujeres: {n} · Hombres: {n}</t>
+          <t>Población Indígena y Afromexicana</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>{n}+ xiuitl · Soamej: {n} · Tlagamej: {n}</t>
+          <t>Maseualmej uan afromexikanojmej</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
@@ -4760,17 +4760,17 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>{n}-{n} años · Mujeres: {n} · Hombres: {n}</t>
+          <t>Habla Lengua Indígena</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>{n}-{n} xiuitl · Soamej: {n} · Tlagamej: {n}</t>
+          <t>Kitlajtouaj maseualtlajtolli</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Razón de dependencia demográfica</t>
+          <t>Monolingüe (no habla español)</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>Keski moneki ma kinpaleuikaj</t>
+          <t>San se tlajtolli (amo kitlajtouaj kaxtilan tlajtolli)</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Personas dependientes ({n}-{n} y {n}+) por cada {n} en edad de trabajar ({n}-{n}: {n})</t>
+          <t>Hogares Censales Indígenas</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Akin moneki ma kinpaleuikaj ({n}-{n} uan {n}+) iga nochi {n} tlen ueli teguitij ({n}-{n}: {n})</t>
+          <t>Kalmej kanin chantij maseualmej</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y Servicios</t>
+          <t>Pob. Afromexicana</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>Kalle uan tlen kipia</t>
+          <t>Afromexikanojmej</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Vivienda</t>
+          <t>Estructura de Población por Edad y Sexo</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Kalle</t>
+          <t>Tlatlaga iga ixiuiu, soamej uan tlagamej</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Total Viviendas</t>
+          <t>{n}+ años · Mujeres: {n} · Hombres: {n}</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>Nochi kalmej</t>
+          <t>{n}+ xiuitl · Soamej: {n} · Tlagamej: {n}</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
@@ -4946,17 +4946,17 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Piso de Tierra</t>
+          <t>{n}-{n} años · Mujeres: {n} · Hombres: {n}</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>Tlalchi san tlale</t>
+          <t>{n}-{n} xiuitl · Soamej: {n} · Tlagamej: {n}</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Un Solo Cuarto</t>
+          <t>Razón de dependencia demográfica</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>San se kalijtik</t>
+          <t>Keski moneki ma kinpaleuikaj</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
@@ -5013,12 +5013,12 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Con Hacinamiento</t>
+          <t>Personas dependientes ({n}-{n} y {n}+) por cada {n} en edad de trabajar ({n}-{n}: {n})</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>Miak chantij ipan se kalle</t>
+          <t>Akin moneki ma kinpaleuikaj ({n}-{n} uan {n}+) iga nochi {n} tlen ueli teguitij ({n}-{n}: {n})</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
@@ -5044,12 +5044,12 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Tecnologías de Información (TIC)</t>
+          <t>Vivienda y Servicios</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>Tepostlapoualli uan tlanonotsalistle (TIC)</t>
+          <t>Kalle uan tlen kipia</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Con Celular</t>
+          <t>Vivienda</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr">
         <is>
-          <t>Kipiaj celular</t>
+          <t>Kalle</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Con Computadora</t>
+          <t>Total Viviendas</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>Kipiaj tepostlapoualli</t>
+          <t>Nochi kalmej</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Con Internet</t>
+          <t>Piso de Tierra</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>Kipiaj internet</t>
+          <t>Tlalchi san tlale</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Bienes y Servicios en la Vivienda</t>
+          <t>Un Solo Cuarto</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>Tlen kipiaj ipan kalle</t>
+          <t>San se kalijtik</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
@@ -5199,16 +5199,20 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Refrigerador</t>
-        </is>
-      </c>
-      <c r="E150" s="4" t="n"/>
-      <c r="F150" s="4" t="n"/>
-      <c r="G150" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Con Hacinamiento</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>Miak chantij ipan se kalle</t>
+        </is>
+      </c>
+      <c r="F150" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n">
@@ -5226,16 +5230,20 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Lavadora</t>
-        </is>
-      </c>
-      <c r="E151" s="4" t="n"/>
-      <c r="F151" s="4" t="n"/>
-      <c r="G151" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Tecnologías de Información (TIC)</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>Tepostlapoualli uan tlanonotsalistle (TIC)</t>
+        </is>
+      </c>
+      <c r="F151" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n">
@@ -5253,16 +5261,20 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Automóvil</t>
-        </is>
-      </c>
-      <c r="E152" s="4" t="n"/>
-      <c r="F152" s="4" t="n"/>
-      <c r="G152" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Con Celular</t>
+        </is>
+      </c>
+      <c r="E152" s="5" t="inlineStr">
+        <is>
+          <t>Kipiaj celular</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n">
@@ -5280,12 +5292,12 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Agua Entubada</t>
+          <t>Con Computadora</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>Atl ipan kalle</t>
+          <t>Kipiaj tepostlapoualli</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
@@ -5311,12 +5323,12 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Drenaje</t>
+          <t>Con Internet</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>Apantle (drenaje)</t>
+          <t>Kipiaj internet</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
@@ -5342,12 +5354,12 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Bienes y Servicios en la Vivienda</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>Tlauille</t>
+          <t>Tlen kipiaj ipan kalle</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
@@ -5373,20 +5385,16 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Salud y Bienestar</t>
-        </is>
-      </c>
-      <c r="E156" s="5" t="inlineStr">
-        <is>
-          <t>Pajtilistle uan kuale nemilistle</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G156" s="4" t="n"/>
+          <t>Refrigerador</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="n"/>
+      <c r="F156" s="4" t="n"/>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n">
@@ -5404,20 +5412,16 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Servicios de Salud</t>
-        </is>
-      </c>
-      <c r="E157" s="5" t="inlineStr">
-        <is>
-          <t>Tlapaleuilistle iga pajtilistle</t>
-        </is>
-      </c>
-      <c r="F157" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G157" s="4" t="n"/>
+          <t>Lavadora</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="n"/>
+      <c r="F157" s="4" t="n"/>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="n">
@@ -5435,20 +5439,16 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Total Afiliados</t>
-        </is>
-      </c>
-      <c r="E158" s="5" t="inlineStr">
-        <is>
-          <t>Nochi tlen kipiaj pajtilistle</t>
-        </is>
-      </c>
-      <c r="F158" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G158" s="4" t="n"/>
+          <t>Automóvil</t>
+        </is>
+      </c>
+      <c r="E158" s="4" t="n"/>
+      <c r="F158" s="4" t="n"/>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Sin Afiliación</t>
+          <t>Agua Entubada</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>Amo kipiaj pajtilistle</t>
+          <t>Atl ipan kalle</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Afiliados al IMSS</t>
+          <t>Drenaje</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>Kipiaj IMSS</t>
+          <t>Apantle (drenaje)</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
@@ -5528,12 +5528,12 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Afiliados al ISSSTE</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>Kipiaj ISSSTE</t>
+          <t>Tlauille</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Otros Servicios de Salud</t>
+          <t>Salud y Bienestar</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>Siguin tlapaleuilistle iga pajtilistle</t>
+          <t>Pajtilistle uan kuale nemilistle</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Discapacidad y Condiciones de Salud</t>
+          <t>Servicios de Salud</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>Amo uelilistle uan kogolistle</t>
+          <t>Tlapaleuilistle iga pajtilistle</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
@@ -5621,12 +5621,12 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Con Discapacidad</t>
+          <t>Total Afiliados</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>Kipiaj amo uelilistle</t>
+          <t>Nochi tlen kipiaj pajtilistle</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Con Limitación</t>
+          <t>Sin Afiliación</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>Kipiaj tlen kintsakua</t>
+          <t>Amo kipiaj pajtilistle</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Con Problema o Condición Mental</t>
+          <t>Afiliados al IMSS</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>Kipiaj kogolistle ipan intsontekon</t>
+          <t>Kipiaj IMSS</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Educación y Economía</t>
+          <t>Afiliados al ISSSTE</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>Temachtilistle uan tomin</t>
+          <t>Kipiaj ISSSTE</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Otros Servicios de Salud</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>Temachtilistle</t>
+          <t>Siguin tlapaleuilistle iga pajtilistle</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Grado Promedio de Escolaridad</t>
+          <t>Discapacidad y Condiciones de Salud</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>Keski xiuitl momachtijkej</t>
+          <t>Amo uelilistle uan kogolistle</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>{n} años</t>
+          <t>Con Discapacidad</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>{n} xiuitl</t>
+          <t>Kipiaj amo uelilistle</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Analfabetas ({n}+)</t>
+          <t>Con Limitación</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>Amo kimatij tlajkuiloj ({n}+)</t>
+          <t>Kipiaj tlen kintsakua</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Sin Educación Básica Completa ({n}+)</t>
+          <t>Con Problema o Condición Mental</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>Amo kitlamiltijkej achtopa temachtilistle ({n}+)</t>
+          <t>Kipiaj kogolistle ipan intsontekon</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Niñas/os {n}-{n} años sin asistir a la escuela</t>
+          <t>Educación y Economía</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>Pipiltontij {n}-{n} xiuitl tlen amo yaj kaltlamachtiloyan</t>
+          <t>Temachtilistle uan tomin</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
@@ -5931,12 +5931,12 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Adolescentes {n}-{n} años sin asistir a la escuela</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Telpogamej {n}-{n} xiuitl tlen amo yaj kaltlamachtiloyan</t>
+          <t>Temachtilistle</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
@@ -5962,12 +5962,12 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Económicamente Activa (PEA)</t>
+          <t>Grado Promedio de Escolaridad</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>Tlen ueli teguitij (PEA)</t>
+          <t>Keski xiuitl momachtijkej</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
@@ -5993,12 +5993,12 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>Ocupada</t>
+          <t>{n} años</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
         <is>
-          <t>Teguitij</t>
+          <t>{n} xiuitl</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
@@ -6024,12 +6024,12 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Desocupada</t>
+          <t>Analfabetas ({n}+)</t>
         </is>
       </c>
       <c r="E177" s="5" t="inlineStr">
         <is>
-          <t>Amo kipiaj teguitl</t>
+          <t>Amo kimatij tlajkuiloj ({n}+)</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Ocupada en Sector Primario</t>
+          <t>Sin Educación Básica Completa ({n}+)</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>Teguitij ipan milpa uan tlale</t>
+          <t>Amo kitlamiltijkej achtopa temachtilistle ({n}+)</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="B179" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (un polígono)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C179" s="4" t="inlineStr">
@@ -6086,12 +6086,12 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Localidades en el Polígono</t>
+          <t>Niñas/os {n}-{n} años sin asistir a la escuela</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin ipan polígono</t>
+          <t>Pipiltontij {n}-{n} xiuitl tlen amo yaj kaltlamachtiloyan</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (un polígono)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
@@ -6117,12 +6117,12 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Localidades en este Polígono</t>
+          <t>Adolescentes {n}-{n} años sin asistir a la escuela</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin ipan nin polígono</t>
+          <t>Telpogamej {n}-{n} xiuitl tlen amo yaj kaltlamachtiloyan</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (una localidad)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Grado de Marginación</t>
+          <t>Económicamente Activa (PEA)</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>Tlapoual iknoyotl</t>
+          <t>Tlen ueli teguitij (PEA)</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="B182" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (una localidad)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C182" s="4" t="inlineStr">
@@ -6179,16 +6179,20 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Polígono {n} · {d}</t>
-        </is>
-      </c>
-      <c r="E182" s="4" t="n"/>
-      <c r="F182" s="4" t="n"/>
-      <c r="G182" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Ocupada</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="inlineStr">
+        <is>
+          <t>Teguitij</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="n">
@@ -6196,7 +6200,7 @@
       </c>
       <c r="B183" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (una localidad)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C183" s="4" t="inlineStr">
@@ -6206,12 +6210,12 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Marginación: {d}</t>
+          <t>Desocupada</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>Iknoyotl: {d}</t>
+          <t>Amo kipiaj teguitl</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
@@ -6227,22 +6231,22 @@
       </c>
       <c r="B184" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (una localidad)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Close popup</t>
+          <t>Ocupada en Sector Primario</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>Xiktsagua</t>
+          <t>Teguitij ipan milpa uan tlale</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
@@ -6258,7 +6262,7 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (localidad sin datos censales)</t>
+          <t>Inicio (buscador de comunidades)</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -6268,12 +6272,12 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Coordenada capturada manualmente</t>
+          <t>Sí, esta comunidad está en el programa.</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>Kanin katej, omojkuilo iga ma</t>
+          <t>Kema, nin altepetsin kalaktok ipan nin tlapaleuilistle.</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
@@ -6289,7 +6293,7 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (localidad sin datos censales)</t>
+          <t>Inicio (buscador de comunidades)</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
@@ -6299,20 +6303,16 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Sin Datos Censales Disponibles</t>
-        </is>
-      </c>
-      <c r="E186" s="5" t="inlineStr">
-        <is>
-          <t>Amo kipia itlapoual censo</t>
-        </is>
-      </c>
-      <c r="F186" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G186" s="4" t="n"/>
+          <t>{d} · Polígono {d}</t>
+        </is>
+      </c>
+      <c r="E186" s="4" t="n"/>
+      <c r="F186" s="4" t="n"/>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>No requiere traducción (nombres y la palabra «Polígono»).</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (localidad sin datos censales)</t>
+          <t>Inicio (buscador de comunidades)</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -6330,12 +6330,12 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>No se encontró una coincidencia confiable para {d} en el Censo INEGI {n} (ITER Morelos). Esto ocurre principalmente con colonias/barrios urbanos que no se registran como localidad censal independiente. El mapa muestra su ubicación (coordenada capturada manualmente) dentro de polígono {n}.</t>
+          <t>Ver sus datos</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>Amo omonexti {d} ipan Censo INEGI {n} (ITER Morelos). Nin panoa ogachi iga colonias o barrios ipan ueyi altepetl tlen amo motlapouaj kemej altepetsin. Tlalamatl kinextia kanin katej (omojkuilo iga ma) ipan polígono {n}.</t>
+          <t>Xikita itlapoual</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (localidad sin datos censales)</t>
+          <t>Inicio (buscador de comunidades)</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Población reportada (Lista TPBV {n})</t>
+          <t>Encontramos {n} comunidades del programa con ese nombre.</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>Tlatlaga tlen motlapoukej (Lista TPBV {n})</t>
+          <t>Otikajsike {n} altepetsitsin tlen nin tlapaleuilistle tlen kipiaj nin itoga.</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (filtro personalizado)</t>
+          <t>Inicio (buscador de comunidades)</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -6392,12 +6392,12 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Elige los polígonos a comparar</t>
+          <t>Y {n} comunidades más. Escribe más letras para afinar la búsqueda.</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>Xikpepena polígono tlen tikinneneuilis</t>
+          <t>Uan ogachi {n} altepetsitsin. Xiktlajkuilo ogachi tlajkuilolli iga tiktemos kuale.</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (filtro personalizado)</t>
+          <t>Inicio (buscador de comunidades)</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Limpiar</t>
+          <t>{d} tiene {n} comunidades en el programa.</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>Xikpojpoa</t>
+          <t>{d} kipia {n} altepetsitsin ipan nin tlapaleuilistle.</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Inicio (buscador de comunidades)</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Territorios de Paz y Buen Vivir · Educación digital</t>
+          <t>{d} no tiene comunidades en la delimitación vigente del programa.</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>Territorios de Paz y Buen Vivir · Temachtilistle iga tepostlapoualli</t>
+          <t>{d} amo kipia altepetsitsin ipan nin tlapaleuilistle axan.</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (un polígono)</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
@@ -6485,12 +6485,12 @@
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Para reducir la brecha digital desde edades tempranas, la Agencia de Transformación Digital del Estado de Morelos (ATDEM), en coordinación con la Secretaría de Educación y el Instituto de Educación Básica del Estado de Morelos (IEBEM), equipó aulas de cómputo en {n} escuelas de {n} municipios ubicadas en los polígonos de Territorios de Paz y Buen Vivir.</t>
+          <t>Localidades en el Polígono</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>Iga ma moyekchiua tlen amo kipiaj tepostlapoualli kuak tsitsikitsin, Agencia de Transformación Digital del Estado de Morelos (ATDEM), sepan iga Secretaría de Educación uan Instituto de Educación Básica del Estado de Morelos (IEBEM), kitlalij tepostlapoualli ipan {n} kaltlamachtiloyan ipan {n} altepemej tlen katej ipan polígono Territorios de Paz y Buen Vivir.</t>
+          <t>Altepetsitsin ipan polígono</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (un polígono)</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -6516,12 +6516,12 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Con computadoras conectadas a internet y software educativo, niñas, niños y jóvenes fortalecen sus procesos de aprendizaje, desarrollan habilidades digitales y amplían sus oportunidades en entornos con mayor infraestructura tecnológica.</t>
+          <t>Localidades en este Polígono</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>Iga tepostlapoualli tlen kipiaj internet uan programas iga temachtilistle, pipiltontij uan telpogamej ogachi kualtsin momachtiaj, kimachtiaj tepostlapoualli uan ogachi ojmej kipiaj.</t>
+          <t>Altepetsitsin ipan nin polígono</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (una localidad)</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -6547,16 +6547,20 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Secretaría de Educación</t>
-        </is>
-      </c>
-      <c r="E194" s="4" t="n"/>
-      <c r="F194" s="4" t="n"/>
-      <c r="G194" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Grado de Marginación</t>
+        </is>
+      </c>
+      <c r="E194" s="5" t="inlineStr">
+        <is>
+          <t>Tlapoual iknoyotl</t>
+        </is>
+      </c>
+      <c r="F194" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n">
@@ -6564,7 +6568,7 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (una localidad)</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -6574,20 +6578,16 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Instalación: diciembre {n} a enero {n}</t>
-        </is>
-      </c>
-      <c r="E195" s="5" t="inlineStr">
-        <is>
-          <t>Motlalij: peuak diciembre {n}, tlamik enero {n}</t>
-        </is>
-      </c>
-      <c r="F195" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G195" s="4" t="n"/>
+          <t>Polígono {n} · {d}</t>
+        </is>
+      </c>
+      <c r="E195" s="4" t="n"/>
+      <c r="F195" s="4" t="n"/>
+      <c r="G195" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="n">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (una localidad)</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>¿Qué incluye cada aula?</t>
+          <t>Marginación: {d}</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>¿Tlen kipia nochi tlamachtiloyan?</t>
+          <t>Iknoyotl: {d}</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
@@ -6626,22 +6626,22 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (una localidad)</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Equipo de cómputo</t>
+          <t>Close popup</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>Tepostlapoualli</t>
+          <t>Xiktsagua</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (localidad sin datos censales)</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -6667,12 +6667,12 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>{n} computadoras con conexión a internet y software educativo.</t>
+          <t>Coordenada capturada manualmente</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>{n} tepostlapoualli iga internet uan programas iga temachtilistle.</t>
+          <t>Kanin katej, omojkuilo iga ma</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (localidad sin datos censales)</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Mobiliario</t>
+          <t>Sin Datos Censales Disponibles</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>Ikpalmej uan tlapechmej</t>
+          <t>Amo kipia itlapoual censo</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (localidad sin datos censales)</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -6729,12 +6729,12 @@
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>{n} sillas y {n} mesas para las aulas que no contaban con mobiliario suficiente.</t>
+          <t>No se encontró una coincidencia confiable para {d} en el Censo INEGI {n} (ITER Morelos). Esto ocurre principalmente con colonias/barrios urbanos que no se registran como localidad censal independiente. El mapa muestra su ubicación (coordenada capturada manualmente) dentro de polígono {n}.</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>{n} ikpalmej uan {n} tlapechmej iga tlamachtiloyan tlen amo kipiayaj.</t>
+          <t>Amo omonexti {d} ipan Censo INEGI {n} (ITER Morelos). Nin panoa ogachi iga colonias o barrios ipan ueyi altepetl tlen amo motlapouaj kemej altepetsin. Tlalamatl kinextia kanin katej (omojkuilo iga ma) ipan polígono {n}.</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (localidad sin datos censales)</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Conectividad</t>
+          <t>Población reportada (Lista TPBV {n})</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
         <is>
-          <t>Mosaloua iga internet</t>
+          <t>Tlatlaga tlen motlapoukej (Lista TPBV {n})</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (filtro personalizado)</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Una tarjeta WiFi por equipo e internet dedicado para el aula.</t>
+          <t>Elige los polígonos a comparar</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>Se tarjeta WiFi iga nochi tepostlapoualli uan internet san iga tlamachtiloyan.</t>
+          <t>Xikpepena polígono tlen tikinneneuilis</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (filtro personalizado)</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -6822,12 +6822,12 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Acompañamiento</t>
+          <t>Limpiar</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>Akin kinpaleuia</t>
+          <t>Xikpojpoa</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Un promotor capacitado en cada escuela para el uso del aula.</t>
+          <t>Territorios de Paz y Buen Vivir · Educación digital</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>Se tlapaleuiani tlen momachtij ipan nochi kaltlamachtiloyan iga ma motekiuti tlamachtiloyan.</t>
+          <t>Territorios de Paz y Buen Vivir · Temachtilistle iga tepostlapoualli</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>Acercar tecnología a las escuelas es abrir oportunidades reales para las niñas y los niños, especialmente en zonas donde el acceso ha sido limitado.</t>
+          <t>Para reducir la brecha digital desde edades tempranas, la Agencia de Transformación Digital del Estado de Morelos (ATDEM), en coordinación con la Secretaría de Educación y el Instituto de Educación Básica del Estado de Morelos (IEBEM), equipó aulas de cómputo en {n} escuelas de {n} municipios ubicadas en los polígonos de Territorios de Paz y Buen Vivir.</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
         <is>
-          <t>Tikitkiliskej tepostlapoualli ipan kaltlamachtiloyan kiijtosneki tiktlapoaj melauak ojmej iga pipiltontij, ogachi kanin amo asiaya.</t>
+          <t>Iga ma moyekchiua tlen amo kipiaj tepostlapoualli kuak tsitsikitsin, Agencia de Transformación Digital del Estado de Morelos (ATDEM), sepan iga Secretaría de Educación uan Instituto de Educación Básica del Estado de Morelos (IEBEM), kitlalij tepostlapoualli ipan {n} kaltlamachtiloyan ipan {n} altepemej tlen katej ipan polígono Territorios de Paz y Buen Vivir.</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>, director de Agenda Digital de la ATDEM, durante una entrega en Jojutla.</t>
+          <t>Con computadoras conectadas a internet y software educativo, niñas, niños y jóvenes fortalecen sus procesos de aprendizaje, desarrollan habilidades digitales y amplían sus oportunidades en entornos con mayor infraestructura tecnológica.</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>, tlayekanki ipan Agenda Digital ATDEM, kuak kitemakak ipan Jojutla.</t>
+          <t>Iga tepostlapoualli tlen kipiaj internet uan programas iga temachtilistle, pipiltontij uan telpogamej ogachi kualtsin momachtiaj, kimachtiaj tepostlapoualli uan ogachi ojmej kipiaj.</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
@@ -6946,20 +6946,16 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Escuelas por nivel educativo</t>
-        </is>
-      </c>
-      <c r="E207" s="5" t="inlineStr">
-        <is>
-          <t>Kaltlamachtiloyan iga temachtilistle</t>
-        </is>
-      </c>
-      <c r="F207" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G207" s="4" t="n"/>
+          <t>Secretaría de Educación</t>
+        </is>
+      </c>
+      <c r="E207" s="4" t="n"/>
+      <c r="F207" s="4" t="n"/>
+      <c r="G207" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="4" t="n">
@@ -6977,12 +6973,12 @@
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>¿Dónde están las aulas?</t>
+          <t>Instalación: diciembre {n} a enero {n}</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>¿Kanin katej tlamachtiloyan?</t>
+          <t>Motlalij: peuak diciembre {n}, tlamik enero {n}</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
@@ -7008,12 +7004,12 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>Todos los municipios</t>
+          <t>¿Qué incluye cada aula?</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
         <is>
-          <t>Nochi altepemej</t>
+          <t>¿Tlen kipia nochi tlamachtiloyan?</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
@@ -7039,12 +7035,12 @@
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>Escuelas equipadas</t>
+          <t>Equipo de cómputo</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan tlen kipiaj tepostlapoualli</t>
+          <t>Tepostlapoualli</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
@@ -7070,12 +7066,12 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>Computadoras</t>
+          <t>{n} computadoras con conexión a internet y software educativo.</t>
         </is>
       </c>
       <c r="E211" s="5" t="inlineStr">
         <is>
-          <t>Tepostlapoualmej</t>
+          <t>{n} tepostlapoualli iga internet uan programas iga temachtilistle.</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
@@ -7101,12 +7097,12 @@
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Escuelas dentro de un polígono</t>
+          <t>Mobiliario</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan ipan se polígono</t>
+          <t>Ikpalmej uan tlapechmej</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
@@ -7132,12 +7128,12 @@
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>Mapa de Aulas</t>
+          <t>{n} sillas y {n} mesas para las aulas que no contaban con mobiliario suficiente.</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
         <is>
-          <t>Tlalamatl iga tlamachtiloyan</t>
+          <t>{n} ikpalmej uan {n} tlapechmej iga tlamachtiloyan tlen amo kipiayaj.</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
@@ -7163,12 +7159,12 @@
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>El tamaño del círculo indica el número de computadoras. Haz clic en una escuela para ver su detalle.</t>
+          <t>Conectividad</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>Kenin ueyi yaualtik kinextia keski tepostlapoualli kipia. Xikpacho se kaltlamachtiloyan iga tikitas nochi.</t>
+          <t>Mosaloua iga internet</t>
         </is>
       </c>
       <c r="F214" s="4" t="inlineStr">
@@ -7194,12 +7190,12 @@
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Computadoras por aula</t>
+          <t>Una tarjeta WiFi por equipo e internet dedicado para el aula.</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>Tepostlapoualli ipan nochi tlamachtiloyan</t>
+          <t>Se tarjeta WiFi iga nochi tepostlapoualli uan internet san iga tlamachtiloyan.</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
@@ -7225,12 +7221,12 @@
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Municipio con aula</t>
+          <t>Acompañamiento</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>Altepetl iga tlamachtiloyan</t>
+          <t>Akin kinpaleuia</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
@@ -7256,12 +7252,12 @@
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>Otros municipios</t>
+          <t>Un promotor capacitado en cada escuela para el uso del aula.</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>Siguin altepemej</t>
+          <t>Se tlapaleuiani tlen momachtij ipan nochi kaltlamachtiloyan iga ma motekiuti tlamachtiloyan.</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
@@ -7287,12 +7283,12 @@
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Equipos por Municipio</t>
+          <t>Acercar tecnología a las escuelas es abrir oportunidades reales para las niñas y los niños, especialmente en zonas donde el acceso ha sido limitado.</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>Tepostlapoualli iga altepetl</t>
+          <t>Tikitkiliskej tepostlapoualli ipan kaltlamachtiloyan kiijtosneki tiktlapoaj melauak ojmej iga pipiltontij, ogachi kanin amo asiaya.</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
@@ -7318,12 +7314,12 @@
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>{n} eq. · {n} esc.</t>
+          <t>, director de Agenda Digital de la ATDEM, durante una entrega en Jojutla.</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
         <is>
-          <t>{n} tep. · {n} kal.</t>
+          <t>, tlayekanki ipan Agenda Digital ATDEM, kuak kitemakak ipan Jojutla.</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
@@ -7349,12 +7345,12 @@
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Escuelas</t>
+          <t>Escuelas por nivel educativo</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan</t>
+          <t>Kaltlamachtiloyan iga temachtilistle</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
@@ -7380,12 +7376,12 @@
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>Escuela</t>
+          <t>¿Dónde están las aulas?</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan</t>
+          <t>¿Kanin katej tlamachtiloyan?</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
@@ -7411,12 +7407,12 @@
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Equipos</t>
+          <t>Todos los municipios</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>Tepostlapoualmej</t>
+          <t>Nochi altepemej</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
@@ -7437,17 +7433,17 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>Ver {d} en el mapa</t>
+          <t>Escuelas equipadas</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>Xikita {d} ipan tlalamatl</t>
+          <t>Kaltlamachtiloyan tlen kipiaj tepostlapoualli</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
@@ -7473,12 +7469,12 @@
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, "Proyecto Escuelas entrega Computadoras" (hoja Concentrado). Ubicación según el enlace de Google Maps capturado por escuela.</t>
+          <t>Computadoras</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, "Proyecto Escuelas entrega Computadoras" (hoja Concentrado). Kanin katej iga ojtle Google Maps tlen motlalij iga nochi kaltlamachtiloyan.</t>
+          <t>Tepostlapoualmej</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
@@ -7494,7 +7490,7 @@
       </c>
       <c r="B225" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C225" s="4" t="inlineStr">
@@ -7504,12 +7500,12 @@
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>Conectividad pública · Agencia de Transformación Digital</t>
+          <t>Escuelas dentro de un polígono</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
         <is>
-          <t>Matlatl tlapojtok · Agencia de Transformación Digital</t>
+          <t>Kaltlamachtiloyan ipan se polígono</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
@@ -7525,7 +7521,7 @@
       </c>
       <c r="B226" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C226" s="4" t="inlineStr">
@@ -7535,12 +7531,12 @@
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Red de Wi-Fi pública, gratuita y abierta impulsada por la Agencia de Transformación Digital del Gobierno del Estado de Morelos (ATDEM). Busca reducir la brecha digital y que la ciudadanía pueda comunicarse sin costo, consultar la programación cultural, realizar trámites y acceder a las plataformas digitales institucionales.</t>
+          <t>Mapa de Aulas</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
         <is>
-          <t>Matlatl Wi-Fi tlen nochi ueli kitekiutiskej, amo iga tomin uan tlapojtok, tlen kichiua Agencia de Transformación Digital ipan Kaltlayekana ipan Morelos (ATDEM). Guinegui ma moyekchiua tlen amo kipiaj internet uan ma tlatlaga ueliskej monotsaskej amo iga tomin, kitaskej iljuimej, kichiuaskej trámites uan kalakiskej ipan plataformas digitales iga Kaltlayekana.</t>
+          <t>Tlalamatl iga tlamachtiloyan</t>
         </is>
       </c>
       <c r="F226" s="4" t="inlineStr">
@@ -7556,7 +7552,7 @@
       </c>
       <c r="B227" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C227" s="4" t="inlineStr">
@@ -7566,12 +7562,12 @@
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>Internet gratuito y abierto</t>
+          <t>El tamaño del círculo indica el número de computadoras. Haz clic en una escuela para ver su detalle.</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
         <is>
-          <t>Internet amo iga tomin uan tlapojtok</t>
+          <t>Kenin ueyi yaualtik kinextia keski tepostlapoualli kipia. Xikpacho se kaltlamachtiloyan iga tikitas nochi.</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
@@ -7587,7 +7583,7 @@
       </c>
       <c r="B228" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C228" s="4" t="inlineStr">
@@ -7597,12 +7593,12 @@
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>Conexión Wi-Fi sin costo para la ciudadanía en espacios públicos y oficinas de gobierno.</t>
+          <t>Computadoras por aula</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>Matlatl Wi-Fi amo iga tomin iga tlatlaga kanin nochi monechikouaj uan ipan teguichiualoyan iga Kaltlayekana.</t>
+          <t>Tepostlapoualli ipan nochi tlamachtiloyan</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
@@ -7618,7 +7614,7 @@
       </c>
       <c r="B229" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C229" s="4" t="inlineStr">
@@ -7628,12 +7624,12 @@
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Reducir la brecha digital</t>
+          <t>Municipio con aula</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
         <is>
-          <t>Moyekchiuas tlen amo kipiaj internet</t>
+          <t>Altepetl iga tlamachtiloyan</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
@@ -7649,7 +7645,7 @@
       </c>
       <c r="B230" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C230" s="4" t="inlineStr">
@@ -7659,12 +7655,12 @@
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Comunicarse sin costo, consultar programación cultural y realizar trámites en plataformas digitales institucionales.</t>
+          <t>Otros municipios</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>Monotsaskej amo iga tomin, kitaskej iljuimej uan kichiuaskej trámites ipan plataformas digitales iga Kaltlayekana.</t>
+          <t>Siguin altepemej</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
@@ -7680,7 +7676,7 @@
       </c>
       <c r="B231" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C231" s="4" t="inlineStr">
@@ -7690,12 +7686,12 @@
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>Puntos de conexión</t>
+          <t>Equipos por Municipio</t>
         </is>
       </c>
       <c r="E231" s="5" t="inlineStr">
         <is>
-          <t>Kanin mosaloua</t>
+          <t>Tepostlapoualli iga altepetl</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
@@ -7711,7 +7707,7 @@
       </c>
       <c r="B232" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C232" s="4" t="inlineStr">
@@ -7721,12 +7717,12 @@
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>Plazas públicas y espacios de alta concurrencia, como la Plaza de Armas Emiliano Zapata (Zócalo de Cuernavaca).</t>
+          <t>{n} eq. · {n} esc.</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>Plazas uan kanin miak tlatlaga monechikouaj, ken Plaza de Armas Emiliano Zapata (Zócalo de Cuernavaca).</t>
+          <t>{n} tep. · {n} kal.</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
@@ -7742,7 +7738,7 @@
       </c>
       <c r="B233" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C233" s="4" t="inlineStr">
@@ -7752,12 +7748,12 @@
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>Eventos especiales, como el Festival Internacional Cervantino en Cuernavaca.</t>
+          <t>Escuelas</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
         <is>
-          <t>Iljuimej, ken Festival Internacional Cervantino ipan Cuernavaca.</t>
+          <t>Kaltlamachtiloyan</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
@@ -7773,7 +7769,7 @@
       </c>
       <c r="B234" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C234" s="4" t="inlineStr">
@@ -7783,12 +7779,12 @@
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>Dependencias estatales, ayudantías municipales y escuelas.</t>
+          <t>Escuela</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>Teguichiualoyan iga Kaltlayekana, ayudantías ipan altepemej uan kaltlamachtiloyan.</t>
+          <t>Kaltlamachtiloyan</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
@@ -7804,7 +7800,7 @@
       </c>
       <c r="B235" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C235" s="4" t="inlineStr">
@@ -7814,12 +7810,12 @@
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>Dependencias con red</t>
+          <t>Equipos</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
         <is>
-          <t>Teguichiualoyan iga matlatl</t>
+          <t>Tepostlapoualmej</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
@@ -7835,22 +7831,22 @@
       </c>
       <c r="B236" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>Secretarías y órganos</t>
+          <t>Ver {d} en el mapa</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
-          <t>Secretarías uan teguichiualoyan</t>
+          <t>Xikita {d} ipan tlalamatl</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
@@ -7866,7 +7862,7 @@
       </c>
       <c r="B237" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C237" s="4" t="inlineStr">
@@ -7876,12 +7872,12 @@
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>Sedes conectadas</t>
+          <t>Fuente: ATDEM, "Proyecto Escuelas entrega Computadoras" (hoja Concentrado). Ubicación según el enlace de Google Maps capturado por escuela.</t>
         </is>
       </c>
       <c r="E237" s="5" t="inlineStr">
         <is>
-          <t>Kalmej tlen mosalojtokej</t>
+          <t>Kanin eua: ATDEM, "Proyecto Escuelas entrega Computadoras" (hoja Concentrado). Kanin katej iga ojtle Google Maps tlen motlalij iga nochi kaltlamachtiloyan.</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
@@ -7907,12 +7903,12 @@
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>Puntos de acceso</t>
+          <t>Conectividad pública · Agencia de Transformación Digital</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
-          <t>Kanin mosaloua</t>
+          <t>Matlatl tlapojtok · Agencia de Transformación Digital</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
@@ -7938,12 +7934,12 @@
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>Mapa de la red</t>
+          <t>Red de Wi-Fi pública, gratuita y abierta impulsada por la Agencia de Transformación Digital del Gobierno del Estado de Morelos (ATDEM). Busca reducir la brecha digital y que la ciudadanía pueda comunicarse sin costo, consultar la programación cultural, realizar trámites y acceder a las plataformas digitales institucionales.</t>
         </is>
       </c>
       <c r="E239" s="5" t="inlineStr">
         <is>
-          <t>Tlalamatl iga matlatl</t>
+          <t>Matlatl Wi-Fi tlen nochi ueli kitekiutiskej, amo iga tomin uan tlapojtok, tlen kichiua Agencia de Transformación Digital ipan Kaltlayekana ipan Morelos (ATDEM). Guinegui ma moyekchiua tlen amo kipiaj internet uan ma tlatlaga ueliskej monotsaskej amo iga tomin, kitaskej iljuimej, kichiuaskej trámites uan kalakiskej ipan plataformas digitales iga Kaltlayekana.</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
@@ -7969,12 +7965,12 @@
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>Sede con red (el tamaño indica cuántas dependencias)</t>
+          <t>Internet gratuito y abierto</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>Kalle iga matlatl (kenin ueyi kinextia keski teguichiualoyan)</t>
+          <t>Internet amo iga tomin uan tlapojtok</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
@@ -8000,12 +7996,12 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>Dependencias por secretaría</t>
+          <t>Conexión Wi-Fi sin costo para la ciudadanía en espacios públicos y oficinas de gobierno.</t>
         </is>
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
-          <t>Teguichiualoyan iga secretaría</t>
+          <t>Matlatl Wi-Fi amo iga tomin iga tlatlaga kanin nochi monechikouaj uan ipan teguichiualoyan iga Kaltlayekana.</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
@@ -8031,12 +8027,12 @@
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>{n} puntos de acceso</t>
+          <t>Reducir la brecha digital</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>{n} kanin mosaloua</t>
+          <t>Moyekchiuas tlen amo kipiaj internet</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
@@ -8062,16 +8058,20 @@
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>Jefatura de la Oficina de la Gubernatura</t>
-        </is>
-      </c>
-      <c r="E243" s="4" t="n"/>
-      <c r="F243" s="4" t="n"/>
-      <c r="G243" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Comunicarse sin costo, consultar programación cultural y realizar trámites en plataformas digitales institucionales.</t>
+        </is>
+      </c>
+      <c r="E243" s="5" t="inlineStr">
+        <is>
+          <t>Monotsaskej amo iga tomin, kitaskej iljuimej uan kichiuaskej trámites ipan plataformas digitales iga Kaltlayekana.</t>
+        </is>
+      </c>
+      <c r="F243" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G243" s="4" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="4" t="n">
@@ -8089,12 +8089,12 @@
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>{n} punto de acceso</t>
+          <t>Puntos de conexión</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
         <is>
-          <t>{n} kanin mosaloua</t>
+          <t>Kanin mosaloua</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, "Agentes_dependencias La Tierra Que Nos Une" (dependencias con red La tierra que nos une). Puntos de acceso según el registro de la ATDEM; algunas dependencias no tienen el dato capturado.</t>
+          <t>Plazas públicas y espacios de alta concurrencia, como la Plaza de Armas Emiliano Zapata (Zócalo de Cuernavaca).</t>
         </is>
       </c>
       <c r="E245" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, "Agentes_dependencias La Tierra Que Nos Une" (teguichiualoyan iga matlatl Nin tlale tech sepaneloa). Kanin mosaloua ken kijkuiloj ATDEM; siguin teguichiualoyan amo kipiaj nin tlapoualli.</t>
+          <t>Plazas uan kanin miak tlatlaga monechikouaj, ken Plaza de Armas Emiliano Zapata (Zócalo de Cuernavaca).</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>Conectividad · Agencia de Transformación Digital</t>
+          <t>Eventos especiales, como el Festival Internacional Cervantino en Cuernavaca.</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>Mosaloua · Agencia de Transformación Digital</t>
+          <t>Iljuimej, ken Festival Internacional Cervantino ipan Cuernavaca.</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
@@ -8182,12 +8182,12 @@
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>Sitios y torres de telecomunicaciones de la red estatal (sitios REEM) que dan servicio a dependencias del Gobierno del Estado, planteles educativos, unidades de salud e instalaciones de seguridad en Morelos.</t>
+          <t>Dependencias estatales, ayudantías municipales y escuelas.</t>
         </is>
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>Sitios uan tepostlaketsalmej iga uejka tlanonotsalistle ipan imatlau Kaltlayekana (sitios REEM) tlen kinpaleuiaj teguichiualoyan iga Kaltlayekana, kaltlamachtiloyan, pajtiloyan uan kanin tlajpiaj ipan Morelos.</t>
+          <t>Teguichiualoyan iga Kaltlayekana, ayudantías ipan altepemej uan kaltlamachtiloyan.</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>Por seguridad de la infraestructura, la información se presenta agregada por municipio y sector. No se publica la ubicación exacta ni el nombre de los sitios.</t>
+          <t>Dependencias con red</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>Iga tlajpialistle, tlamachilistle monextia sepan iga altepetl uan teguitl. Amo monextia kanin melauak katej nin intogayo sitios.</t>
+          <t>Teguichiualoyan iga matlatl</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>Sitios de telecomunicaciones</t>
+          <t>Secretarías y órganos</t>
         </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
-          <t>Sitios iga uejka tlanonotsalistle</t>
+          <t>Secretarías uan teguichiualoyan</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>Municipios con sitios</t>
+          <t>Sedes conectadas</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>Altepemej iga sitios</t>
+          <t>Kalmej tlen mosalojtokej</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>Sectores atendidos</t>
+          <t>Puntos de acceso</t>
         </is>
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>Teguimej tlen kinpaleuiaj</t>
+          <t>Kanin mosaloua</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>Mayor concentración ({n} sitios)</t>
+          <t>Mapa de la red</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>Kanin ogachi miak ({n} sitios)</t>
+          <t>Tlalamatl iga matlatl</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>Sitios por municipio</t>
+          <t>Sede con red (el tamaño indica cuántas dependencias)</t>
         </is>
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
-          <t>Sitios iga altepetl</t>
+          <t>Kalle iga matlatl (kenin ueyi kinextia keski teguichiualoyan)</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>Pasa el cursor sobre un municipio para ver el desglose por sector.</t>
+          <t>Dependencias por secretaría</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>Xikpano tepostlapacholi ipan se altepetl iga tikitas tlen kipia iga teguitl.</t>
+          <t>Teguichiualoyan iga secretaría</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>{n} o más</t>
+          <t>{n} puntos de acceso</t>
         </is>
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
-          <t>{n} o ogachi</t>
+          <t>{n} kanin mosaloua</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
@@ -8461,20 +8461,16 @@
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>Sin sitios</t>
-        </is>
-      </c>
-      <c r="E256" s="5" t="inlineStr">
-        <is>
-          <t>Amo kipia sitios</t>
-        </is>
-      </c>
-      <c r="F256" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G256" s="4" t="n"/>
+          <t>Jefatura de la Oficina de la Gubernatura</t>
+        </is>
+      </c>
+      <c r="E256" s="4" t="n"/>
+      <c r="F256" s="4" t="n"/>
+      <c r="G256" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="4" t="n">
@@ -8482,7 +8478,7 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
@@ -8492,12 +8488,12 @@
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>Sitios por sector</t>
+          <t>{n} punto de acceso</t>
         </is>
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
-          <t>Sitios iga teguitl</t>
+          <t>{n} kanin mosaloua</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
@@ -8513,7 +8509,7 @@
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
@@ -8523,12 +8519,12 @@
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>Gobierno del Estado</t>
+          <t>Fuente: ATDEM, "Agentes_dependencias La Tierra Que Nos Une" (dependencias con red La tierra que nos une). Puntos de acceso según el registro de la ATDEM; algunas dependencias no tienen el dato capturado.</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>Kaltlayekana</t>
+          <t>Kanin eua: ATDEM, "Agentes_dependencias La Tierra Que Nos Une" (teguichiualoyan iga matlatl Nin tlale tech sepaneloa). Kanin mosaloua ken kijkuiloj ATDEM; siguin teguichiualoyan amo kipiaj nin tlapoualli.</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
@@ -8554,12 +8550,12 @@
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Conectividad · Agencia de Transformación Digital</t>
         </is>
       </c>
       <c r="E259" s="5" t="inlineStr">
         <is>
-          <t>Pajtilistle</t>
+          <t>Mosaloua · Agencia de Transformación Digital</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
@@ -8585,12 +8581,12 @@
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>Seguridad y Protección Ciudadana</t>
+          <t>Sitios y torres de telecomunicaciones de la red estatal (sitios REEM) que dan servicio a dependencias del Gobierno del Estado, planteles educativos, unidades de salud e instalaciones de seguridad en Morelos.</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>Tlajpialistle uan Tlapaleuilistle iga Tlatlaga</t>
+          <t>Sitios uan tepostlaketsalmej iga uejka tlanonotsalistle ipan imatlau Kaltlayekana (sitios REEM) tlen kinpaleuiaj teguichiualoyan iga Kaltlayekana, kaltlamachtiloyan, pajtiloyan uan kanin tlajpiaj ipan Morelos.</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
@@ -8616,12 +8612,12 @@
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>Municipios con infraestructura</t>
+          <t>Por seguridad de la infraestructura, la información se presenta agregada por municipio y sector. No se publica la ubicación exacta ni el nombre de los sitios.</t>
         </is>
       </c>
       <c r="E261" s="5" t="inlineStr">
         <is>
-          <t>Altepemej iga tepostlaketsalmej</t>
+          <t>Iga tlajpialistle, tlamachilistle monextia sepan iga altepetl uan teguitl. Amo monextia kanin melauak katej nin intogayo sitios.</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
@@ -8647,12 +8643,12 @@
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>Sectores</t>
+          <t>Sitios de telecomunicaciones</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>Teguimej</t>
+          <t>Sitios iga uejka tlanonotsalistle</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
@@ -8678,12 +8674,12 @@
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>Sitios</t>
+          <t>Municipios con sitios</t>
         </is>
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
-          <t>Sitios</t>
+          <t>Altepemej iga sitios</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
@@ -8709,12 +8705,12 @@
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>Gobierno del Estado · {n}</t>
+          <t>Sectores atendidos</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>Kaltlayekana · {n}</t>
+          <t>Teguimej tlen kinpaleuiaj</t>
         </is>
       </c>
       <c r="F264" s="4" t="inlineStr">
@@ -8740,12 +8736,12 @@
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>Salud · {n}</t>
+          <t>Mayor concentración ({n} sitios)</t>
         </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
-          <t>Pajtilistle · {n}</t>
+          <t>Kanin ogachi miak ({n} sitios)</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
@@ -8771,12 +8767,12 @@
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>Educación · {n}</t>
+          <t>Sitios por municipio</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>Temachtilistle · {n}</t>
+          <t>Sitios iga altepetl</t>
         </is>
       </c>
       <c r="F266" s="4" t="inlineStr">
@@ -8802,12 +8798,12 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>Seguridad y Protección Ciudadana · {n}</t>
+          <t>Pasa el cursor sobre un municipio para ver el desglose por sector.</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
         <is>
-          <t>Tlajpialistle uan Tlapaleuilistle iga Tlatlaga · {n}</t>
+          <t>Xikpano tepostlapacholi ipan se altepetl iga tikitas tlen kipia iga teguitl.</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
@@ -8833,12 +8829,12 @@
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, registro de sitios REEM. Municipio asignado con los límites municipales del INE.</t>
+          <t>{n} o más</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, sitios REEM. Altepetl motlalij iga itlalxelol altepemej tlen INE.</t>
+          <t>{n} o ogachi</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
@@ -8854,7 +8850,7 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
@@ -8864,12 +8860,12 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>Territorios de Paz y Buen Vivir · Transparencia</t>
+          <t>Sin sitios</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>Territorios de Paz y Buen Vivir · Tlen nochi ueli kitaskej</t>
+          <t>Amo kipia sitios</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
@@ -8885,7 +8881,7 @@
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
@@ -8895,12 +8891,12 @@
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>Descarga las bases de datos que alimentan este tablero. Cada conjunto está disponible en CSV, para abrirlo en Excel o cualquier herramienta de análisis, y en KML, para verlo en Google Earth o Google My Maps.</t>
+          <t>Sitios por sector</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga tlapoualli tlen kitekiutia nin tablero. Nochi kipia CSV, iga tiktlapos ipan Excel o siguin programa, uan KML, iga tikitas ipan Google Earth o Google My Maps.</t>
+          <t>Sitios iga teguitl</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
@@ -8916,7 +8912,7 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
@@ -8926,12 +8922,12 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>{n} conjuntos de datos</t>
+          <t>Gobierno del Estado</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>{n} tlapoualamatl</t>
+          <t>Kaltlayekana</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
@@ -8947,7 +8943,7 @@
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
@@ -8957,12 +8953,12 @@
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>CSV · UTF-{n}, separado por comas</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>CSV · UTF-{n}, xeloltok iga comas</t>
+          <t>Pajtilistle</t>
         </is>
       </c>
       <c r="F272" s="4" t="inlineStr">
@@ -8978,7 +8974,7 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
@@ -8988,12 +8984,12 @@
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>KML · una sola capa</t>
+          <t>Seguridad y Protección Ciudadana</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
-          <t>KML · san se tlapachtli</t>
+          <t>Tlajpialistle uan Tlapaleuilistle iga Tlatlaga</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
@@ -9009,7 +9005,7 @@
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
@@ -9019,12 +9015,12 @@
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>Localidades · Propuesta Actual</t>
+          <t>Municipios con infraestructura</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin · Tlen axan</t>
+          <t>Altepemej iga tepostlaketsalmej</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
@@ -9040,7 +9036,7 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
@@ -9050,12 +9046,12 @@
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>{n} registros · {n} campos</t>
+          <t>Sectores</t>
         </is>
       </c>
       <c r="E275" s="5" t="inlineStr">
         <is>
-          <t>{n} tlajkuilolli · {n} tlamachilistle</t>
+          <t>Teguimej</t>
         </is>
       </c>
       <c r="F275" s="4" t="inlineStr">
@@ -9071,7 +9067,7 @@
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
@@ -9081,12 +9077,12 @@
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>Las localidades de los {n} polígonos vigentes con sus indicadores de población, vivienda, salud, educación, economía y marginación.</t>
+          <t>Sitios</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin tlen {n} polígono tlen axan iga itlapoual tlatlaga, kalmej, pajtilistle, temachtilistle, tomin uan iknoyotl.</t>
+          <t>Sitios</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr">
@@ -9102,7 +9098,7 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
@@ -9112,12 +9108,12 @@
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>Fuente: INEGI, Censo {n} (ITER Morelos) y Lista de Comunidades TPBV {n}</t>
+          <t>Gobierno del Estado · {n}</t>
         </is>
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: INEGI, Censo {n} (ITER Morelos) uan Lista de Comunidades TPBV {n}</t>
+          <t>Kaltlayekana · {n}</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
@@ -9133,7 +9129,7 @@
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
@@ -9143,12 +9139,12 @@
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>Ver campos</t>
+          <t>Salud · {n}</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>Xikita tlen kipia</t>
+          <t>Pajtilistle · {n}</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
@@ -9164,22 +9160,22 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>Descargar Localidades · Propuesta Actual en CSV</t>
+          <t>Educación · {n}</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Altepetsitsin · Tlen axan ipan CSV</t>
+          <t>Temachtilistle · {n}</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
@@ -9195,22 +9191,22 @@
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>Descargar Localidades · Propuesta Actual en KML</t>
+          <t>Seguridad y Protección Ciudadana · {n}</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Altepetsitsin · Tlen axan ipan KML</t>
+          <t>Tlajpialistle uan Tlapaleuilistle iga Tlatlaga · {n}</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
@@ -9226,7 +9222,7 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
@@ -9236,12 +9232,12 @@
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>Polígonos · Propuesta Actual</t>
+          <t>Fuente: ATDEM, registro de sitios REEM. Municipio asignado con los límites municipales del INE.</t>
         </is>
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
-          <t>Polígono · Tlen axan</t>
+          <t>Kanin eua: ATDEM, sitios REEM. Altepetl motlalij iga itlalxelol altepemej tlen INE.</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
@@ -9267,12 +9263,12 @@
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>Contorno de los {n} polígonos vigentes de Territorios de Paz y Buen Vivir, con número de localidades y población.</t>
+          <t>Territorios de Paz y Buen Vivir · Transparencia</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>Itlalxelol {n} polígono tlen axan ipan Territorios de Paz y Buen Vivir, iga keski altepetsitsin uan tlatlaga.</t>
+          <t>Territorios de Paz y Buen Vivir · Tlen nochi ueli kitaskej</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
@@ -9298,12 +9294,12 @@
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>Fuente: TPBV {n}.geojson</t>
+          <t>Descarga las bases de datos que alimentan este tablero. Cada conjunto está disponible en CSV, para abrirlo en Excel o cualquier herramienta de análisis, y en KML, para verlo en Google Earth o Google My Maps.</t>
         </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: TPBV {n}.geojson</t>
+          <t>Xikuiga tlapoualli tlen kitekiutia nin tablero. Nochi kipia CSV, iga tiktlapos ipan Excel o siguin programa, uan KML, iga tikitas ipan Google Earth o Google My Maps.</t>
         </is>
       </c>
       <c r="F283" s="4" t="inlineStr">
@@ -9324,17 +9320,17 @@
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Descargar Polígonos · Propuesta Actual en CSV</t>
+          <t>{n} conjuntos de datos</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Polígono · Tlen axan ipan CSV</t>
+          <t>{n} tlapoualamatl</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
@@ -9355,17 +9351,17 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>Descargar Polígonos · Propuesta Actual en KML</t>
+          <t>CSV · UTF-{n}, separado por comas</t>
         </is>
       </c>
       <c r="E285" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Polígono · Tlen axan ipan KML</t>
+          <t>CSV · UTF-{n}, xeloltok iga comas</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
@@ -9391,12 +9387,12 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>Escuelas donde ATDEM instaló aulas de cómputo: CCT, nivel, computadoras, fecha de instalación y polígono TPBV.</t>
+          <t>KML · una sola capa</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan kanin ATDEM kitlalij tepostlapoualli: CCT, temachtilistle, tepostlapoualmej, kemanian motlalij uan polígono TPBV.</t>
+          <t>KML · san se tlapachtli</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
@@ -9422,12 +9418,12 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, Proyecto Escuelas entrega Computadoras</t>
+          <t>Localidades · Propuesta Actual</t>
         </is>
       </c>
       <c r="E287" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, Proyecto Escuelas entrega Computadoras</t>
+          <t>Altepetsitsin · Tlen axan</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
@@ -9448,17 +9444,17 @@
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>Descargar Aulas Tecnológicas en CSV</t>
+          <t>{n} registros · {n} campos</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Tlamachtiloyan iga tepostlapoualli ipan CSV</t>
+          <t>{n} tlajkuilolli · {n} tlamachilistle</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
@@ -9479,17 +9475,17 @@
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>Descargar Aulas Tecnológicas en KML</t>
+          <t>Las localidades de los {n} polígonos vigentes con sus indicadores de población, vivienda, salud, educación, economía y marginación.</t>
         </is>
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Tlamachtiloyan iga tepostlapoualli ipan KML</t>
+          <t>Altepetsitsin tlen {n} polígono tlen axan iga itlapoual tlatlaga, kalmej, pajtilistle, temachtilistle, tomin uan iknoyotl.</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
@@ -9515,12 +9511,12 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>Dependencias estatales con la red Wi-Fi pública de la ATDEM: secretaría, sede, coordenadas y puntos de acceso.</t>
+          <t>Fuente: INEGI, Censo {n} (ITER Morelos) y Lista de Comunidades TPBV {n}</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>Teguichiualoyan iga Kaltlayekana tlen kipiaj matlatl Wi-Fi tlen ATDEM: secretaría, kalle, kanin katej uan kanin mosaloua.</t>
+          <t>Kanin eua: INEGI, Censo {n} (ITER Morelos) uan Lista de Comunidades TPBV {n}</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
@@ -9546,12 +9542,12 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, Agentes_dependencias La Tierra Que Nos Une</t>
+          <t>Ver campos</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, Agentes_dependencias La Tierra Que Nos Une</t>
+          <t>Xikita tlen kipia</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
@@ -9577,12 +9573,12 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>Descargar Red La tierra que nos une en CSV</t>
+          <t>Descargar Localidades · Propuesta Actual en CSV</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Matlatl Nin tlale tech sepaneloa ipan CSV</t>
+          <t>Xikuiga Altepetsitsin · Tlen axan ipan CSV</t>
         </is>
       </c>
       <c r="F292" s="4" t="inlineStr">
@@ -9608,12 +9604,12 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>Descargar Red La tierra que nos une en KML</t>
+          <t>Descargar Localidades · Propuesta Actual en KML</t>
         </is>
       </c>
       <c r="E293" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Matlatl Nin tlale tech sepaneloa ipan KML</t>
+          <t>Xikuiga Altepetsitsin · Tlen axan ipan KML</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
@@ -9639,12 +9635,12 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>Límites municipales de Morelos</t>
+          <t>Polígonos · Propuesta Actual</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>Itlalxelol altepemej ipan Morelos</t>
+          <t>Polígono · Tlen axan</t>
         </is>
       </c>
       <c r="F294" s="4" t="inlineStr">
@@ -9670,12 +9666,12 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>Contorno de los {n} municipios del estado, con clave geoestadística (CVEGEO) y nombre.</t>
+          <t>Contorno de los {n} polígonos vigentes de Territorios de Paz y Buen Vivir, con número de localidades y población.</t>
         </is>
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>Itlalxelol {n} altepemej, iga iclave geoestadística (CVEGEO) uan itoga.</t>
+          <t>Itlalxelol {n} polígono tlen axan ipan Territorios de Paz y Buen Vivir, iga keski altepetsitsin uan tlatlaga.</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
@@ -9701,12 +9697,12 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>Fuente: INE, límites municipales</t>
+          <t>Fuente: TPBV {n}.geojson</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: INE, itlalxelol altepemej</t>
+          <t>Kanin eua: TPBV {n}.geojson</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
@@ -9732,12 +9728,12 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>Descargar Límites municipales de Morelos en CSV</t>
+          <t>Descargar Polígonos · Propuesta Actual en CSV</t>
         </is>
       </c>
       <c r="E297" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Itlalxelol altepemej ipan Morelos ipan CSV</t>
+          <t>Xikuiga Polígono · Tlen axan ipan CSV</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
@@ -9763,12 +9759,12 @@
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>Descargar Límites municipales de Morelos en KML</t>
+          <t>Descargar Polígonos · Propuesta Actual en KML</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Itlalxelol altepemej ipan Morelos ipan KML</t>
+          <t>Xikuiga Polígono · Tlen axan ipan KML</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
@@ -9794,12 +9790,12 @@
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>Los archivos se generan en tu navegador con la misma información que muestra el tablero. Para Google My Maps importa el KML en una capa nueva y usa "Aplicar estilo por columna de datos" para colorear por municipio, polígono u otro campo.</t>
+          <t>Escuelas donde ATDEM instaló aulas de cómputo: CCT, nivel, computadoras, fecha de instalación y polígono TPBV.</t>
         </is>
       </c>
       <c r="E299" s="5" t="inlineStr">
         <is>
-          <t>Nin amatl mochiua ipan motepostlapoual iga nochi tlamachilistle tlen kinextia nin tablero. Iga Google My Maps, xikalaki KML ipan se yankuik tlapachtli uan xiktekiuti "Aplicar estilo por columna de datos" iga tiktlapaluis iga altepetl, polígono o siguin.</t>
+          <t>Kaltlamachtiloyan kanin ATDEM kitlalij tepostlapoualli: CCT, temachtilistle, tepostlapoualmej, kemanian motlalij uan polígono TPBV.</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
@@ -9815,33 +9811,529 @@
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D300" s="4" t="inlineStr">
+        <is>
+          <t>Fuente: ATDEM, Proyecto Escuelas entrega Computadoras</t>
+        </is>
+      </c>
+      <c r="E300" s="5" t="inlineStr">
+        <is>
+          <t>Kanin eua: ATDEM, Proyecto Escuelas entrega Computadoras</t>
+        </is>
+      </c>
+      <c r="F300" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G300" s="4" t="n"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C301" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D301" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Aulas Tecnológicas en CSV</t>
+        </is>
+      </c>
+      <c r="E301" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Tlamachtiloyan iga tepostlapoualli ipan CSV</t>
+        </is>
+      </c>
+      <c r="F301" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G301" s="4" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="4" t="n">
+        <v>301</v>
+      </c>
+      <c r="B302" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D302" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Aulas Tecnológicas en KML</t>
+        </is>
+      </c>
+      <c r="E302" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Tlamachtiloyan iga tepostlapoualli ipan KML</t>
+        </is>
+      </c>
+      <c r="F302" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G302" s="4" t="n"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="n">
+        <v>302</v>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D303" s="4" t="inlineStr">
+        <is>
+          <t>Dependencias estatales con la red Wi-Fi pública de la ATDEM: secretaría, sede, coordenadas y puntos de acceso.</t>
+        </is>
+      </c>
+      <c r="E303" s="5" t="inlineStr">
+        <is>
+          <t>Teguichiualoyan iga Kaltlayekana tlen kipiaj matlatl Wi-Fi tlen ATDEM: secretaría, kalle, kanin katej uan kanin mosaloua.</t>
+        </is>
+      </c>
+      <c r="F303" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G303" s="4" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D304" s="4" t="inlineStr">
+        <is>
+          <t>Fuente: ATDEM, Agentes_dependencias La Tierra Que Nos Une</t>
+        </is>
+      </c>
+      <c r="E304" s="5" t="inlineStr">
+        <is>
+          <t>Kanin eua: ATDEM, Agentes_dependencias La Tierra Que Nos Une</t>
+        </is>
+      </c>
+      <c r="F304" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G304" s="4" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="4" t="n">
+        <v>304</v>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C305" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D305" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Red La tierra que nos une en CSV</t>
+        </is>
+      </c>
+      <c r="E305" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Matlatl Nin tlale tech sepaneloa ipan CSV</t>
+        </is>
+      </c>
+      <c r="F305" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G305" s="4" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="4" t="n">
+        <v>305</v>
+      </c>
+      <c r="B306" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C306" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D306" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Red La tierra que nos une en KML</t>
+        </is>
+      </c>
+      <c r="E306" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Matlatl Nin tlale tech sepaneloa ipan KML</t>
+        </is>
+      </c>
+      <c r="F306" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G306" s="4" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="4" t="n">
+        <v>306</v>
+      </c>
+      <c r="B307" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C307" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D307" s="4" t="inlineStr">
+        <is>
+          <t>Límites municipales de Morelos</t>
+        </is>
+      </c>
+      <c r="E307" s="5" t="inlineStr">
+        <is>
+          <t>Itlalxelol altepemej ipan Morelos</t>
+        </is>
+      </c>
+      <c r="F307" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G307" s="4" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="4" t="n">
+        <v>307</v>
+      </c>
+      <c r="B308" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C308" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D308" s="4" t="inlineStr">
+        <is>
+          <t>Contorno de los {n} municipios del estado, con clave geoestadística (CVEGEO) y nombre.</t>
+        </is>
+      </c>
+      <c r="E308" s="5" t="inlineStr">
+        <is>
+          <t>Itlalxelol {n} altepemej, iga iclave geoestadística (CVEGEO) uan itoga.</t>
+        </is>
+      </c>
+      <c r="F308" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G308" s="4" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="4" t="n">
+        <v>308</v>
+      </c>
+      <c r="B309" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C309" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D309" s="4" t="inlineStr">
+        <is>
+          <t>Fuente: INE, límites municipales</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="inlineStr">
+        <is>
+          <t>Kanin eua: INE, itlalxelol altepemej</t>
+        </is>
+      </c>
+      <c r="F309" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G309" s="4" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="4" t="n">
+        <v>309</v>
+      </c>
+      <c r="B310" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C310" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D310" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Límites municipales de Morelos en CSV</t>
+        </is>
+      </c>
+      <c r="E310" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Itlalxelol altepemej ipan Morelos ipan CSV</t>
+        </is>
+      </c>
+      <c r="F310" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G310" s="4" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="4" t="n">
+        <v>310</v>
+      </c>
+      <c r="B311" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C311" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D311" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Límites municipales de Morelos en KML</t>
+        </is>
+      </c>
+      <c r="E311" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Itlalxelol altepemej ipan Morelos ipan KML</t>
+        </is>
+      </c>
+      <c r="F311" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G311" s="4" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="4" t="n">
+        <v>311</v>
+      </c>
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D312" s="4" t="inlineStr">
+        <is>
+          <t>Los archivos se generan en tu navegador con la misma información que muestra el tablero. Para Google My Maps importa el KML en una capa nueva y usa "Aplicar estilo por columna de datos" para colorear por municipio, polígono u otro campo.</t>
+        </is>
+      </c>
+      <c r="E312" s="5" t="inlineStr">
+        <is>
+          <t>Nin amatl mochiua ipan motepostlapoual iga nochi tlamachilistle tlen kinextia nin tablero. Iga Google My Maps, xikalaki KML ipan se yankuik tlapachtli uan xiktekiuti "Aplicar estilo por columna de datos" iga tiktlapaluis iga altepetl, polígono o siguin.</t>
+        </is>
+      </c>
+      <c r="F312" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G312" s="4" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="4" t="n">
+        <v>312</v>
+      </c>
+      <c r="B313" s="4" t="inlineStr">
+        <is>
+          <t>Inicio (buscador de comunidades)</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D313" s="4" t="inlineStr">
+        <is>
+          <t>No encontramos «{d}» entre las {n} comunidades del programa. Revisa cómo está escrito o busca por municipio.</t>
+        </is>
+      </c>
+      <c r="E313" s="5" t="inlineStr">
+        <is>
+          <t>Amo otikajsike «{d}» ipan {n} altepetsitsin tlen nin tlapaleuilistle. Xiktlachili kenin otiktlajkuilo o xiktemo iga altepetl.</t>
+        </is>
+      </c>
+      <c r="F313" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G313" s="4" t="n"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="4" t="n">
+        <v>313</v>
+      </c>
+      <c r="B314" s="4" t="inlineStr">
+        <is>
+          <t>Inicio (buscador de comunidades)</t>
+        </is>
+      </c>
+      <c r="C314" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D314" s="4" t="inlineStr">
+        <is>
+          <t>{d} tiene {n} comunidad en el programa.</t>
+        </is>
+      </c>
+      <c r="E314" s="5" t="inlineStr">
+        <is>
+          <t>{d} kipia {n} altepetsin ipan nin tlapaleuilistle.</t>
+        </is>
+      </c>
+      <c r="F314" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G314" s="4" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="4" t="n">
+        <v>314</v>
+      </c>
+      <c r="B315" s="4" t="inlineStr">
+        <is>
+          <t>Inicio (buscador de comunidades)</t>
+        </is>
+      </c>
+      <c r="C315" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D315" s="4" t="inlineStr">
+        <is>
+          <t>Y {n} comunidad más. Escribe más letras para afinar la búsqueda.</t>
+        </is>
+      </c>
+      <c r="E315" s="5" t="inlineStr">
+        <is>
+          <t>Uan ogachi {n} altepetsin. Xiktlajkuilo ogachi tlajkuilolli iga tiktemos kuale.</t>
+        </is>
+      </c>
+      <c r="F315" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G315" s="4" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="4" t="n">
+        <v>315</v>
+      </c>
+      <c r="B316" s="4" t="inlineStr">
+        <is>
           <t>Encabezado y menú</t>
         </is>
       </c>
-      <c r="C300" s="4" t="inlineStr">
+      <c r="C316" s="4" t="inlineStr">
         <is>
           <t>atributo</t>
         </is>
       </c>
-      <c r="D300" s="4" t="inlineStr">
-        <is>
-          <t>TPBV {n} · Tablero Sociodemográfico</t>
-        </is>
-      </c>
-      <c r="E300" s="5" t="inlineStr">
-        <is>
-          <t>TPBV {n} · Tlapoualli iga tlatlaga</t>
-        </is>
-      </c>
-      <c r="F300" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G300" s="4" t="n"/>
+      <c r="D316" s="4" t="inlineStr">
+        <is>
+          <t>Territorios de Paz y Buen Vivir · Gobierno de Morelos</t>
+        </is>
+      </c>
+      <c r="E316" s="5" t="inlineStr">
+        <is>
+          <t>Territorios de Paz y Buen Vivir · Kaltlayekana ipan Morelos</t>
+        </is>
+      </c>
+      <c r="F316" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G316" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G300"/>
+  <autoFilter ref="A1:G316"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/traducciones/Traduccion_nahuatl_tablero.xlsx
+++ b/traducciones/Traduccion_nahuatl_tablero.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glosario" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$G$316</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$G$335</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G316"/>
+  <dimension ref="A1:G335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2355,12 +2355,12 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>¿Cómo funciona?</t>
+          <t>{n} de octubre de {n} · Xochitepec</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>¿Kenin teguiti?</t>
+          <t>{n} octubre, {n} xiuitl · Xochitepec</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Diagnóstico territorial</t>
+          <t>Segundo Encuentro Estatal de Consejos Comunitarios</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>Tlatemolistle ipan tlale</t>
+          <t>Ika ome nechikolistle ipan Morelos tlen Consejos Comunitarios</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -2417,12 +2417,12 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Las comunidades se identifican mediante un diagnóstico realizado por la Jefatura de la Oficina de la Gubernatura, que define los polígonos de atención.</t>
+          <t>Más de mil representantes de las comunidades se reunieron con la gobernadora Margarita González Saravia para fortalecer la organización comunitaria, que coloca a las comunidades en el centro de las decisiones.</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin moixmatij iga se tlatemolistle tlen kichiua Jefatura de la Oficina de la Gubernatura, uan yejua kitlalia polígono kanin motekipanos.</t>
+          <t>Ogachi miak ke se mil tlatlaga tlen kinixpantiaj altepetsitsin mosentlalijke iga Soatlayekanki Margarita González Saravia iga kichikauaskej kenin mosentlaliaj altepetsitsin, uan iga ma altepetsitsin kitlalikaj tlen mochiuas.</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Promotores comunitarios</t>
+          <t>comunidades (eran {n} al inicio)</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Tlapaleuianij ipan altepetsitsin</t>
+          <t>altepetsitsin (achtopa katka {n})</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Promotores capacitados visitan a la población para escuchar y conocer a detalle sus necesidades básicas.</t>
+          <t>millones de pesos de inversión interinstitucional</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>Tlapaleuianij tlen momachtijkej kinpaxalouaj tlatlaga iga kinkaguiskej uan kualtsin kiixmatiskej tlen kinmonekij.</t>
+          <t>millones tomin tlen kitlalijke sepan teguichiualoyan</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Acción coordinada</t>
+          <t>representantes comunitarios</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Teguitl tlen sepan mochiua</t>
+          <t>tlatlaga tlen kinixpantiaj altepetsitsin</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -2541,12 +2541,12 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Cada secretaría y organismo del Poder Ejecutivo lleva a cabo acciones coordinadas para fortalecer proyectos de mejora en las localidades.</t>
+          <t>Leer la nota completa</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Nochi secretaría uan teguichiualoyan iga Kaltlayekana sepan teguitij iga kichikauaskej tlachiualmej tlen kikualtlaliaj altepetsitsin.</t>
+          <t>Xikamapoua nochi tlanonotsalli</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -2567,17 +2567,17 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Equidad y dignidad</t>
+          <t>Fotos del Segundo Encuentro Estatal</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Sepan tiuejueyij uan tlakaitalistle</t>
+          <t>Ixkopinkayotlmej tlen ika ome nechikolistle</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -2598,17 +2598,17 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>El objetivo es construir una sociedad más equitativa y justa, donde todas las personas puedan vivir con dignidad.</t>
+          <t>{n} de {n}</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>Tlen tiknegui: tikchiuaskej se altepetl kanin nochi sepan katej uan melauak, kanin nochi tlatlaga ueliskej nemiskej iga tlakaitalistle.</t>
+          <t>{n} ipan {n}</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -2629,17 +2629,17 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>El programa en cifras</t>
+          <t>Segundo Encuentro Estatal de Consejos Comunitarios en el Centro de Convenciones Morelos, Xochitepec.</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Nin tlapaleuilistle iga tlapoualli</t>
+          <t>Ika ome nechikolistle ipan Morelos tlen Consejos Comunitarios ipan Centro de Convenciones Morelos, Xochitepec.</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -2660,17 +2660,17 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Localidades</t>
+          <t>Mesa principal del encuentro, con más de mil representantes comunitarios.</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin</t>
+          <t>Achtopa tlapechtle ipan nechikolistle, iga ogachi miak ke se mil tlatlaga tlen kinixpantiaj altepetsitsin.</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Polígonos</t>
+          <t>Representantes de las comunidades durante el encuentro.</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Tlatlaga tlen kinixpantiaj altepetsitsin ipan nechikolistle.</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -2722,17 +2722,17 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Municipios</t>
+          <t>Consejeras y consejeros comunitarios de Territorios de Paz y Buen Vivir.</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Altepemej</t>
+          <t>Consejeras uan consejeros tlen altepetsitsin ipan Territorios de Paz y Buen Vivir.</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -2753,17 +2753,17 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Habitantes</t>
+          <t>Participantes del encuentro.</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Tlatlaga</t>
+          <t>Tlatlaga tlen ouajlaj ipan nechikolistle.</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Escuelas con aula</t>
+          <t>Las comunidades en el centro de las decisiones.</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan iga tepostlapoualli</t>
+          <t>Altepetsitsin ipan iyolo nochi tlen mochiua.</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -2815,17 +2815,17 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Hitos</t>
+          <t>Promotoras y promotores que acompañan a las comunidades.</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Tlen ueyi omochiu</t>
+          <t>Tlapaleuianij tlen kinpaleuiaj altepetsitsin.</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>{n} de abril de {n}</t>
+          <t>Foto anterior</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>{n} abril, {n} xiuitl</t>
+          <t>Achtopa ixkopinkayotl</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -2877,17 +2877,17 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Presentación del programa</t>
+          <t>Foto siguiente</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Teixpantilistle iga nin tlapaleuilistle</t>
+          <t>Ixkopinkayotl tlen uala</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -2908,17 +2908,17 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Arranca la primera etapa con {n} comunidades y {n} promotores comunitarios capacitados.</t>
+          <t>Ver foto {n} de {n}</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>Peua achtopa tlachiualistle iga {n} altepetsitsin uan {n} tlapaleuianij tlen momachtijkej.</t>
+          <t>Xikita ixkopinkayotl {n} ipan {n}</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -2944,16 +2944,20 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Diciembre {n} – enero {n}</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="n"/>
-      <c r="F77" s="4" t="n"/>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Fotos: Gobierno del Estado de Morelos</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>Ixkopinkayotlmej: Kaltlayekana ipan Morelos</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
@@ -2971,12 +2975,12 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>La ATDEM instala aulas de cómputo en {n} escuelas de los polígonos.</t>
+          <t>¿Cómo funciona?</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>ATDEM kitlalia tepostlapoualli ipan {n} kaltlamachtiloyan tlen polígono.</t>
+          <t>¿Kenin teguiti?</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3002,12 +3006,12 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Delimitación vigente</t>
+          <t>Diagnóstico territorial</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Polígono tlen axan</t>
+          <t>Tlatemolistle ipan tlale</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -3033,12 +3037,12 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>{n} localidades en {n} polígonos de atención, que se analizan en este tablero.</t>
+          <t>Las comunidades se identifican mediante un diagnóstico realizado por la Jefatura de la Oficina de la Gubernatura, que define los polígonos de atención.</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>{n} altepetsitsin ipan {n} polígono, tlen motlachilia ipan nin tlapoualli.</t>
+          <t>Altepetsitsin moixmatij iga se tlatemolistle tlen kichiua Jefatura de la Oficina de la Gubernatura, uan yejua kitlalia polígono kanin motekipanos.</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -3064,12 +3068,12 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>Grados de marginación</t>
+          <t>Promotores comunitarios</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Tlapoual iknoyotl</t>
+          <t>Tlapaleuianij ipan altepetsitsin</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -3095,12 +3099,12 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Localidades ({n})</t>
+          <t>Promotores capacitados visitan a la población para escuchar y conocer a detalle sus necesidades básicas.</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin ({n})</t>
+          <t>Tlapaleuianij tlen momachtijkej kinpaxalouaj tlatlaga iga kinkaguiskej uan kualtsin kiixmatiskej tlen kinmonekij.</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -3126,12 +3130,12 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Comunidades prioritarias</t>
+          <t>Acción coordinada</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin tlen achtopa</t>
+          <t>Teguitl tlen sepan mochiua</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -3157,12 +3161,12 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Sin grado de marginación</t>
+          <t>Cada secretaría y organismo del Poder Ejecutivo lleva a cabo acciones coordinadas para fortalecer proyectos de mejora en las localidades.</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Amo kipia itlapoual iknoyotl</t>
+          <t>Nochi secretaría uan teguichiualoyan iga Kaltlayekana sepan teguitij iga kichikauaskej tlachiualmej tlen kikualtlaliaj altepetsitsin.</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -3188,12 +3192,12 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>¿Qué encontrarás en este tablero?</t>
+          <t>Equidad y dignidad</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>¿Tlen tikajsis ipan nin tlapoualli?</t>
+          <t>Sepan tiuejueyij uan tlakaitalistle</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -3219,12 +3223,12 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Indicadores de población, vivienda, tecnologías de la información, salud, educación y economía de las {n} localidades de los {n} polígonos vigentes, por localidad o por polígono completo.</t>
+          <t>El objetivo es construir una sociedad más equitativa y justa, donde todas las personas puedan vivir con dignidad.</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Tlapoualli iga tlatlaga, kalmej, tepostlapoualli uan internet, pajtilistle, temachtilistle uan tomin ipan {n} altepetsitsin tlen {n} polígono tlen axan, iga se altepetsin o iga se polígono nochi.</t>
+          <t>Tlen tiknegui: tikchiuaskej se altepetl kanin nochi sepan katej uan melauak, kanin nochi tlatlaga ueliskej nemiskej iga tlakaitalistle.</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -3250,12 +3254,12 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Ir a Análisis Demográfico</t>
+          <t>El programa en cifras</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Xiyau ipan Tlapoualli iga tlatlaga</t>
+          <t>Nin tlapaleuilistle iga tlapoualli</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -3281,12 +3285,12 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Mapa de las {n} escuelas donde ATDEM instaló aulas de cómputo en los polígonos TPBV: computadoras, nivel educativo y ubicación de cada una.</t>
+          <t>Localidades</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Tlalamatl iga {n} kaltlamachtiloyan kanin ATDEM kitlalij tepostlapoualli ipan polígono TPBV: tepostlapoualmej, temachtilistle uan kanin katej.</t>
+          <t>Altepetsitsin</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -3312,12 +3316,12 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Ir a Aulas Tecnológicas</t>
+          <t>Polígonos</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Xiyau ipan Tlamachtiloyan iga tepostlapoualli</t>
+          <t>Polígono</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -3343,12 +3347,12 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Mapa de las dependencias estatales que ya cuentan con la red Wi-Fi pública y gratuita de la ATDEM: sedes, secretarías y puntos de acceso.</t>
+          <t>Municipios</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Tlalamatl iga teguichiualoyan iga Kaltlayekana tlen ya kipiaj matlatl Wi-Fi tlapojtok uan amo iga tomin tlen ATDEM: kalmej, secretarías uan kanin mosaloua.</t>
+          <t>Altepemej</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -3374,12 +3378,12 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Ir a Red La tierra que nos une</t>
+          <t>Habitantes</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Xiyau ipan Matlatl Nin tlale tech sepaneloa</t>
+          <t>Tlatlaga</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -3405,12 +3409,12 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Escuelas con aula</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Tepostlaketsalmej iga uejka tlanonotsalistle</t>
+          <t>Kaltlamachtiloyan iga tepostlapoualli</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -3436,12 +3440,12 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Sitios y torres de la red estatal por municipio y sector (gobierno, educación, salud y seguridad). Por seguridad se muestran solo de forma agregada.</t>
+          <t>Hitos</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Sitios uan tepostlaketsalmej tlen imatlau Kaltlayekana, iga altepetl uan teguitl (kaltlayekana, temachtilistle, pajtilistle uan tlajpialistle). Iga tlajpialistle san monextiaj sepan.</t>
+          <t>Tlen ueyi omochiu</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -3467,12 +3471,12 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Ir a Telecomunicaciones</t>
+          <t>{n} de abril de {n}</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Xiyau ipan Uejka tlanonotsalistle</t>
+          <t>{n} abril, {n} xiuitl</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -3498,12 +3502,12 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Descarga en CSV y KML las bases de datos del tablero: localidades y polígonos vigentes, Aulas Tecnológicas y límites municipales.</t>
+          <t>Presentación del programa</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga ipan CSV uan KML itlapoual nin tablero: altepetsitsin uan polígono tlen axan, Tlamachtiloyan iga tepostlapoualli uan itlalxelol altepemej.</t>
+          <t>Teixpantilistle iga nin tlapaleuilistle</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -3529,12 +3533,12 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Ir a Datos Abiertos</t>
+          <t>Arranca la primera etapa con {n} comunidades y {n} promotores comunitarios capacitados.</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Xiyau ipan Tlapoualli tlapojtok</t>
+          <t>Peua achtopa tlachiualistle iga {n} altepetsitsin uan {n} tlapaleuianij tlen momachtijkej.</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -3560,20 +3564,16 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Reportes Institucionales</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>Tlapoualamatl iga Kaltlayekana</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="n"/>
+          <t>Diciembre {n} – enero {n}</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="n"/>
+      <c r="F97" s="4" t="n"/>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Genera, para la localidad o el polígono que estés viendo, un documento formal con portada y todas las tablas de indicadores, listo para imprimir o exportar a PDF.</t>
+          <t>La ATDEM instala aulas de cómputo en {n} escuelas de los polígonos.</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Xikchiua, iga altepetsin o polígono tlen tikitta, se amatl iga ixko uan nochi tlapoualli, iga tiktlalis ipan amatl o ipan PDF.</t>
+          <t>ATDEM kitlalia tepostlapoualli ipan {n} kaltlamachtiloyan tlen polígono.</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Ir a generar un reporte</t>
+          <t>Delimitación vigente</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Xikchiua se tlapoualamatl</t>
+          <t>Polígono tlen axan</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -3653,12 +3653,12 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Cómo empezar</t>
+          <t>{n} localidades en {n} polígonos de atención, que se analizan en este tablero.</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Kenin tipeuas</t>
+          <t>{n} altepetsitsin ipan {n} polígono, tlen motlachilia ipan nin tlapoualli.</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Filtra por polígono o localidad</t>
+          <t>Grados de marginación</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Xikpepena polígono o altepetsin</t>
+          <t>Tlapoual iknoyotl</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>En Análisis Demográfico, usa los selectores de la parte superior, o entra directo a un polígono desde el mapa o la lista de localidades.</t>
+          <t>Localidades ({n})</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Ipan Tlapoualli iga tlatlaga, xiktekiuti tlapepenalli tlen kaninpa, o xiyau nimantsin ipan se polígono iga tlalamatl o iga itlapoual altepetsitsin.</t>
+          <t>Altepetsitsin ({n})</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Explora los indicadores</t>
+          <t>Comunidades prioritarias</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Xiktlachili tlapoualli</t>
+          <t>Altepetsitsin tlen achtopa</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Revisa las tarjetas de población, vivienda, salud, educación, economía y la pirámide poblacional, además del mapa de ubicación.</t>
+          <t>Sin grado de marginación</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Xiktlachili tlapoualli iga tlatlaga, kalmej, pajtilistle, temachtilistle, tomin uan keski xiuitl kipiaj, uan tlalamatl kanin katej.</t>
+          <t>Amo kipia itlapoual iknoyotl</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
@@ -3808,12 +3808,12 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Consulta las aulas</t>
+          <t>¿Qué encontrarás en este tablero?</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Xiktlachili tlamachtiloyan</t>
+          <t>¿Tlen tikajsis ipan nin tlapoualli?</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Revisa el mapa de Aulas Tecnológicas instaladas en las escuelas de los polígonos.</t>
+          <t>Indicadores de población, vivienda, tecnologías de la información, salud, educación y economía de las {n} localidades de los {n} polígonos vigentes, por localidad o por polígono completo.</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Xiktlachili tlalamatl iga Tlamachtiloyan iga tepostlapoualli tlen motlalijkej ipan kaltlamachtiloyan tlen polígono.</t>
+          <t>Tlapoualli iga tlatlaga, kalmej, tepostlapoualli uan internet, pajtilistle, temachtilistle uan tomin ipan {n} altepetsitsin tlen {n} polígono tlen axan, iga se altepetsin o iga se polígono nochi.</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Descarga los datos</t>
+          <t>Ir a Análisis Demográfico</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga tlapoualli</t>
+          <t>Xiyau ipan Tlapoualli iga tlatlaga</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -3901,12 +3901,12 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>En Datos Abiertos encontrarás las bases de datos del tablero en CSV y KML.</t>
+          <t>Mapa de las {n} escuelas donde ATDEM instaló aulas de cómputo en los polígonos TPBV: computadoras, nivel educativo y ubicación de cada una.</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Ipan Tlapoualli tlapojtok tikajsis itlapoual nin tablero ipan CSV uan KML.</t>
+          <t>Tlalamatl iga {n} kaltlamachtiloyan kanin ATDEM kitlalij tepostlapoualli ipan polígono TPBV: tepostlapoualmej, temachtilistle uan kanin katej.</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Genera tu reporte</t>
+          <t>Ir a Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>Xikchiua motlapoualamau</t>
+          <t>Xiyau ipan Tlamachtiloyan iga tepostlapoualli</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Usa el botón "Reporte Institucional" para exportar un documento formal en PDF de lo que estés viendo.</t>
+          <t>Mapa de las dependencias estatales que ya cuentan con la red Wi-Fi pública y gratuita de la ATDEM: sedes, secretarías y puntos de acceso.</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Xiktekiuti "Tlapoualamatl iga Kaltlayekana" iga tikixtis se amatl PDF iga tlen tikitta.</t>
+          <t>Tlalamatl iga teguichiualoyan iga Kaltlayekana tlen ya kipiaj matlatl Wi-Fi tlapojtok uan amo iga tomin tlen ATDEM: kalmej, secretarías uan kanin mosaloua.</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Población Total</t>
+          <t>Ir a Red La tierra que nos une</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>Nochi tlatlaga</t>
+          <t>Xiyau ipan Matlatl Nin tlale tech sepaneloa</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -4025,12 +4025,12 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Viviendas Totales</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Nochi kalmej</t>
+          <t>Tepostlaketsalmej iga uejka tlanonotsalistle</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Afiliación a Salud</t>
+          <t>Sitios y torres de la red estatal por municipio y sector (gobierno, educación, salud y seguridad). Por seguridad se muestran solo de forma agregada.</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>Tlen kipiaj pajtilistle</t>
+          <t>Sitios uan tepostlaketsalmej tlen imatlau Kaltlayekana, iga altepetl uan teguitl (kaltlayekana, temachtilistle, pajtilistle uan tlajpialistle). Iga tlajpialistle san monextiaj sepan.</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Localidades Totales</t>
+          <t>Ir a Telecomunicaciones</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Nochi altepetsitsin</t>
+          <t>Xiyau ipan Uejka tlanonotsalistle</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
@@ -4118,12 +4118,12 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Información General</t>
+          <t>Descarga en CSV y KML las bases de datos del tablero: localidades y polígonos vigentes, Aulas Tecnológicas y límites municipales.</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>Tlamachilistle</t>
+          <t>Xikuiga ipan CSV uan KML itlapoual nin tablero: altepetsitsin uan polígono tlen axan, Tlamachtiloyan iga tepostlapoualli uan itlalxelol altepemej.</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
@@ -4149,12 +4149,12 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Municipio</t>
+          <t>Ir a Datos Abiertos</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Altepetl</t>
+          <t>Xiyau ipan Tlapoualli tlapojtok</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>{n} municipios</t>
+          <t>Reportes Institucionales</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>{n} altepemej</t>
+          <t>Tlapoualamatl iga Kaltlayekana</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Región</t>
+          <t>Genera, para la localidad o el polígono que estés viendo, un documento formal con portada y todas las tablas de indicadores, listo para imprimir o exportar a PDF.</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>Tlalxeloli</t>
+          <t>Xikchiua, iga altepetsin o polígono tlen tikitta, se amatl iga ixko uan nochi tlapoualli, iga tiktlalis ipan amatl o ipan PDF.</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Ir a generar un reporte</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Xikchiua se tlapoualamatl</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Polígonos incluidos</t>
+          <t>Cómo empezar</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>Polígono tlen kipia</t>
+          <t>Kenin tipeuas</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Localidades incluidas</t>
+          <t>Filtra por polígono o localidad</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin tlen kipia</t>
+          <t>Xikpepena polígono o altepetsin</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
@@ -4335,12 +4335,12 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>{n} de {n}</t>
+          <t>En Análisis Demográfico, usa los selectores de la parte superior, o entra directo a un polígono desde el mapa o la lista de localidades.</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>{n} ipan {n}</t>
+          <t>Ipan Tlapoualli iga tlatlaga, xiktekiuti tlapepenalli tlen kaninpa, o xiyau nimantsin ipan se polígono iga tlalamatl o iga itlapoual altepetsitsin.</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Grados de Marginación</t>
+          <t>Explora los indicadores</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>Tlapoual iknoyotl</t>
+          <t>Xiktlachili tlapoualli</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Todas las Localidades</t>
+          <t>Revisa las tarjetas de población, vivienda, salud, educación, economía y la pirámide poblacional, además del mapa de ubicación.</t>
         </is>
       </c>
       <c r="E124" s="5" t="inlineStr">
         <is>
-          <t>Nochi altepetsitsin</t>
+          <t>Xiktlachili tlapoualli iga tlatlaga, kalmej, pajtilistle, temachtilistle, tomin uan keski xiuitl kipiaj, uan tlalamatl kanin katej.</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Ubicación Geográfica</t>
+          <t>Consulta las aulas</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr">
         <is>
-          <t>Kanin katej</t>
+          <t>Xiktlachili tlamachtiloyan</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Localidad</t>
+          <t>Revisa el mapa de Aulas Tecnológicas instaladas en las escuelas de los polígonos.</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr">
         <is>
-          <t>Altepetsin</t>
+          <t>Xiktlachili tlalamatl iga Tlamachtiloyan iga tepostlapoualli tlen motlalijkej ipan kaltlamachtiloyan tlen polígono.</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
@@ -4490,16 +4490,20 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Polígono TPBV</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="n"/>
-      <c r="F127" s="4" t="n"/>
-      <c r="G127" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Descarga los datos</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga tlapoualli</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="n">
@@ -4512,17 +4516,17 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Zoom in</t>
+          <t>En Datos Abiertos encontrarás las bases de datos del tablero en CSV y KML.</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr">
         <is>
-          <t>Xikueyichiua</t>
+          <t>Ipan Tlapoualli tlapojtok tikajsis itlapoual nin tablero ipan CSV uan KML.</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -4543,17 +4547,17 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>Zoom out</t>
+          <t>Genera tu reporte</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr">
         <is>
-          <t>Xiktepitonchiua</t>
+          <t>Xikchiua motlapoualamau</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
@@ -4579,12 +4583,12 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>{n} de {n} localidades no tienen coincidencia en el Censo INEGI {n} (suelen ser colonias/barrios dentro de una cabecera urbana). Su población sí está incluida en el total (vía la Lista TPBV {n}), pero vivienda, salud, educación y economía no — esos indicadores solo suman las localidades con coincidencia censal. Revísalas en la lista de localidades.</t>
+          <t>Usa el botón "Reporte Institucional" para exportar un documento formal en PDF de lo que estés viendo.</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr">
         <is>
-          <t>{n} ipan {n} altepetsitsin amo monextiaj ipan Censo INEGI {n} (miakpa colonias o barrios ipan se ueyi altepetl). Intlatlaga motlapouaj ipan nochi (iga Lista TPBV {n}), san kalmej, pajtilistle, temachtilistle uan tomin amo — nin tlapoualli san kinsentlalia altepetsitsin tlen monextiaj ipan censo. Xikintlachili ipan itlapoual altepetsitsin.</t>
+          <t>Xiktekiuti "Tlapoualamatl iga Kaltlayekana" iga tikixtis se amatl PDF iga tlen tikitta.</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
@@ -4610,12 +4614,12 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Demografía</t>
+          <t>Población Total</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr">
         <is>
-          <t>Tlatlaga iga tlapoualli</t>
+          <t>Nochi tlatlaga</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
@@ -4641,12 +4645,12 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Población</t>
+          <t>Viviendas Totales</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr">
         <is>
-          <t>Tlatlaga</t>
+          <t>Nochi kalmej</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
@@ -4672,12 +4676,12 @@
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Mujeres</t>
+          <t>Afiliación a Salud</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr">
         <is>
-          <t>Soamej</t>
+          <t>Tlen kipiaj pajtilistle</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
@@ -4703,12 +4707,12 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Hombres</t>
+          <t>Localidades Totales</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr">
         <is>
-          <t>Tlagamej</t>
+          <t>Nochi altepetsitsin</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
@@ -4734,12 +4738,12 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Población Indígena y Afromexicana</t>
+          <t>Información General</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
         <is>
-          <t>Maseualmej uan afromexikanojmej</t>
+          <t>Tlamachilistle</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
@@ -4765,12 +4769,12 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Habla Lengua Indígena</t>
+          <t>Municipio</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr">
         <is>
-          <t>Kitlajtouaj maseualtlajtolli</t>
+          <t>Altepetl</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -4796,12 +4800,12 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Monolingüe (no habla español)</t>
+          <t>{n} municipios</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr">
         <is>
-          <t>San se tlajtolli (amo kitlajtouaj kaxtilan tlajtolli)</t>
+          <t>{n} altepemej</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
@@ -4827,12 +4831,12 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Hogares Censales Indígenas</t>
+          <t>Región</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>Kalmej kanin chantij maseualmej</t>
+          <t>Tlalxeloli</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
@@ -4858,12 +4862,12 @@
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Pob. Afromexicana</t>
+          <t>Polígono</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr">
         <is>
-          <t>Afromexikanojmej</t>
+          <t>Polígono</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
@@ -4889,12 +4893,12 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Estructura de Población por Edad y Sexo</t>
+          <t>Polígonos incluidos</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr">
         <is>
-          <t>Tlatlaga iga ixiuiu, soamej uan tlagamej</t>
+          <t>Polígono tlen kipia</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
@@ -4915,17 +4919,17 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>{n}+ años · Mujeres: {n} · Hombres: {n}</t>
+          <t>Localidades incluidas</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr">
         <is>
-          <t>{n}+ xiuitl · Soamej: {n} · Tlagamej: {n}</t>
+          <t>Altepetsitsin tlen kipia</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
@@ -4946,17 +4950,17 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>{n}-{n} años · Mujeres: {n} · Hombres: {n}</t>
+          <t>Grados de Marginación</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr">
         <is>
-          <t>{n}-{n} xiuitl · Soamej: {n} · Tlagamej: {n}</t>
+          <t>Tlapoual iknoyotl</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
@@ -4982,12 +4986,12 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Razón de dependencia demográfica</t>
+          <t>Todas las Localidades</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr">
         <is>
-          <t>Keski moneki ma kinpaleuikaj</t>
+          <t>Nochi altepetsitsin</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
@@ -5013,12 +5017,12 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Personas dependientes ({n}-{n} y {n}+) por cada {n} en edad de trabajar ({n}-{n}: {n})</t>
+          <t>Ubicación Geográfica</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr">
         <is>
-          <t>Akin moneki ma kinpaleuikaj ({n}-{n} uan {n}+) iga nochi {n} tlen ueli teguitij ({n}-{n}: {n})</t>
+          <t>Kanin katej</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
@@ -5044,12 +5048,12 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Vivienda y Servicios</t>
+          <t>Localidad</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr">
         <is>
-          <t>Kalle uan tlen kipia</t>
+          <t>Altepetsin</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
@@ -5075,20 +5079,16 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Vivienda</t>
-        </is>
-      </c>
-      <c r="E146" s="5" t="inlineStr">
-        <is>
-          <t>Kalle</t>
-        </is>
-      </c>
-      <c r="F146" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G146" s="4" t="n"/>
+          <t>Polígono TPBV</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="n"/>
+      <c r="F146" s="4" t="n"/>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n">
@@ -5101,17 +5101,17 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Total Viviendas</t>
+          <t>Zoom in</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr">
         <is>
-          <t>Nochi kalmej</t>
+          <t>Xikueyichiua</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
@@ -5132,17 +5132,17 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Piso de Tierra</t>
+          <t>Zoom out</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr">
         <is>
-          <t>Tlalchi san tlale</t>
+          <t>Xiktepitonchiua</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Un Solo Cuarto</t>
+          <t>{n} de {n} localidades no tienen coincidencia en el Censo INEGI {n} (suelen ser colonias/barrios dentro de una cabecera urbana). Su población sí está incluida en el total (vía la Lista TPBV {n}), pero vivienda, salud, educación y economía no — esos indicadores solo suman las localidades con coincidencia censal. Revísalas en la lista de localidades.</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
         <is>
-          <t>San se kalijtik</t>
+          <t>{n} ipan {n} altepetsitsin amo monextiaj ipan Censo INEGI {n} (miakpa colonias o barrios ipan se ueyi altepetl). Intlatlaga motlapouaj ipan nochi (iga Lista TPBV {n}), san kalmej, pajtilistle, temachtilistle uan tomin amo — nin tlapoualli san kinsentlalia altepetsitsin tlen monextiaj ipan censo. Xikintlachili ipan itlapoual altepetsitsin.</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Con Hacinamiento</t>
+          <t>Demografía</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
         <is>
-          <t>Miak chantij ipan se kalle</t>
+          <t>Tlatlaga iga tlapoualli</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Tecnologías de Información (TIC)</t>
+          <t>Población</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
         <is>
-          <t>Tepostlapoualli uan tlanonotsalistle (TIC)</t>
+          <t>Tlatlaga</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
@@ -5261,12 +5261,12 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Con Celular</t>
+          <t>Mujeres</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
         <is>
-          <t>Kipiaj celular</t>
+          <t>Soamej</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
@@ -5292,12 +5292,12 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Con Computadora</t>
+          <t>Hombres</t>
         </is>
       </c>
       <c r="E153" s="5" t="inlineStr">
         <is>
-          <t>Kipiaj tepostlapoualli</t>
+          <t>Tlagamej</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Con Internet</t>
+          <t>Población Indígena y Afromexicana</t>
         </is>
       </c>
       <c r="E154" s="5" t="inlineStr">
         <is>
-          <t>Kipiaj internet</t>
+          <t>Maseualmej uan afromexikanojmej</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Bienes y Servicios en la Vivienda</t>
+          <t>Habla Lengua Indígena</t>
         </is>
       </c>
       <c r="E155" s="5" t="inlineStr">
         <is>
-          <t>Tlen kipiaj ipan kalle</t>
+          <t>Kitlajtouaj maseualtlajtolli</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
@@ -5385,16 +5385,20 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Refrigerador</t>
-        </is>
-      </c>
-      <c r="E156" s="4" t="n"/>
-      <c r="F156" s="4" t="n"/>
-      <c r="G156" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Monolingüe (no habla español)</t>
+        </is>
+      </c>
+      <c r="E156" s="5" t="inlineStr">
+        <is>
+          <t>San se tlajtolli (amo kitlajtouaj kaxtilan tlajtolli)</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n">
@@ -5412,16 +5416,20 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Lavadora</t>
-        </is>
-      </c>
-      <c r="E157" s="4" t="n"/>
-      <c r="F157" s="4" t="n"/>
-      <c r="G157" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Hogares Censales Indígenas</t>
+        </is>
+      </c>
+      <c r="E157" s="5" t="inlineStr">
+        <is>
+          <t>Kalmej kanin chantij maseualmej</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="n">
@@ -5439,16 +5447,20 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Automóvil</t>
-        </is>
-      </c>
-      <c r="E158" s="4" t="n"/>
-      <c r="F158" s="4" t="n"/>
-      <c r="G158" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Pob. Afromexicana</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>Afromexikanojmej</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="n">
@@ -5466,12 +5478,12 @@
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Agua Entubada</t>
+          <t>Estructura de Población por Edad y Sexo</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
         <is>
-          <t>Atl ipan kalle</t>
+          <t>Tlatlaga iga ixiuiu, soamej uan tlagamej</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
@@ -5492,17 +5504,17 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>Drenaje</t>
+          <t>{n}+ años · Mujeres: {n} · Hombres: {n}</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
         <is>
-          <t>Apantle (drenaje)</t>
+          <t>{n}+ xiuitl · Soamej: {n} · Tlagamej: {n}</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
@@ -5523,17 +5535,17 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>{n}-{n} años · Mujeres: {n} · Hombres: {n}</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
         <is>
-          <t>Tlauille</t>
+          <t>{n}-{n} xiuitl · Soamej: {n} · Tlagamej: {n}</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
@@ -5559,12 +5571,12 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Salud y Bienestar</t>
+          <t>Razón de dependencia demográfica</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
         <is>
-          <t>Pajtilistle uan kuale nemilistle</t>
+          <t>Keski moneki ma kinpaleuikaj</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
@@ -5590,12 +5602,12 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Servicios de Salud</t>
+          <t>Personas dependientes ({n}-{n} y {n}+) por cada {n} en edad de trabajar ({n}-{n}: {n})</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>Tlapaleuilistle iga pajtilistle</t>
+          <t>Akin moneki ma kinpaleuikaj ({n}-{n} uan {n}+) iga nochi {n} tlen ueli teguitij ({n}-{n}: {n})</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
@@ -5621,12 +5633,12 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Total Afiliados</t>
+          <t>Vivienda y Servicios</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>Nochi tlen kipiaj pajtilistle</t>
+          <t>Kalle uan tlen kipia</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
@@ -5652,12 +5664,12 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Sin Afiliación</t>
+          <t>Vivienda</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>Amo kipiaj pajtilistle</t>
+          <t>Kalle</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
@@ -5683,12 +5695,12 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>Afiliados al IMSS</t>
+          <t>Total Viviendas</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>Kipiaj IMSS</t>
+          <t>Nochi kalmej</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
@@ -5714,12 +5726,12 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Afiliados al ISSSTE</t>
+          <t>Piso de Tierra</t>
         </is>
       </c>
       <c r="E167" s="5" t="inlineStr">
         <is>
-          <t>Kipiaj ISSSTE</t>
+          <t>Tlalchi san tlale</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
@@ -5745,12 +5757,12 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Otros Servicios de Salud</t>
+          <t>Un Solo Cuarto</t>
         </is>
       </c>
       <c r="E168" s="5" t="inlineStr">
         <is>
-          <t>Siguin tlapaleuilistle iga pajtilistle</t>
+          <t>San se kalijtik</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
@@ -5776,12 +5788,12 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Discapacidad y Condiciones de Salud</t>
+          <t>Con Hacinamiento</t>
         </is>
       </c>
       <c r="E169" s="5" t="inlineStr">
         <is>
-          <t>Amo uelilistle uan kogolistle</t>
+          <t>Miak chantij ipan se kalle</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
@@ -5807,12 +5819,12 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Con Discapacidad</t>
+          <t>Tecnologías de Información (TIC)</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
         <is>
-          <t>Kipiaj amo uelilistle</t>
+          <t>Tepostlapoualli uan tlanonotsalistle (TIC)</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
@@ -5838,12 +5850,12 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>Con Limitación</t>
+          <t>Con Celular</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
         <is>
-          <t>Kipiaj tlen kintsakua</t>
+          <t>Kipiaj celular</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
@@ -5869,12 +5881,12 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>Con Problema o Condición Mental</t>
+          <t>Con Computadora</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
         <is>
-          <t>Kipiaj kogolistle ipan intsontekon</t>
+          <t>Kipiaj tepostlapoualli</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
@@ -5900,12 +5912,12 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>Educación y Economía</t>
+          <t>Con Internet</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>Temachtilistle uan tomin</t>
+          <t>Kipiaj internet</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
@@ -5931,12 +5943,12 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>Bienes y Servicios en la Vivienda</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Temachtilistle</t>
+          <t>Tlen kipiaj ipan kalle</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
@@ -5962,20 +5974,16 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>Grado Promedio de Escolaridad</t>
-        </is>
-      </c>
-      <c r="E175" s="5" t="inlineStr">
-        <is>
-          <t>Keski xiuitl momachtijkej</t>
-        </is>
-      </c>
-      <c r="F175" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G175" s="4" t="n"/>
+          <t>Refrigerador</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="n"/>
+      <c r="F175" s="4" t="n"/>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="n">
@@ -5993,20 +6001,16 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>{n} años</t>
-        </is>
-      </c>
-      <c r="E176" s="5" t="inlineStr">
-        <is>
-          <t>{n} xiuitl</t>
-        </is>
-      </c>
-      <c r="F176" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G176" s="4" t="n"/>
+          <t>Lavadora</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="n"/>
+      <c r="F176" s="4" t="n"/>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n">
@@ -6024,20 +6028,16 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Analfabetas ({n}+)</t>
-        </is>
-      </c>
-      <c r="E177" s="5" t="inlineStr">
-        <is>
-          <t>Amo kimatij tlajkuiloj ({n}+)</t>
-        </is>
-      </c>
-      <c r="F177" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G177" s="4" t="n"/>
+          <t>Automóvil</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="n"/>
+      <c r="F177" s="4" t="n"/>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="n">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Sin Educación Básica Completa ({n}+)</t>
+          <t>Agua Entubada</t>
         </is>
       </c>
       <c r="E178" s="5" t="inlineStr">
         <is>
-          <t>Amo kitlamiltijkej achtopa temachtilistle ({n}+)</t>
+          <t>Atl ipan kalle</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
@@ -6086,12 +6086,12 @@
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Niñas/os {n}-{n} años sin asistir a la escuela</t>
+          <t>Drenaje</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
         <is>
-          <t>Pipiltontij {n}-{n} xiuitl tlen amo yaj kaltlamachtiloyan</t>
+          <t>Apantle (drenaje)</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
@@ -6117,12 +6117,12 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Adolescentes {n}-{n} años sin asistir a la escuela</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>Telpogamej {n}-{n} xiuitl tlen amo yaj kaltlamachtiloyan</t>
+          <t>Tlauille</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Económicamente Activa (PEA)</t>
+          <t>Salud y Bienestar</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>Tlen ueli teguitij (PEA)</t>
+          <t>Pajtilistle uan kuale nemilistle</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Ocupada</t>
+          <t>Servicios de Salud</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>Teguitij</t>
+          <t>Tlapaleuilistle iga pajtilistle</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
@@ -6210,12 +6210,12 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Desocupada</t>
+          <t>Total Afiliados</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>Amo kipiaj teguitl</t>
+          <t>Nochi tlen kipiaj pajtilistle</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Ocupada en Sector Primario</t>
+          <t>Sin Afiliación</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
         <is>
-          <t>Teguitij ipan milpa uan tlale</t>
+          <t>Amo kipiaj pajtilistle</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="B185" s="4" t="inlineStr">
         <is>
-          <t>Inicio (buscador de comunidades)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C185" s="4" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Sí, esta comunidad está en el programa.</t>
+          <t>Afiliados al IMSS</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>Kema, nin altepetsin kalaktok ipan nin tlapaleuilistle.</t>
+          <t>Kipiaj IMSS</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="B186" s="4" t="inlineStr">
         <is>
-          <t>Inicio (buscador de comunidades)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C186" s="4" t="inlineStr">
@@ -6303,16 +6303,20 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>{d} · Polígono {d}</t>
-        </is>
-      </c>
-      <c r="E186" s="4" t="n"/>
-      <c r="F186" s="4" t="n"/>
-      <c r="G186" s="4" t="inlineStr">
-        <is>
-          <t>No requiere traducción (nombres y la palabra «Polígono»).</t>
-        </is>
-      </c>
+          <t>Afiliados al ISSSTE</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="inlineStr">
+        <is>
+          <t>Kipiaj ISSSTE</t>
+        </is>
+      </c>
+      <c r="F186" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="n">
@@ -6320,7 +6324,7 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>Inicio (buscador de comunidades)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C187" s="4" t="inlineStr">
@@ -6330,12 +6334,12 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Ver sus datos</t>
+          <t>Otros Servicios de Salud</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>Xikita itlapoual</t>
+          <t>Siguin tlapaleuilistle iga pajtilistle</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
@@ -6351,7 +6355,7 @@
       </c>
       <c r="B188" s="4" t="inlineStr">
         <is>
-          <t>Inicio (buscador de comunidades)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C188" s="4" t="inlineStr">
@@ -6361,12 +6365,12 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Encontramos {n} comunidades del programa con ese nombre.</t>
+          <t>Discapacidad y Condiciones de Salud</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>Otikajsike {n} altepetsitsin tlen nin tlapaleuilistle tlen kipiaj nin itoga.</t>
+          <t>Amo uelilistle uan kogolistle</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
@@ -6382,7 +6386,7 @@
       </c>
       <c r="B189" s="4" t="inlineStr">
         <is>
-          <t>Inicio (buscador de comunidades)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C189" s="4" t="inlineStr">
@@ -6392,12 +6396,12 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Y {n} comunidades más. Escribe más letras para afinar la búsqueda.</t>
+          <t>Con Discapacidad</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>Uan ogachi {n} altepetsitsin. Xiktlajkuilo ogachi tlajkuilolli iga tiktemos kuale.</t>
+          <t>Kipiaj amo uelilistle</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
@@ -6413,7 +6417,7 @@
       </c>
       <c r="B190" s="4" t="inlineStr">
         <is>
-          <t>Inicio (buscador de comunidades)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C190" s="4" t="inlineStr">
@@ -6423,12 +6427,12 @@
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>{d} tiene {n} comunidades en el programa.</t>
+          <t>Con Limitación</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>{d} kipia {n} altepetsitsin ipan nin tlapaleuilistle.</t>
+          <t>Kipiaj tlen kintsakua</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
@@ -6444,7 +6448,7 @@
       </c>
       <c r="B191" s="4" t="inlineStr">
         <is>
-          <t>Inicio (buscador de comunidades)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C191" s="4" t="inlineStr">
@@ -6454,12 +6458,12 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>{d} no tiene comunidades en la delimitación vigente del programa.</t>
+          <t>Con Problema o Condición Mental</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>{d} amo kipia altepetsitsin ipan nin tlapaleuilistle axan.</t>
+          <t>Kipiaj kogolistle ipan intsontekon</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
@@ -6475,7 +6479,7 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (un polígono)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C192" s="4" t="inlineStr">
@@ -6485,12 +6489,12 @@
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Localidades en el Polígono</t>
+          <t>Educación y Economía</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin ipan polígono</t>
+          <t>Temachtilistle uan tomin</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
@@ -6506,7 +6510,7 @@
       </c>
       <c r="B193" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (un polígono)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C193" s="4" t="inlineStr">
@@ -6516,12 +6520,12 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Localidades en este Polígono</t>
+          <t>Educación</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin ipan nin polígono</t>
+          <t>Temachtilistle</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
@@ -6537,7 +6541,7 @@
       </c>
       <c r="B194" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (una localidad)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C194" s="4" t="inlineStr">
@@ -6547,12 +6551,12 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Grado de Marginación</t>
+          <t>Grado Promedio de Escolaridad</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>Tlapoual iknoyotl</t>
+          <t>Keski xiuitl momachtijkej</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
@@ -6568,7 +6572,7 @@
       </c>
       <c r="B195" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (una localidad)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C195" s="4" t="inlineStr">
@@ -6578,16 +6582,20 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Polígono {n} · {d}</t>
-        </is>
-      </c>
-      <c r="E195" s="4" t="n"/>
-      <c r="F195" s="4" t="n"/>
-      <c r="G195" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>{n} años</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="inlineStr">
+        <is>
+          <t>{n} xiuitl</t>
+        </is>
+      </c>
+      <c r="F195" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="4" t="n">
@@ -6595,7 +6603,7 @@
       </c>
       <c r="B196" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (una localidad)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C196" s="4" t="inlineStr">
@@ -6605,12 +6613,12 @@
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>Marginación: {d}</t>
+          <t>Analfabetas ({n}+)</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>Iknoyotl: {d}</t>
+          <t>Amo kimatij tlajkuiloj ({n}+)</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
@@ -6626,22 +6634,22 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (una localidad)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Close popup</t>
+          <t>Sin Educación Básica Completa ({n}+)</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>Xiktsagua</t>
+          <t>Amo kitlamiltijkej achtopa temachtilistle ({n}+)</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
@@ -6657,7 +6665,7 @@
       </c>
       <c r="B198" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (localidad sin datos censales)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C198" s="4" t="inlineStr">
@@ -6667,12 +6675,12 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Coordenada capturada manualmente</t>
+          <t>Niñas/os {n}-{n} años sin asistir a la escuela</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>Kanin katej, omojkuilo iga ma</t>
+          <t>Pipiltontij {n}-{n} xiuitl tlen amo yaj kaltlamachtiloyan</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
@@ -6688,7 +6696,7 @@
       </c>
       <c r="B199" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (localidad sin datos censales)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C199" s="4" t="inlineStr">
@@ -6698,12 +6706,12 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>Sin Datos Censales Disponibles</t>
+          <t>Adolescentes {n}-{n} años sin asistir a la escuela</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>Amo kipia itlapoual censo</t>
+          <t>Telpogamej {n}-{n} xiuitl tlen amo yaj kaltlamachtiloyan</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
@@ -6719,7 +6727,7 @@
       </c>
       <c r="B200" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (localidad sin datos censales)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C200" s="4" t="inlineStr">
@@ -6729,12 +6737,12 @@
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>No se encontró una coincidencia confiable para {d} en el Censo INEGI {n} (ITER Morelos). Esto ocurre principalmente con colonias/barrios urbanos que no se registran como localidad censal independiente. El mapa muestra su ubicación (coordenada capturada manualmente) dentro de polígono {n}.</t>
+          <t>Económicamente Activa (PEA)</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>Amo omonexti {d} ipan Censo INEGI {n} (ITER Morelos). Nin panoa ogachi iga colonias o barrios ipan ueyi altepetl tlen amo motlapouaj kemej altepetsin. Tlalamatl kinextia kanin katej (omojkuilo iga ma) ipan polígono {n}.</t>
+          <t>Tlen ueli teguitij (PEA)</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
@@ -6750,7 +6758,7 @@
       </c>
       <c r="B201" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (localidad sin datos censales)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C201" s="4" t="inlineStr">
@@ -6760,12 +6768,12 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>Población reportada (Lista TPBV {n})</t>
+          <t>Ocupada</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
         <is>
-          <t>Tlatlaga tlen motlapoukej (Lista TPBV {n})</t>
+          <t>Teguitij</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
@@ -6781,7 +6789,7 @@
       </c>
       <c r="B202" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (filtro personalizado)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C202" s="4" t="inlineStr">
@@ -6791,12 +6799,12 @@
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>Elige los polígonos a comparar</t>
+          <t>Desocupada</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
         <is>
-          <t>Xikpepena polígono tlen tikinneneuilis</t>
+          <t>Amo kipiaj teguitl</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
@@ -6812,7 +6820,7 @@
       </c>
       <c r="B203" s="4" t="inlineStr">
         <is>
-          <t>Análisis Demográfico (filtro personalizado)</t>
+          <t>Inicio</t>
         </is>
       </c>
       <c r="C203" s="4" t="inlineStr">
@@ -6822,12 +6830,12 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>Limpiar</t>
+          <t>Ocupada en Sector Primario</t>
         </is>
       </c>
       <c r="E203" s="5" t="inlineStr">
         <is>
-          <t>Xikpojpoa</t>
+          <t>Teguitij ipan milpa uan tlale</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
@@ -6843,7 +6851,7 @@
       </c>
       <c r="B204" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Inicio (buscador de comunidades)</t>
         </is>
       </c>
       <c r="C204" s="4" t="inlineStr">
@@ -6853,12 +6861,12 @@
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>Territorios de Paz y Buen Vivir · Educación digital</t>
+          <t>Sí, esta comunidad está en el programa.</t>
         </is>
       </c>
       <c r="E204" s="5" t="inlineStr">
         <is>
-          <t>Territorios de Paz y Buen Vivir · Temachtilistle iga tepostlapoualli</t>
+          <t>Kema, nin altepetsin kalaktok ipan nin tlapaleuilistle.</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
@@ -6874,7 +6882,7 @@
       </c>
       <c r="B205" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Inicio (buscador de comunidades)</t>
         </is>
       </c>
       <c r="C205" s="4" t="inlineStr">
@@ -6884,20 +6892,16 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>Para reducir la brecha digital desde edades tempranas, la Agencia de Transformación Digital del Estado de Morelos (ATDEM), en coordinación con la Secretaría de Educación y el Instituto de Educación Básica del Estado de Morelos (IEBEM), equipó aulas de cómputo en {n} escuelas de {n} municipios ubicadas en los polígonos de Territorios de Paz y Buen Vivir.</t>
-        </is>
-      </c>
-      <c r="E205" s="5" t="inlineStr">
-        <is>
-          <t>Iga ma moyekchiua tlen amo kipiaj tepostlapoualli kuak tsitsikitsin, Agencia de Transformación Digital del Estado de Morelos (ATDEM), sepan iga Secretaría de Educación uan Instituto de Educación Básica del Estado de Morelos (IEBEM), kitlalij tepostlapoualli ipan {n} kaltlamachtiloyan ipan {n} altepemej tlen katej ipan polígono Territorios de Paz y Buen Vivir.</t>
-        </is>
-      </c>
-      <c r="F205" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G205" s="4" t="n"/>
+          <t>{d} · Polígono {d}</t>
+        </is>
+      </c>
+      <c r="E205" s="4" t="n"/>
+      <c r="F205" s="4" t="n"/>
+      <c r="G205" s="4" t="inlineStr">
+        <is>
+          <t>No requiere traducción (nombres y la palabra «Polígono»).</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="n">
@@ -6905,7 +6909,7 @@
       </c>
       <c r="B206" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Inicio (buscador de comunidades)</t>
         </is>
       </c>
       <c r="C206" s="4" t="inlineStr">
@@ -6915,12 +6919,12 @@
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>Con computadoras conectadas a internet y software educativo, niñas, niños y jóvenes fortalecen sus procesos de aprendizaje, desarrollan habilidades digitales y amplían sus oportunidades en entornos con mayor infraestructura tecnológica.</t>
+          <t>Ver sus datos</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>Iga tepostlapoualli tlen kipiaj internet uan programas iga temachtilistle, pipiltontij uan telpogamej ogachi kualtsin momachtiaj, kimachtiaj tepostlapoualli uan ogachi ojmej kipiaj.</t>
+          <t>Xikita itlapoual</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
@@ -6936,7 +6940,7 @@
       </c>
       <c r="B207" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Inicio (buscador de comunidades)</t>
         </is>
       </c>
       <c r="C207" s="4" t="inlineStr">
@@ -6946,16 +6950,20 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>Secretaría de Educación</t>
-        </is>
-      </c>
-      <c r="E207" s="4" t="n"/>
-      <c r="F207" s="4" t="n"/>
-      <c r="G207" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Encontramos {n} comunidades del programa con ese nombre.</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>Otikajsike {n} altepetsitsin tlen nin tlapaleuilistle tlen kipiaj nin itoga.</t>
+        </is>
+      </c>
+      <c r="F207" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="4" t="n">
@@ -6963,7 +6971,7 @@
       </c>
       <c r="B208" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Inicio (buscador de comunidades)</t>
         </is>
       </c>
       <c r="C208" s="4" t="inlineStr">
@@ -6973,12 +6981,12 @@
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>Instalación: diciembre {n} a enero {n}</t>
+          <t>Y {n} comunidades más. Escribe más letras para afinar la búsqueda.</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
         <is>
-          <t>Motlalij: peuak diciembre {n}, tlamik enero {n}</t>
+          <t>Uan ogachi {n} altepetsitsin. Xiktlajkuilo ogachi tlajkuilolli iga tiktemos kuale.</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
@@ -6994,7 +7002,7 @@
       </c>
       <c r="B209" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Inicio (buscador de comunidades)</t>
         </is>
       </c>
       <c r="C209" s="4" t="inlineStr">
@@ -7004,12 +7012,12 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>¿Qué incluye cada aula?</t>
+          <t>{d} tiene {n} comunidades en el programa.</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
         <is>
-          <t>¿Tlen kipia nochi tlamachtiloyan?</t>
+          <t>{d} kipia {n} altepetsitsin ipan nin tlapaleuilistle.</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
@@ -7025,7 +7033,7 @@
       </c>
       <c r="B210" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Inicio (buscador de comunidades)</t>
         </is>
       </c>
       <c r="C210" s="4" t="inlineStr">
@@ -7035,12 +7043,12 @@
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>Equipo de cómputo</t>
+          <t>{d} no tiene comunidades en la delimitación vigente del programa.</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
         <is>
-          <t>Tepostlapoualli</t>
+          <t>{d} amo kipia altepetsitsin ipan nin tlapaleuilistle axan.</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
@@ -7056,7 +7064,7 @@
       </c>
       <c r="B211" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (un polígono)</t>
         </is>
       </c>
       <c r="C211" s="4" t="inlineStr">
@@ -7066,12 +7074,12 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>{n} computadoras con conexión a internet y software educativo.</t>
+          <t>Localidades en el Polígono</t>
         </is>
       </c>
       <c r="E211" s="5" t="inlineStr">
         <is>
-          <t>{n} tepostlapoualli iga internet uan programas iga temachtilistle.</t>
+          <t>Altepetsitsin ipan polígono</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
@@ -7087,7 +7095,7 @@
       </c>
       <c r="B212" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (un polígono)</t>
         </is>
       </c>
       <c r="C212" s="4" t="inlineStr">
@@ -7097,12 +7105,12 @@
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>Mobiliario</t>
+          <t>Localidades en este Polígono</t>
         </is>
       </c>
       <c r="E212" s="5" t="inlineStr">
         <is>
-          <t>Ikpalmej uan tlapechmej</t>
+          <t>Altepetsitsin ipan nin polígono</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
@@ -7118,7 +7126,7 @@
       </c>
       <c r="B213" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (una localidad)</t>
         </is>
       </c>
       <c r="C213" s="4" t="inlineStr">
@@ -7128,12 +7136,12 @@
       </c>
       <c r="D213" s="4" t="inlineStr">
         <is>
-          <t>{n} sillas y {n} mesas para las aulas que no contaban con mobiliario suficiente.</t>
+          <t>Grado de Marginación</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
         <is>
-          <t>{n} ikpalmej uan {n} tlapechmej iga tlamachtiloyan tlen amo kipiayaj.</t>
+          <t>Tlapoual iknoyotl</t>
         </is>
       </c>
       <c r="F213" s="4" t="inlineStr">
@@ -7149,7 +7157,7 @@
       </c>
       <c r="B214" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (una localidad)</t>
         </is>
       </c>
       <c r="C214" s="4" t="inlineStr">
@@ -7159,20 +7167,16 @@
       </c>
       <c r="D214" s="4" t="inlineStr">
         <is>
-          <t>Conectividad</t>
-        </is>
-      </c>
-      <c r="E214" s="5" t="inlineStr">
-        <is>
-          <t>Mosaloua iga internet</t>
-        </is>
-      </c>
-      <c r="F214" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G214" s="4" t="n"/>
+          <t>Polígono {n} · {d}</t>
+        </is>
+      </c>
+      <c r="E214" s="4" t="n"/>
+      <c r="F214" s="4" t="n"/>
+      <c r="G214" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="n">
@@ -7180,7 +7184,7 @@
       </c>
       <c r="B215" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (una localidad)</t>
         </is>
       </c>
       <c r="C215" s="4" t="inlineStr">
@@ -7190,12 +7194,12 @@
       </c>
       <c r="D215" s="4" t="inlineStr">
         <is>
-          <t>Una tarjeta WiFi por equipo e internet dedicado para el aula.</t>
+          <t>Marginación: {d}</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>Se tarjeta WiFi iga nochi tepostlapoualli uan internet san iga tlamachtiloyan.</t>
+          <t>Iknoyotl: {d}</t>
         </is>
       </c>
       <c r="F215" s="4" t="inlineStr">
@@ -7211,22 +7215,22 @@
       </c>
       <c r="B216" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (una localidad)</t>
         </is>
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
         <is>
-          <t>Acompañamiento</t>
+          <t>Close popup</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>Akin kinpaleuia</t>
+          <t>Xiktsagua</t>
         </is>
       </c>
       <c r="F216" s="4" t="inlineStr">
@@ -7242,7 +7246,7 @@
       </c>
       <c r="B217" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (localidad sin datos censales)</t>
         </is>
       </c>
       <c r="C217" s="4" t="inlineStr">
@@ -7252,12 +7256,12 @@
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>Un promotor capacitado en cada escuela para el uso del aula.</t>
+          <t>Coordenada capturada manualmente</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>Se tlapaleuiani tlen momachtij ipan nochi kaltlamachtiloyan iga ma motekiuti tlamachtiloyan.</t>
+          <t>Kanin katej, omojkuilo iga ma</t>
         </is>
       </c>
       <c r="F217" s="4" t="inlineStr">
@@ -7273,7 +7277,7 @@
       </c>
       <c r="B218" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (localidad sin datos censales)</t>
         </is>
       </c>
       <c r="C218" s="4" t="inlineStr">
@@ -7283,12 +7287,12 @@
       </c>
       <c r="D218" s="4" t="inlineStr">
         <is>
-          <t>Acercar tecnología a las escuelas es abrir oportunidades reales para las niñas y los niños, especialmente en zonas donde el acceso ha sido limitado.</t>
+          <t>Sin Datos Censales Disponibles</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
         <is>
-          <t>Tikitkiliskej tepostlapoualli ipan kaltlamachtiloyan kiijtosneki tiktlapoaj melauak ojmej iga pipiltontij, ogachi kanin amo asiaya.</t>
+          <t>Amo kipia itlapoual censo</t>
         </is>
       </c>
       <c r="F218" s="4" t="inlineStr">
@@ -7304,7 +7308,7 @@
       </c>
       <c r="B219" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (localidad sin datos censales)</t>
         </is>
       </c>
       <c r="C219" s="4" t="inlineStr">
@@ -7314,12 +7318,12 @@
       </c>
       <c r="D219" s="4" t="inlineStr">
         <is>
-          <t>, director de Agenda Digital de la ATDEM, durante una entrega en Jojutla.</t>
+          <t>No se encontró una coincidencia confiable para {d} en el Censo INEGI {n} (ITER Morelos). Esto ocurre principalmente con colonias/barrios urbanos que no se registran como localidad censal independiente. El mapa muestra su ubicación (coordenada capturada manualmente) dentro de polígono {n}.</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
         <is>
-          <t>, tlayekanki ipan Agenda Digital ATDEM, kuak kitemakak ipan Jojutla.</t>
+          <t>Amo omonexti {d} ipan Censo INEGI {n} (ITER Morelos). Nin panoa ogachi iga colonias o barrios ipan ueyi altepetl tlen amo motlapouaj kemej altepetsin. Tlalamatl kinextia kanin katej (omojkuilo iga ma) ipan polígono {n}.</t>
         </is>
       </c>
       <c r="F219" s="4" t="inlineStr">
@@ -7335,7 +7339,7 @@
       </c>
       <c r="B220" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (localidad sin datos censales)</t>
         </is>
       </c>
       <c r="C220" s="4" t="inlineStr">
@@ -7345,12 +7349,12 @@
       </c>
       <c r="D220" s="4" t="inlineStr">
         <is>
-          <t>Escuelas por nivel educativo</t>
+          <t>Población reportada (Lista TPBV {n})</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan iga temachtilistle</t>
+          <t>Tlatlaga tlen motlapoukej (Lista TPBV {n})</t>
         </is>
       </c>
       <c r="F220" s="4" t="inlineStr">
@@ -7366,7 +7370,7 @@
       </c>
       <c r="B221" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (filtro personalizado)</t>
         </is>
       </c>
       <c r="C221" s="4" t="inlineStr">
@@ -7376,12 +7380,12 @@
       </c>
       <c r="D221" s="4" t="inlineStr">
         <is>
-          <t>¿Dónde están las aulas?</t>
+          <t>Elige los polígonos a comparar</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
         <is>
-          <t>¿Kanin katej tlamachtiloyan?</t>
+          <t>Xikpepena polígono tlen tikinneneuilis</t>
         </is>
       </c>
       <c r="F221" s="4" t="inlineStr">
@@ -7397,7 +7401,7 @@
       </c>
       <c r="B222" s="4" t="inlineStr">
         <is>
-          <t>Aulas Tecnológicas</t>
+          <t>Análisis Demográfico (filtro personalizado)</t>
         </is>
       </c>
       <c r="C222" s="4" t="inlineStr">
@@ -7407,12 +7411,12 @@
       </c>
       <c r="D222" s="4" t="inlineStr">
         <is>
-          <t>Todos los municipios</t>
+          <t>Limpiar</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
         <is>
-          <t>Nochi altepemej</t>
+          <t>Xikpojpoa</t>
         </is>
       </c>
       <c r="F222" s="4" t="inlineStr">
@@ -7438,12 +7442,12 @@
       </c>
       <c r="D223" s="4" t="inlineStr">
         <is>
-          <t>Escuelas equipadas</t>
+          <t>Territorios de Paz y Buen Vivir · Educación digital</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan tlen kipiaj tepostlapoualli</t>
+          <t>Territorios de Paz y Buen Vivir · Temachtilistle iga tepostlapoualli</t>
         </is>
       </c>
       <c r="F223" s="4" t="inlineStr">
@@ -7469,12 +7473,12 @@
       </c>
       <c r="D224" s="4" t="inlineStr">
         <is>
-          <t>Computadoras</t>
+          <t>Para reducir la brecha digital desde edades tempranas, la Agencia de Transformación Digital del Estado de Morelos (ATDEM), en coordinación con la Secretaría de Educación y el Instituto de Educación Básica del Estado de Morelos (IEBEM), equipó aulas de cómputo en {n} escuelas de {n} municipios ubicadas en los polígonos de Territorios de Paz y Buen Vivir.</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
         <is>
-          <t>Tepostlapoualmej</t>
+          <t>Iga ma moyekchiua tlen amo kipiaj tepostlapoualli kuak tsitsikitsin, Agencia de Transformación Digital del Estado de Morelos (ATDEM), sepan iga Secretaría de Educación uan Instituto de Educación Básica del Estado de Morelos (IEBEM), kitlalij tepostlapoualli ipan {n} kaltlamachtiloyan ipan {n} altepemej tlen katej ipan polígono Territorios de Paz y Buen Vivir.</t>
         </is>
       </c>
       <c r="F224" s="4" t="inlineStr">
@@ -7500,12 +7504,12 @@
       </c>
       <c r="D225" s="4" t="inlineStr">
         <is>
-          <t>Escuelas dentro de un polígono</t>
+          <t>Con computadoras conectadas a internet y software educativo, niñas, niños y jóvenes fortalecen sus procesos de aprendizaje, desarrollan habilidades digitales y amplían sus oportunidades en entornos con mayor infraestructura tecnológica.</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan ipan se polígono</t>
+          <t>Iga tepostlapoualli tlen kipiaj internet uan programas iga temachtilistle, pipiltontij uan telpogamej ogachi kualtsin momachtiaj, kimachtiaj tepostlapoualli uan ogachi ojmej kipiaj.</t>
         </is>
       </c>
       <c r="F225" s="4" t="inlineStr">
@@ -7531,20 +7535,16 @@
       </c>
       <c r="D226" s="4" t="inlineStr">
         <is>
-          <t>Mapa de Aulas</t>
-        </is>
-      </c>
-      <c r="E226" s="5" t="inlineStr">
-        <is>
-          <t>Tlalamatl iga tlamachtiloyan</t>
-        </is>
-      </c>
-      <c r="F226" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G226" s="4" t="n"/>
+          <t>Secretaría de Educación</t>
+        </is>
+      </c>
+      <c r="E226" s="4" t="n"/>
+      <c r="F226" s="4" t="n"/>
+      <c r="G226" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="4" t="n">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="D227" s="4" t="inlineStr">
         <is>
-          <t>El tamaño del círculo indica el número de computadoras. Haz clic en una escuela para ver su detalle.</t>
+          <t>Instalación: diciembre {n} a enero {n}</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
         <is>
-          <t>Kenin ueyi yaualtik kinextia keski tepostlapoualli kipia. Xikpacho se kaltlamachtiloyan iga tikitas nochi.</t>
+          <t>Motlalij: peuak diciembre {n}, tlamik enero {n}</t>
         </is>
       </c>
       <c r="F227" s="4" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="D228" s="4" t="inlineStr">
         <is>
-          <t>Computadoras por aula</t>
+          <t>¿Qué incluye cada aula?</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
         <is>
-          <t>Tepostlapoualli ipan nochi tlamachtiloyan</t>
+          <t>¿Tlen kipia nochi tlamachtiloyan?</t>
         </is>
       </c>
       <c r="F228" s="4" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="D229" s="4" t="inlineStr">
         <is>
-          <t>Municipio con aula</t>
+          <t>Equipo de cómputo</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
         <is>
-          <t>Altepetl iga tlamachtiloyan</t>
+          <t>Tepostlapoualli</t>
         </is>
       </c>
       <c r="F229" s="4" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="D230" s="4" t="inlineStr">
         <is>
-          <t>Otros municipios</t>
+          <t>{n} computadoras con conexión a internet y software educativo.</t>
         </is>
       </c>
       <c r="E230" s="5" t="inlineStr">
         <is>
-          <t>Siguin altepemej</t>
+          <t>{n} tepostlapoualli iga internet uan programas iga temachtilistle.</t>
         </is>
       </c>
       <c r="F230" s="4" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="D231" s="4" t="inlineStr">
         <is>
-          <t>Equipos por Municipio</t>
+          <t>Mobiliario</t>
         </is>
       </c>
       <c r="E231" s="5" t="inlineStr">
         <is>
-          <t>Tepostlapoualli iga altepetl</t>
+          <t>Ikpalmej uan tlapechmej</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="D232" s="4" t="inlineStr">
         <is>
-          <t>{n} eq. · {n} esc.</t>
+          <t>{n} sillas y {n} mesas para las aulas que no contaban con mobiliario suficiente.</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
         <is>
-          <t>{n} tep. · {n} kal.</t>
+          <t>{n} ikpalmej uan {n} tlapechmej iga tlamachtiloyan tlen amo kipiayaj.</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="D233" s="4" t="inlineStr">
         <is>
-          <t>Escuelas</t>
+          <t>Conectividad</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan</t>
+          <t>Mosaloua iga internet</t>
         </is>
       </c>
       <c r="F233" s="4" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="D234" s="4" t="inlineStr">
         <is>
-          <t>Escuela</t>
+          <t>Una tarjeta WiFi por equipo e internet dedicado para el aula.</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan</t>
+          <t>Se tarjeta WiFi iga nochi tepostlapoualli uan internet san iga tlamachtiloyan.</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="D235" s="4" t="inlineStr">
         <is>
-          <t>Equipos</t>
+          <t>Acompañamiento</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
         <is>
-          <t>Tepostlapoualmej</t>
+          <t>Akin kinpaleuia</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
@@ -7836,17 +7836,17 @@
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
         <is>
-          <t>Ver {d} en el mapa</t>
+          <t>Un promotor capacitado en cada escuela para el uso del aula.</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
         <is>
-          <t>Xikita {d} ipan tlalamatl</t>
+          <t>Se tlapaleuiani tlen momachtij ipan nochi kaltlamachtiloyan iga ma motekiuti tlamachtiloyan.</t>
         </is>
       </c>
       <c r="F236" s="4" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, "Proyecto Escuelas entrega Computadoras" (hoja Concentrado). Ubicación según el enlace de Google Maps capturado por escuela.</t>
+          <t>Acercar tecnología a las escuelas es abrir oportunidades reales para las niñas y los niños, especialmente en zonas donde el acceso ha sido limitado.</t>
         </is>
       </c>
       <c r="E237" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, "Proyecto Escuelas entrega Computadoras" (hoja Concentrado). Kanin katej iga ojtle Google Maps tlen motlalij iga nochi kaltlamachtiloyan.</t>
+          <t>Tikitkiliskej tepostlapoualli ipan kaltlamachtiloyan kiijtosneki tiktlapoaj melauak ojmej iga pipiltontij, ogachi kanin amo asiaya.</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
@@ -7893,7 +7893,7 @@
       </c>
       <c r="B238" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C238" s="4" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>Conectividad pública · Agencia de Transformación Digital</t>
+          <t>, director de Agenda Digital de la ATDEM, durante una entrega en Jojutla.</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
-          <t>Matlatl tlapojtok · Agencia de Transformación Digital</t>
+          <t>, tlayekanki ipan Agenda Digital ATDEM, kuak kitemakak ipan Jojutla.</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="B239" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C239" s="4" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>Red de Wi-Fi pública, gratuita y abierta impulsada por la Agencia de Transformación Digital del Gobierno del Estado de Morelos (ATDEM). Busca reducir la brecha digital y que la ciudadanía pueda comunicarse sin costo, consultar la programación cultural, realizar trámites y acceder a las plataformas digitales institucionales.</t>
+          <t>Escuelas por nivel educativo</t>
         </is>
       </c>
       <c r="E239" s="5" t="inlineStr">
         <is>
-          <t>Matlatl Wi-Fi tlen nochi ueli kitekiutiskej, amo iga tomin uan tlapojtok, tlen kichiua Agencia de Transformación Digital ipan Kaltlayekana ipan Morelos (ATDEM). Guinegui ma moyekchiua tlen amo kipiaj internet uan ma tlatlaga ueliskej monotsaskej amo iga tomin, kitaskej iljuimej, kichiuaskej trámites uan kalakiskej ipan plataformas digitales iga Kaltlayekana.</t>
+          <t>Kaltlamachtiloyan iga temachtilistle</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="B240" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C240" s="4" t="inlineStr">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>Internet gratuito y abierto</t>
+          <t>¿Dónde están las aulas?</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>Internet amo iga tomin uan tlapojtok</t>
+          <t>¿Kanin katej tlamachtiloyan?</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="B241" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C241" s="4" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>Conexión Wi-Fi sin costo para la ciudadanía en espacios públicos y oficinas de gobierno.</t>
+          <t>Todos los municipios</t>
         </is>
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
-          <t>Matlatl Wi-Fi amo iga tomin iga tlatlaga kanin nochi monechikouaj uan ipan teguichiualoyan iga Kaltlayekana.</t>
+          <t>Nochi altepemej</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="B242" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C242" s="4" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>Reducir la brecha digital</t>
+          <t>Escuelas equipadas</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>Moyekchiuas tlen amo kipiaj internet</t>
+          <t>Kaltlamachtiloyan tlen kipiaj tepostlapoualli</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="B243" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C243" s="4" t="inlineStr">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>Comunicarse sin costo, consultar programación cultural y realizar trámites en plataformas digitales institucionales.</t>
+          <t>Computadoras</t>
         </is>
       </c>
       <c r="E243" s="5" t="inlineStr">
         <is>
-          <t>Monotsaskej amo iga tomin, kitaskej iljuimej uan kichiuaskej trámites ipan plataformas digitales iga Kaltlayekana.</t>
+          <t>Tepostlapoualmej</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="B244" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C244" s="4" t="inlineStr">
@@ -8089,12 +8089,12 @@
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>Puntos de conexión</t>
+          <t>Escuelas dentro de un polígono</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
         <is>
-          <t>Kanin mosaloua</t>
+          <t>Kaltlamachtiloyan ipan se polígono</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="B245" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C245" s="4" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>Plazas públicas y espacios de alta concurrencia, como la Plaza de Armas Emiliano Zapata (Zócalo de Cuernavaca).</t>
+          <t>Mapa de Aulas</t>
         </is>
       </c>
       <c r="E245" s="5" t="inlineStr">
         <is>
-          <t>Plazas uan kanin miak tlatlaga monechikouaj, ken Plaza de Armas Emiliano Zapata (Zócalo de Cuernavaca).</t>
+          <t>Tlalamatl iga tlamachtiloyan</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="B246" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C246" s="4" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>Eventos especiales, como el Festival Internacional Cervantino en Cuernavaca.</t>
+          <t>El tamaño del círculo indica el número de computadoras. Haz clic en una escuela para ver su detalle.</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>Iljuimej, ken Festival Internacional Cervantino ipan Cuernavaca.</t>
+          <t>Kenin ueyi yaualtik kinextia keski tepostlapoualli kipia. Xikpacho se kaltlamachtiloyan iga tikitas nochi.</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="B247" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C247" s="4" t="inlineStr">
@@ -8182,12 +8182,12 @@
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>Dependencias estatales, ayudantías municipales y escuelas.</t>
+          <t>Computadoras por aula</t>
         </is>
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>Teguichiualoyan iga Kaltlayekana, ayudantías ipan altepemej uan kaltlamachtiloyan.</t>
+          <t>Tepostlapoualli ipan nochi tlamachtiloyan</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="B248" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C248" s="4" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>Dependencias con red</t>
+          <t>Municipio con aula</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>Teguichiualoyan iga matlatl</t>
+          <t>Altepetl iga tlamachtiloyan</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="B249" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C249" s="4" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>Secretarías y órganos</t>
+          <t>Otros municipios</t>
         </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
-          <t>Secretarías uan teguichiualoyan</t>
+          <t>Siguin altepemej</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="B250" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C250" s="4" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>Sedes conectadas</t>
+          <t>Equipos por Municipio</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>Kalmej tlen mosalojtokej</t>
+          <t>Tepostlapoualli iga altepetl</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="B251" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C251" s="4" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>Puntos de acceso</t>
+          <t>{n} eq. · {n} esc.</t>
         </is>
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>Kanin mosaloua</t>
+          <t>{n} tep. · {n} kal.</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="B252" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C252" s="4" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>Mapa de la red</t>
+          <t>Escuelas</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>Tlalamatl iga matlatl</t>
+          <t>Kaltlamachtiloyan</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="B253" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C253" s="4" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>Sede con red (el tamaño indica cuántas dependencias)</t>
+          <t>Escuela</t>
         </is>
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
-          <t>Kalle iga matlatl (kenin ueyi kinextia keski teguichiualoyan)</t>
+          <t>Kaltlamachtiloyan</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="B254" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C254" s="4" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>Dependencias por secretaría</t>
+          <t>Equipos</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>Teguichiualoyan iga secretaría</t>
+          <t>Tepostlapoualmej</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
@@ -8420,22 +8420,22 @@
       </c>
       <c r="B255" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>{n} puntos de acceso</t>
+          <t>Ver {d} en el mapa</t>
         </is>
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
-          <t>{n} kanin mosaloua</t>
+          <t>Xikita {d} ipan tlalamatl</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="B256" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C256" s="4" t="inlineStr">
@@ -8461,16 +8461,20 @@
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>Jefatura de la Oficina de la Gubernatura</t>
-        </is>
-      </c>
-      <c r="E256" s="4" t="n"/>
-      <c r="F256" s="4" t="n"/>
-      <c r="G256" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Fuente: ATDEM, "Proyecto Escuelas entrega Computadoras" (hoja Concentrado). Ubicación según el enlace de Google Maps capturado por escuela.</t>
+        </is>
+      </c>
+      <c r="E256" s="5" t="inlineStr">
+        <is>
+          <t>Kanin eua: ATDEM, "Proyecto Escuelas entrega Computadoras" (hoja Concentrado). Kanin katej iga ojtle Google Maps tlen motlalij iga nochi kaltlamachtiloyan.</t>
+        </is>
+      </c>
+      <c r="F256" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G256" s="4" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="n">
@@ -8488,12 +8492,12 @@
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>{n} punto de acceso</t>
+          <t>Conectividad pública · Agencia de Transformación Digital</t>
         </is>
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
-          <t>{n} kanin mosaloua</t>
+          <t>Matlatl tlapojtok · Agencia de Transformación Digital</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
@@ -8519,12 +8523,12 @@
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, "Agentes_dependencias La Tierra Que Nos Une" (dependencias con red La tierra que nos une). Puntos de acceso según el registro de la ATDEM; algunas dependencias no tienen el dato capturado.</t>
+          <t>Red de Wi-Fi pública, gratuita y abierta impulsada por la Agencia de Transformación Digital del Gobierno del Estado de Morelos (ATDEM). Busca reducir la brecha digital y que la ciudadanía pueda comunicarse sin costo, consultar la programación cultural, realizar trámites y acceder a las plataformas digitales institucionales.</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, "Agentes_dependencias La Tierra Que Nos Une" (teguichiualoyan iga matlatl Nin tlale tech sepaneloa). Kanin mosaloua ken kijkuiloj ATDEM; siguin teguichiualoyan amo kipiaj nin tlapoualli.</t>
+          <t>Matlatl Wi-Fi tlen nochi ueli kitekiutiskej, amo iga tomin uan tlapojtok, tlen kichiua Agencia de Transformación Digital ipan Kaltlayekana ipan Morelos (ATDEM). Guinegui ma moyekchiua tlen amo kipiaj internet uan ma tlatlaga ueliskej monotsaskej amo iga tomin, kitaskej iljuimej, kichiuaskej trámites uan kalakiskej ipan plataformas digitales iga Kaltlayekana.</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
@@ -8540,7 +8544,7 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
@@ -8550,12 +8554,12 @@
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>Conectividad · Agencia de Transformación Digital</t>
+          <t>Internet gratuito y abierto</t>
         </is>
       </c>
       <c r="E259" s="5" t="inlineStr">
         <is>
-          <t>Mosaloua · Agencia de Transformación Digital</t>
+          <t>Internet amo iga tomin uan tlapojtok</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
@@ -8571,7 +8575,7 @@
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
@@ -8581,12 +8585,12 @@
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>Sitios y torres de telecomunicaciones de la red estatal (sitios REEM) que dan servicio a dependencias del Gobierno del Estado, planteles educativos, unidades de salud e instalaciones de seguridad en Morelos.</t>
+          <t>Conexión Wi-Fi sin costo para la ciudadanía en espacios públicos y oficinas de gobierno.</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>Sitios uan tepostlaketsalmej iga uejka tlanonotsalistle ipan imatlau Kaltlayekana (sitios REEM) tlen kinpaleuiaj teguichiualoyan iga Kaltlayekana, kaltlamachtiloyan, pajtiloyan uan kanin tlajpiaj ipan Morelos.</t>
+          <t>Matlatl Wi-Fi amo iga tomin iga tlatlaga kanin nochi monechikouaj uan ipan teguichiualoyan iga Kaltlayekana.</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
@@ -8602,7 +8606,7 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
@@ -8612,12 +8616,12 @@
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>Por seguridad de la infraestructura, la información se presenta agregada por municipio y sector. No se publica la ubicación exacta ni el nombre de los sitios.</t>
+          <t>Reducir la brecha digital</t>
         </is>
       </c>
       <c r="E261" s="5" t="inlineStr">
         <is>
-          <t>Iga tlajpialistle, tlamachilistle monextia sepan iga altepetl uan teguitl. Amo monextia kanin melauak katej nin intogayo sitios.</t>
+          <t>Moyekchiuas tlen amo kipiaj internet</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
@@ -8633,7 +8637,7 @@
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
@@ -8643,12 +8647,12 @@
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>Sitios de telecomunicaciones</t>
+          <t>Comunicarse sin costo, consultar programación cultural y realizar trámites en plataformas digitales institucionales.</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>Sitios iga uejka tlanonotsalistle</t>
+          <t>Monotsaskej amo iga tomin, kitaskej iljuimej uan kichiuaskej trámites ipan plataformas digitales iga Kaltlayekana.</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
@@ -8664,7 +8668,7 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
@@ -8674,12 +8678,12 @@
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>Municipios con sitios</t>
+          <t>Puntos de conexión</t>
         </is>
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
-          <t>Altepemej iga sitios</t>
+          <t>Kanin mosaloua</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
@@ -8695,7 +8699,7 @@
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
@@ -8705,12 +8709,12 @@
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>Sectores atendidos</t>
+          <t>Plazas públicas y espacios de alta concurrencia, como la Plaza de Armas Emiliano Zapata (Zócalo de Cuernavaca).</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>Teguimej tlen kinpaleuiaj</t>
+          <t>Plazas uan kanin miak tlatlaga monechikouaj, ken Plaza de Armas Emiliano Zapata (Zócalo de Cuernavaca).</t>
         </is>
       </c>
       <c r="F264" s="4" t="inlineStr">
@@ -8726,7 +8730,7 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
@@ -8736,12 +8740,12 @@
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>Mayor concentración ({n} sitios)</t>
+          <t>Eventos especiales, como el Festival Internacional Cervantino en Cuernavaca.</t>
         </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
-          <t>Kanin ogachi miak ({n} sitios)</t>
+          <t>Iljuimej, ken Festival Internacional Cervantino ipan Cuernavaca.</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
@@ -8757,7 +8761,7 @@
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
@@ -8767,12 +8771,12 @@
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>Sitios por municipio</t>
+          <t>Dependencias estatales, ayudantías municipales y escuelas.</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>Sitios iga altepetl</t>
+          <t>Teguichiualoyan iga Kaltlayekana, ayudantías ipan altepemej uan kaltlamachtiloyan.</t>
         </is>
       </c>
       <c r="F266" s="4" t="inlineStr">
@@ -8788,7 +8792,7 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
@@ -8798,12 +8802,12 @@
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>Pasa el cursor sobre un municipio para ver el desglose por sector.</t>
+          <t>Dependencias con red</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
         <is>
-          <t>Xikpano tepostlapacholi ipan se altepetl iga tikitas tlen kipia iga teguitl.</t>
+          <t>Teguichiualoyan iga matlatl</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
@@ -8819,7 +8823,7 @@
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
@@ -8829,12 +8833,12 @@
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>{n} o más</t>
+          <t>Secretarías y órganos</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>{n} o ogachi</t>
+          <t>Secretarías uan teguichiualoyan</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
@@ -8850,7 +8854,7 @@
       </c>
       <c r="B269" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C269" s="4" t="inlineStr">
@@ -8860,12 +8864,12 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>Sin sitios</t>
+          <t>Sedes conectadas</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>Amo kipia sitios</t>
+          <t>Kalmej tlen mosalojtokej</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
@@ -8881,7 +8885,7 @@
       </c>
       <c r="B270" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C270" s="4" t="inlineStr">
@@ -8891,12 +8895,12 @@
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>Sitios por sector</t>
+          <t>Puntos de acceso</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>Sitios iga teguitl</t>
+          <t>Kanin mosaloua</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
@@ -8912,7 +8916,7 @@
       </c>
       <c r="B271" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C271" s="4" t="inlineStr">
@@ -8922,12 +8926,12 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>Gobierno del Estado</t>
+          <t>Mapa de la red</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>Kaltlayekana</t>
+          <t>Tlalamatl iga matlatl</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
@@ -8943,7 +8947,7 @@
       </c>
       <c r="B272" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C272" s="4" t="inlineStr">
@@ -8953,12 +8957,12 @@
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Sede con red (el tamaño indica cuántas dependencias)</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>Pajtilistle</t>
+          <t>Kalle iga matlatl (kenin ueyi kinextia keski teguichiualoyan)</t>
         </is>
       </c>
       <c r="F272" s="4" t="inlineStr">
@@ -8974,7 +8978,7 @@
       </c>
       <c r="B273" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C273" s="4" t="inlineStr">
@@ -8984,12 +8988,12 @@
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>Seguridad y Protección Ciudadana</t>
+          <t>Dependencias por secretaría</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
-          <t>Tlajpialistle uan Tlapaleuilistle iga Tlatlaga</t>
+          <t>Teguichiualoyan iga secretaría</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
@@ -9005,7 +9009,7 @@
       </c>
       <c r="B274" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C274" s="4" t="inlineStr">
@@ -9015,12 +9019,12 @@
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>Municipios con infraestructura</t>
+          <t>{n} puntos de acceso</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>Altepemej iga tepostlaketsalmej</t>
+          <t>{n} kanin mosaloua</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
@@ -9036,7 +9040,7 @@
       </c>
       <c r="B275" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C275" s="4" t="inlineStr">
@@ -9046,20 +9050,16 @@
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>Sectores</t>
-        </is>
-      </c>
-      <c r="E275" s="5" t="inlineStr">
-        <is>
-          <t>Teguimej</t>
-        </is>
-      </c>
-      <c r="F275" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G275" s="4" t="n"/>
+          <t>Jefatura de la Oficina de la Gubernatura</t>
+        </is>
+      </c>
+      <c r="E275" s="4" t="n"/>
+      <c r="F275" s="4" t="n"/>
+      <c r="G275" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="4" t="n">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="B276" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C276" s="4" t="inlineStr">
@@ -9077,12 +9077,12 @@
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>Sitios</t>
+          <t>{n} punto de acceso</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>Sitios</t>
+          <t>{n} kanin mosaloua</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="B277" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C277" s="4" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>Gobierno del Estado · {n}</t>
+          <t>Fuente: ATDEM, "Agentes_dependencias La Tierra Que Nos Une" (dependencias con red La tierra que nos une). Puntos de acceso según el registro de la ATDEM; algunas dependencias no tienen el dato capturado.</t>
         </is>
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
-          <t>Kaltlayekana · {n}</t>
+          <t>Kanin eua: ATDEM, "Agentes_dependencias La Tierra Que Nos Une" (teguichiualoyan iga matlatl Nin tlale tech sepaneloa). Kanin mosaloua ken kijkuiloj ATDEM; siguin teguichiualoyan amo kipiaj nin tlapoualli.</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
@@ -9139,12 +9139,12 @@
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>Salud · {n}</t>
+          <t>Conectividad · Agencia de Transformación Digital</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>Pajtilistle · {n}</t>
+          <t>Mosaloua · Agencia de Transformación Digital</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
@@ -9170,12 +9170,12 @@
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>Educación · {n}</t>
+          <t>Sitios y torres de telecomunicaciones de la red estatal (sitios REEM) que dan servicio a dependencias del Gobierno del Estado, planteles educativos, unidades de salud e instalaciones de seguridad en Morelos.</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>Temachtilistle · {n}</t>
+          <t>Sitios uan tepostlaketsalmej iga uejka tlanonotsalistle ipan imatlau Kaltlayekana (sitios REEM) tlen kinpaleuiaj teguichiualoyan iga Kaltlayekana, kaltlamachtiloyan, pajtiloyan uan kanin tlajpiaj ipan Morelos.</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>Seguridad y Protección Ciudadana · {n}</t>
+          <t>Por seguridad de la infraestructura, la información se presenta agregada por municipio y sector. No se publica la ubicación exacta ni el nombre de los sitios.</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>Tlajpialistle uan Tlapaleuilistle iga Tlatlaga · {n}</t>
+          <t>Iga tlajpialistle, tlamachilistle monextia sepan iga altepetl uan teguitl. Amo monextia kanin melauak katej nin intogayo sitios.</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, registro de sitios REEM. Municipio asignado con los límites municipales del INE.</t>
+          <t>Sitios de telecomunicaciones</t>
         </is>
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, sitios REEM. Altepetl motlalij iga itlalxelol altepemej tlen INE.</t>
+          <t>Sitios iga uejka tlanonotsalistle</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>Territorios de Paz y Buen Vivir · Transparencia</t>
+          <t>Municipios con sitios</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>Territorios de Paz y Buen Vivir · Tlen nochi ueli kitaskej</t>
+          <t>Altepemej iga sitios</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>Descarga las bases de datos que alimentan este tablero. Cada conjunto está disponible en CSV, para abrirlo en Excel o cualquier herramienta de análisis, y en KML, para verlo en Google Earth o Google My Maps.</t>
+          <t>Sectores atendidos</t>
         </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga tlapoualli tlen kitekiutia nin tablero. Nochi kipia CSV, iga tiktlapos ipan Excel o siguin programa, uan KML, iga tikitas ipan Google Earth o Google My Maps.</t>
+          <t>Teguimej tlen kinpaleuiaj</t>
         </is>
       </c>
       <c r="F283" s="4" t="inlineStr">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>{n} conjuntos de datos</t>
+          <t>Mayor concentración ({n} sitios)</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>{n} tlapoualamatl</t>
+          <t>Kanin ogachi miak ({n} sitios)</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
@@ -9356,12 +9356,12 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>CSV · UTF-{n}, separado por comas</t>
+          <t>Sitios por municipio</t>
         </is>
       </c>
       <c r="E285" s="5" t="inlineStr">
         <is>
-          <t>CSV · UTF-{n}, xeloltok iga comas</t>
+          <t>Sitios iga altepetl</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
@@ -9377,7 +9377,7 @@
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
@@ -9387,12 +9387,12 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>KML · una sola capa</t>
+          <t>Pasa el cursor sobre un municipio para ver el desglose por sector.</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>KML · san se tlapachtli</t>
+          <t>Xikpano tepostlapacholi ipan se altepetl iga tikitas tlen kipia iga teguitl.</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
@@ -9418,12 +9418,12 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>Localidades · Propuesta Actual</t>
+          <t>{n} o más</t>
         </is>
       </c>
       <c r="E287" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin · Tlen axan</t>
+          <t>{n} o ogachi</t>
         </is>
       </c>
       <c r="F287" s="4" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
@@ -9449,12 +9449,12 @@
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>{n} registros · {n} campos</t>
+          <t>Sin sitios</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>{n} tlajkuilolli · {n} tlamachilistle</t>
+          <t>Amo kipia sitios</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>Las localidades de los {n} polígonos vigentes con sus indicadores de población, vivienda, salud, educación, economía y marginación.</t>
+          <t>Sitios por sector</t>
         </is>
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin tlen {n} polígono tlen axan iga itlapoual tlatlaga, kalmej, pajtilistle, temachtilistle, tomin uan iknoyotl.</t>
+          <t>Sitios iga teguitl</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
@@ -9511,12 +9511,12 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>Fuente: INEGI, Censo {n} (ITER Morelos) y Lista de Comunidades TPBV {n}</t>
+          <t>Gobierno del Estado</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: INEGI, Censo {n} (ITER Morelos) uan Lista de Comunidades TPBV {n}</t>
+          <t>Kaltlayekana</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
@@ -9542,12 +9542,12 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>Ver campos</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>Xikita tlen kipia</t>
+          <t>Pajtilistle</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
@@ -9563,22 +9563,22 @@
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>Descargar Localidades · Propuesta Actual en CSV</t>
+          <t>Seguridad y Protección Ciudadana</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Altepetsitsin · Tlen axan ipan CSV</t>
+          <t>Tlajpialistle uan Tlapaleuilistle iga Tlatlaga</t>
         </is>
       </c>
       <c r="F292" s="4" t="inlineStr">
@@ -9594,22 +9594,22 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>Descargar Localidades · Propuesta Actual en KML</t>
+          <t>Municipios con infraestructura</t>
         </is>
       </c>
       <c r="E293" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Altepetsitsin · Tlen axan ipan KML</t>
+          <t>Altepemej iga tepostlaketsalmej</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>Polígonos · Propuesta Actual</t>
+          <t>Sectores</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>Polígono · Tlen axan</t>
+          <t>Teguimej</t>
         </is>
       </c>
       <c r="F294" s="4" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>Contorno de los {n} polígonos vigentes de Territorios de Paz y Buen Vivir, con número de localidades y población.</t>
+          <t>Sitios</t>
         </is>
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>Itlalxelol {n} polígono tlen axan ipan Territorios de Paz y Buen Vivir, iga keski altepetsitsin uan tlatlaga.</t>
+          <t>Sitios</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
@@ -9697,12 +9697,12 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>Fuente: TPBV {n}.geojson</t>
+          <t>Gobierno del Estado · {n}</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: TPBV {n}.geojson</t>
+          <t>Kaltlayekana · {n}</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
@@ -9718,22 +9718,22 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>Descargar Polígonos · Propuesta Actual en CSV</t>
+          <t>Salud · {n}</t>
         </is>
       </c>
       <c r="E297" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Polígono · Tlen axan ipan CSV</t>
+          <t>Pajtilistle · {n}</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
@@ -9749,22 +9749,22 @@
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>Descargar Polígonos · Propuesta Actual en KML</t>
+          <t>Educación · {n}</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Polígono · Tlen axan ipan KML</t>
+          <t>Temachtilistle · {n}</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>Escuelas donde ATDEM instaló aulas de cómputo: CCT, nivel, computadoras, fecha de instalación y polígono TPBV.</t>
+          <t>Seguridad y Protección Ciudadana · {n}</t>
         </is>
       </c>
       <c r="E299" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan kanin ATDEM kitlalij tepostlapoualli: CCT, temachtilistle, tepostlapoualmej, kemanian motlalij uan polígono TPBV.</t>
+          <t>Tlajpialistle uan Tlapaleuilistle iga Tlatlaga · {n}</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, Proyecto Escuelas entrega Computadoras</t>
+          <t>Fuente: ATDEM, registro de sitios REEM. Municipio asignado con los límites municipales del INE.</t>
         </is>
       </c>
       <c r="E300" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, Proyecto Escuelas entrega Computadoras</t>
+          <t>Kanin eua: ATDEM, sitios REEM. Altepetl motlalij iga itlalxelol altepemej tlen INE.</t>
         </is>
       </c>
       <c r="F300" s="4" t="inlineStr">
@@ -9847,17 +9847,17 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>Descargar Aulas Tecnológicas en CSV</t>
+          <t>Territorios de Paz y Buen Vivir · Transparencia</t>
         </is>
       </c>
       <c r="E301" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Tlamachtiloyan iga tepostlapoualli ipan CSV</t>
+          <t>Territorios de Paz y Buen Vivir · Tlen nochi ueli kitaskej</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
@@ -9878,17 +9878,17 @@
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>Descargar Aulas Tecnológicas en KML</t>
+          <t>Descarga las bases de datos que alimentan este tablero. Cada conjunto está disponible en CSV, para abrirlo en Excel o cualquier herramienta de análisis, y en KML, para verlo en Google Earth o Google My Maps.</t>
         </is>
       </c>
       <c r="E302" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Tlamachtiloyan iga tepostlapoualli ipan KML</t>
+          <t>Xikuiga tlapoualli tlen kitekiutia nin tablero. Nochi kipia CSV, iga tiktlapos ipan Excel o siguin programa, uan KML, iga tikitas ipan Google Earth o Google My Maps.</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>Dependencias estatales con la red Wi-Fi pública de la ATDEM: secretaría, sede, coordenadas y puntos de acceso.</t>
+          <t>{n} conjuntos de datos</t>
         </is>
       </c>
       <c r="E303" s="5" t="inlineStr">
         <is>
-          <t>Teguichiualoyan iga Kaltlayekana tlen kipiaj matlatl Wi-Fi tlen ATDEM: secretaría, kalle, kanin katej uan kanin mosaloua.</t>
+          <t>{n} tlapoualamatl</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
@@ -9945,12 +9945,12 @@
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, Agentes_dependencias La Tierra Que Nos Une</t>
+          <t>CSV · UTF-{n}, separado por comas</t>
         </is>
       </c>
       <c r="E304" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, Agentes_dependencias La Tierra Que Nos Une</t>
+          <t>CSV · UTF-{n}, xeloltok iga comas</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
@@ -9971,17 +9971,17 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>Descargar Red La tierra que nos une en CSV</t>
+          <t>KML · una sola capa</t>
         </is>
       </c>
       <c r="E305" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Matlatl Nin tlale tech sepaneloa ipan CSV</t>
+          <t>KML · san se tlapachtli</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
@@ -10002,17 +10002,17 @@
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>Descargar Red La tierra que nos une en KML</t>
+          <t>Localidades · Propuesta Actual</t>
         </is>
       </c>
       <c r="E306" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Matlatl Nin tlale tech sepaneloa ipan KML</t>
+          <t>Altepetsitsin · Tlen axan</t>
         </is>
       </c>
       <c r="F306" s="4" t="inlineStr">
@@ -10038,12 +10038,12 @@
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>Límites municipales de Morelos</t>
+          <t>{n} registros · {n} campos</t>
         </is>
       </c>
       <c r="E307" s="5" t="inlineStr">
         <is>
-          <t>Itlalxelol altepemej ipan Morelos</t>
+          <t>{n} tlajkuilolli · {n} tlamachilistle</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr">
@@ -10069,12 +10069,12 @@
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>Contorno de los {n} municipios del estado, con clave geoestadística (CVEGEO) y nombre.</t>
+          <t>Las localidades de los {n} polígonos vigentes con sus indicadores de población, vivienda, salud, educación, economía y marginación.</t>
         </is>
       </c>
       <c r="E308" s="5" t="inlineStr">
         <is>
-          <t>Itlalxelol {n} altepemej, iga iclave geoestadística (CVEGEO) uan itoga.</t>
+          <t>Altepetsitsin tlen {n} polígono tlen axan iga itlapoual tlatlaga, kalmej, pajtilistle, temachtilistle, tomin uan iknoyotl.</t>
         </is>
       </c>
       <c r="F308" s="4" t="inlineStr">
@@ -10100,12 +10100,12 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>Fuente: INE, límites municipales</t>
+          <t>Fuente: INEGI, Censo {n} (ITER Morelos) y Lista de Comunidades TPBV {n}</t>
         </is>
       </c>
       <c r="E309" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: INE, itlalxelol altepemej</t>
+          <t>Kanin eua: INEGI, Censo {n} (ITER Morelos) uan Lista de Comunidades TPBV {n}</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
@@ -10126,17 +10126,17 @@
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>Descargar Límites municipales de Morelos en CSV</t>
+          <t>Ver campos</t>
         </is>
       </c>
       <c r="E310" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Itlalxelol altepemej ipan Morelos ipan CSV</t>
+          <t>Xikita tlen kipia</t>
         </is>
       </c>
       <c r="F310" s="4" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>Descargar Límites municipales de Morelos en KML</t>
+          <t>Descargar Localidades · Propuesta Actual en CSV</t>
         </is>
       </c>
       <c r="E311" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Itlalxelol altepemej ipan Morelos ipan KML</t>
+          <t>Xikuiga Altepetsitsin · Tlen axan ipan CSV</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
@@ -10188,17 +10188,17 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>Los archivos se generan en tu navegador con la misma información que muestra el tablero. Para Google My Maps importa el KML en una capa nueva y usa "Aplicar estilo por columna de datos" para colorear por municipio, polígono u otro campo.</t>
+          <t>Descargar Localidades · Propuesta Actual en KML</t>
         </is>
       </c>
       <c r="E312" s="5" t="inlineStr">
         <is>
-          <t>Nin amatl mochiua ipan motepostlapoual iga nochi tlamachilistle tlen kinextia nin tablero. Iga Google My Maps, xikalaki KML ipan se yankuik tlapachtli uan xiktekiuti "Aplicar estilo por columna de datos" iga tiktlapaluis iga altepetl, polígono o siguin.</t>
+          <t>Xikuiga Altepetsitsin · Tlen axan ipan KML</t>
         </is>
       </c>
       <c r="F312" s="4" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Inicio (buscador de comunidades)</t>
+          <t>Datos Abiertos</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>No encontramos «{d}» entre las {n} comunidades del programa. Revisa cómo está escrito o busca por municipio.</t>
+          <t>Polígonos · Propuesta Actual</t>
         </is>
       </c>
       <c r="E313" s="5" t="inlineStr">
         <is>
-          <t>Amo otikajsike «{d}» ipan {n} altepetsitsin tlen nin tlapaleuilistle. Xiktlachili kenin otiktlajkuilo o xiktemo iga altepetl.</t>
+          <t>Polígono · Tlen axan</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>Inicio (buscador de comunidades)</t>
+          <t>Datos Abiertos</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>{d} tiene {n} comunidad en el programa.</t>
+          <t>Contorno de los {n} polígonos vigentes de Territorios de Paz y Buen Vivir, con número de localidades y población.</t>
         </is>
       </c>
       <c r="E314" s="5" t="inlineStr">
         <is>
-          <t>{d} kipia {n} altepetsin ipan nin tlapaleuilistle.</t>
+          <t>Itlalxelol {n} polígono tlen axan ipan Territorios de Paz y Buen Vivir, iga keski altepetsitsin uan tlatlaga.</t>
         </is>
       </c>
       <c r="F314" s="4" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>Inicio (buscador de comunidades)</t>
+          <t>Datos Abiertos</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>Y {n} comunidad más. Escribe más letras para afinar la búsqueda.</t>
+          <t>Fuente: TPBV {n}.geojson</t>
         </is>
       </c>
       <c r="E315" s="5" t="inlineStr">
         <is>
-          <t>Uan ogachi {n} altepetsin. Xiktlajkuilo ogachi tlajkuilolli iga tiktemos kuale.</t>
+          <t>Kanin eua: TPBV {n}.geojson</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
@@ -10307,33 +10307,622 @@
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C316" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D316" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Polígonos · Propuesta Actual en CSV</t>
+        </is>
+      </c>
+      <c r="E316" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Polígono · Tlen axan ipan CSV</t>
+        </is>
+      </c>
+      <c r="F316" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G316" s="4" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="4" t="n">
+        <v>316</v>
+      </c>
+      <c r="B317" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C317" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D317" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Polígonos · Propuesta Actual en KML</t>
+        </is>
+      </c>
+      <c r="E317" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Polígono · Tlen axan ipan KML</t>
+        </is>
+      </c>
+      <c r="F317" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G317" s="4" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="4" t="n">
+        <v>317</v>
+      </c>
+      <c r="B318" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C318" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D318" s="4" t="inlineStr">
+        <is>
+          <t>Escuelas donde ATDEM instaló aulas de cómputo: CCT, nivel, computadoras, fecha de instalación y polígono TPBV.</t>
+        </is>
+      </c>
+      <c r="E318" s="5" t="inlineStr">
+        <is>
+          <t>Kaltlamachtiloyan kanin ATDEM kitlalij tepostlapoualli: CCT, temachtilistle, tepostlapoualmej, kemanian motlalij uan polígono TPBV.</t>
+        </is>
+      </c>
+      <c r="F318" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G318" s="4" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="4" t="n">
+        <v>318</v>
+      </c>
+      <c r="B319" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C319" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D319" s="4" t="inlineStr">
+        <is>
+          <t>Fuente: ATDEM, Proyecto Escuelas entrega Computadoras</t>
+        </is>
+      </c>
+      <c r="E319" s="5" t="inlineStr">
+        <is>
+          <t>Kanin eua: ATDEM, Proyecto Escuelas entrega Computadoras</t>
+        </is>
+      </c>
+      <c r="F319" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G319" s="4" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="4" t="n">
+        <v>319</v>
+      </c>
+      <c r="B320" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C320" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D320" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Aulas Tecnológicas en CSV</t>
+        </is>
+      </c>
+      <c r="E320" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Tlamachtiloyan iga tepostlapoualli ipan CSV</t>
+        </is>
+      </c>
+      <c r="F320" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G320" s="4" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="4" t="n">
+        <v>320</v>
+      </c>
+      <c r="B321" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C321" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D321" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Aulas Tecnológicas en KML</t>
+        </is>
+      </c>
+      <c r="E321" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Tlamachtiloyan iga tepostlapoualli ipan KML</t>
+        </is>
+      </c>
+      <c r="F321" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G321" s="4" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="4" t="n">
+        <v>321</v>
+      </c>
+      <c r="B322" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C322" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D322" s="4" t="inlineStr">
+        <is>
+          <t>Dependencias estatales con la red Wi-Fi pública de la ATDEM: secretaría, sede, coordenadas y puntos de acceso.</t>
+        </is>
+      </c>
+      <c r="E322" s="5" t="inlineStr">
+        <is>
+          <t>Teguichiualoyan iga Kaltlayekana tlen kipiaj matlatl Wi-Fi tlen ATDEM: secretaría, kalle, kanin katej uan kanin mosaloua.</t>
+        </is>
+      </c>
+      <c r="F322" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G322" s="4" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="4" t="n">
+        <v>322</v>
+      </c>
+      <c r="B323" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C323" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D323" s="4" t="inlineStr">
+        <is>
+          <t>Fuente: ATDEM, Agentes_dependencias La Tierra Que Nos Une</t>
+        </is>
+      </c>
+      <c r="E323" s="5" t="inlineStr">
+        <is>
+          <t>Kanin eua: ATDEM, Agentes_dependencias La Tierra Que Nos Une</t>
+        </is>
+      </c>
+      <c r="F323" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G323" s="4" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="4" t="n">
+        <v>323</v>
+      </c>
+      <c r="B324" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C324" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D324" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Red La tierra que nos une en CSV</t>
+        </is>
+      </c>
+      <c r="E324" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Matlatl Nin tlale tech sepaneloa ipan CSV</t>
+        </is>
+      </c>
+      <c r="F324" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G324" s="4" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="4" t="n">
+        <v>324</v>
+      </c>
+      <c r="B325" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C325" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D325" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Red La tierra que nos une en KML</t>
+        </is>
+      </c>
+      <c r="E325" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Matlatl Nin tlale tech sepaneloa ipan KML</t>
+        </is>
+      </c>
+      <c r="F325" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G325" s="4" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="4" t="n">
+        <v>325</v>
+      </c>
+      <c r="B326" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C326" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D326" s="4" t="inlineStr">
+        <is>
+          <t>Límites municipales de Morelos</t>
+        </is>
+      </c>
+      <c r="E326" s="5" t="inlineStr">
+        <is>
+          <t>Itlalxelol altepemej ipan Morelos</t>
+        </is>
+      </c>
+      <c r="F326" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G326" s="4" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="4" t="n">
+        <v>326</v>
+      </c>
+      <c r="B327" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C327" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D327" s="4" t="inlineStr">
+        <is>
+          <t>Contorno de los {n} municipios del estado, con clave geoestadística (CVEGEO) y nombre.</t>
+        </is>
+      </c>
+      <c r="E327" s="5" t="inlineStr">
+        <is>
+          <t>Itlalxelol {n} altepemej, iga iclave geoestadística (CVEGEO) uan itoga.</t>
+        </is>
+      </c>
+      <c r="F327" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G327" s="4" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="4" t="n">
+        <v>327</v>
+      </c>
+      <c r="B328" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C328" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D328" s="4" t="inlineStr">
+        <is>
+          <t>Fuente: INE, límites municipales</t>
+        </is>
+      </c>
+      <c r="E328" s="5" t="inlineStr">
+        <is>
+          <t>Kanin eua: INE, itlalxelol altepemej</t>
+        </is>
+      </c>
+      <c r="F328" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G328" s="4" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="4" t="n">
+        <v>328</v>
+      </c>
+      <c r="B329" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C329" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D329" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Límites municipales de Morelos en CSV</t>
+        </is>
+      </c>
+      <c r="E329" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Itlalxelol altepemej ipan Morelos ipan CSV</t>
+        </is>
+      </c>
+      <c r="F329" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G329" s="4" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="4" t="n">
+        <v>329</v>
+      </c>
+      <c r="B330" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C330" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D330" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Límites municipales de Morelos en KML</t>
+        </is>
+      </c>
+      <c r="E330" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Itlalxelol altepemej ipan Morelos ipan KML</t>
+        </is>
+      </c>
+      <c r="F330" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G330" s="4" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="4" t="n">
+        <v>330</v>
+      </c>
+      <c r="B331" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C331" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D331" s="4" t="inlineStr">
+        <is>
+          <t>Los archivos se generan en tu navegador con la misma información que muestra el tablero. Para Google My Maps importa el KML en una capa nueva y usa "Aplicar estilo por columna de datos" para colorear por municipio, polígono u otro campo.</t>
+        </is>
+      </c>
+      <c r="E331" s="5" t="inlineStr">
+        <is>
+          <t>Nin amatl mochiua ipan motepostlapoual iga nochi tlamachilistle tlen kinextia nin tablero. Iga Google My Maps, xikalaki KML ipan se yankuik tlapachtli uan xiktekiuti "Aplicar estilo por columna de datos" iga tiktlapaluis iga altepetl, polígono o siguin.</t>
+        </is>
+      </c>
+      <c r="F331" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G331" s="4" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="4" t="n">
+        <v>331</v>
+      </c>
+      <c r="B332" s="4" t="inlineStr">
+        <is>
+          <t>Inicio (buscador de comunidades)</t>
+        </is>
+      </c>
+      <c r="C332" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D332" s="4" t="inlineStr">
+        <is>
+          <t>No encontramos «{d}» entre las {n} comunidades del programa. Revisa cómo está escrito o busca por municipio.</t>
+        </is>
+      </c>
+      <c r="E332" s="5" t="inlineStr">
+        <is>
+          <t>Amo otikajsike «{d}» ipan {n} altepetsitsin tlen nin tlapaleuilistle. Xiktlachili kenin otiktlajkuilo o xiktemo iga altepetl.</t>
+        </is>
+      </c>
+      <c r="F332" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G332" s="4" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="4" t="n">
+        <v>332</v>
+      </c>
+      <c r="B333" s="4" t="inlineStr">
+        <is>
+          <t>Inicio (buscador de comunidades)</t>
+        </is>
+      </c>
+      <c r="C333" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D333" s="4" t="inlineStr">
+        <is>
+          <t>{d} tiene {n} comunidad en el programa.</t>
+        </is>
+      </c>
+      <c r="E333" s="5" t="inlineStr">
+        <is>
+          <t>{d} kipia {n} altepetsin ipan nin tlapaleuilistle.</t>
+        </is>
+      </c>
+      <c r="F333" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G333" s="4" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="4" t="n">
+        <v>333</v>
+      </c>
+      <c r="B334" s="4" t="inlineStr">
+        <is>
+          <t>Inicio (buscador de comunidades)</t>
+        </is>
+      </c>
+      <c r="C334" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D334" s="4" t="inlineStr">
+        <is>
+          <t>Y {n} comunidad más. Escribe más letras para afinar la búsqueda.</t>
+        </is>
+      </c>
+      <c r="E334" s="5" t="inlineStr">
+        <is>
+          <t>Uan ogachi {n} altepetsin. Xiktlajkuilo ogachi tlajkuilolli iga tiktemos kuale.</t>
+        </is>
+      </c>
+      <c r="F334" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G334" s="4" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="4" t="n">
+        <v>334</v>
+      </c>
+      <c r="B335" s="4" t="inlineStr">
+        <is>
           <t>Encabezado y menú</t>
         </is>
       </c>
-      <c r="C316" s="4" t="inlineStr">
+      <c r="C335" s="4" t="inlineStr">
         <is>
           <t>atributo</t>
         </is>
       </c>
-      <c r="D316" s="4" t="inlineStr">
+      <c r="D335" s="4" t="inlineStr">
         <is>
           <t>Territorios de Paz y Buen Vivir · Gobierno de Morelos</t>
         </is>
       </c>
-      <c r="E316" s="5" t="inlineStr">
+      <c r="E335" s="5" t="inlineStr">
         <is>
           <t>Territorios de Paz y Buen Vivir · Kaltlayekana ipan Morelos</t>
         </is>
       </c>
-      <c r="F316" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G316" s="4" t="n"/>
+      <c r="F335" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G335" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G316"/>
+  <autoFilter ref="A1:G335"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/traducciones/Traduccion_nahuatl_tablero.xlsx
+++ b/traducciones/Traduccion_nahuatl_tablero.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glosario" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$G$335</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$G$347</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G335"/>
+  <dimension ref="A1:G347"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7872,12 +7872,12 @@
       </c>
       <c r="D237" s="4" t="inlineStr">
         <is>
-          <t>Acercar tecnología a las escuelas es abrir oportunidades reales para las niñas y los niños, especialmente en zonas donde el acceso ha sido limitado.</t>
+          <t>{n} de abril de {n} · {d}</t>
         </is>
       </c>
       <c r="E237" s="5" t="inlineStr">
         <is>
-          <t>Tikitkiliskej tepostlapoualli ipan kaltlamachtiloyan kiijtosneki tiktlapoaj melauak ojmej iga pipiltontij, ogachi kanin amo asiaya.</t>
+          <t>{n} abril, {n} xiuitl · {d}</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="D238" s="4" t="inlineStr">
         <is>
-          <t>, director de Agenda Digital de la ATDEM, durante una entrega en Jojutla.</t>
+          <t>Entrega en la Escuela {d}</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
         <is>
-          <t>, tlayekanki ipan Agenda Digital ATDEM, kuak kitemakak ipan Jojutla.</t>
+          <t>Temakalistle ipan Kaltlamachtiloyan {d}</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="D239" s="4" t="inlineStr">
         <is>
-          <t>Escuelas por nivel educativo</t>
+          <t>La ATDEM instaló computadoras con software educativo y conexión a internet en la Escuela {d}, en la colonia {d} de {d}, una escuela en zona de atención prioritaria.</t>
         </is>
       </c>
       <c r="E239" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan iga temachtilistle</t>
+          <t>ATDEM kitlalij tepostlapoualli iga programas iga temachtilistle uan internet ipan Kaltlamachtiloyan {d}, ipan colonia {d} ipan {d}, se kaltlamachtiloyan kanin achtopa moneki tlapaleuilistle.</t>
         </is>
       </c>
       <c r="F239" s="4" t="inlineStr">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="D240" s="4" t="inlineStr">
         <is>
-          <t>¿Dónde están las aulas?</t>
+          <t>computadoras en el aula</t>
         </is>
       </c>
       <c r="E240" s="5" t="inlineStr">
         <is>
-          <t>¿Kanin katej tlamachtiloyan?</t>
+          <t>tepostlapoualli ipan tlamachtiloyan</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="D241" s="4" t="inlineStr">
         <is>
-          <t>Todos los municipios</t>
+          <t>nivel educativo</t>
         </is>
       </c>
       <c r="E241" s="5" t="inlineStr">
         <is>
-          <t>Nochi altepemej</t>
+          <t>itemachtilis</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="D242" s="4" t="inlineStr">
         <is>
-          <t>Escuelas equipadas</t>
+          <t>“La transformación digital en Morelos tiene un propósito claro: que ninguna niña o niño se quede atrás.”</t>
         </is>
       </c>
       <c r="E242" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan tlen kipiaj tepostlapoualli</t>
+          <t>“Tlapatlalistle iga tepostlapoualli ipan Morelos kipia se melauak tlen guinegui: ma amigaj ichpogakonetl o piltontle mokaua iteipan.”</t>
         </is>
       </c>
       <c r="F242" s="4" t="inlineStr">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="D243" s="4" t="inlineStr">
         <is>
-          <t>Computadoras</t>
+          <t>Daniel Sotelo Salazar, director de Agenda Digital de la ATDEM</t>
         </is>
       </c>
       <c r="E243" s="5" t="inlineStr">
         <is>
-          <t>Tepostlapoualmej</t>
+          <t>Daniel Sotelo Salazar, tlayekanki ipan Agenda Digital ATDEM</t>
         </is>
       </c>
       <c r="F243" s="4" t="inlineStr">
@@ -8084,17 +8084,17 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
         <is>
-          <t>Escuelas dentro de un polígono</t>
+          <t>Fotos de la entrega en {d}</t>
         </is>
       </c>
       <c r="E244" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan ipan se polígono</t>
+          <t>Ixkopinkayomej tlen temakalistle ipan {d}</t>
         </is>
       </c>
       <c r="F244" s="4" t="inlineStr">
@@ -8115,17 +8115,17 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
         <is>
-          <t>Mapa de Aulas</t>
+          <t>Inauguración del aula de cómputo en la Escuela {d}, {d}.</t>
         </is>
       </c>
       <c r="E245" s="5" t="inlineStr">
         <is>
-          <t>Tlalamatl iga tlamachtiloyan</t>
+          <t>Peualistle tlen tlamachtiloyan iga tepostlapoualli ipan Kaltlamachtiloyan {d}, {d}.</t>
         </is>
       </c>
       <c r="F245" s="4" t="inlineStr">
@@ -8146,17 +8146,17 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
         <is>
-          <t>El tamaño del círculo indica el número de computadoras. Haz clic en una escuela para ver su detalle.</t>
+          <t>Aula equipada con computadoras, software educativo y conexión a internet.</t>
         </is>
       </c>
       <c r="E246" s="5" t="inlineStr">
         <is>
-          <t>Kenin ueyi yaualtik kinextia keski tepostlapoualli kipia. Xikpacho se kaltlamachtiloyan iga tikitas nochi.</t>
+          <t>Tlamachtiloyan iga tepostlapoualli, programas iga temachtilistle uan internet.</t>
         </is>
       </c>
       <c r="F246" s="4" t="inlineStr">
@@ -8177,17 +8177,17 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
         <is>
-          <t>Computadoras por aula</t>
+          <t>Entrega del aula a la comunidad escolar.</t>
         </is>
       </c>
       <c r="E247" s="5" t="inlineStr">
         <is>
-          <t>Tepostlapoualli ipan nochi tlamachtiloyan</t>
+          <t>Kitemakakej tlamachtiloyan ipan tlatlaga tlen kaltlamachtiloyan.</t>
         </is>
       </c>
       <c r="F247" s="4" t="inlineStr">
@@ -8208,17 +8208,17 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
         <is>
-          <t>Municipio con aula</t>
+          <t>Ceremonia de entrega en la colonia {d}.</t>
         </is>
       </c>
       <c r="E248" s="5" t="inlineStr">
         <is>
-          <t>Altepetl iga tlamachtiloyan</t>
+          <t>Temakalistle ipan colonia {d}.</t>
         </is>
       </c>
       <c r="F248" s="4" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="D249" s="4" t="inlineStr">
         <is>
-          <t>Otros municipios</t>
+          <t>Acercar tecnología a las escuelas es abrir oportunidades reales para las niñas y los niños, especialmente en zonas donde el acceso ha sido limitado.</t>
         </is>
       </c>
       <c r="E249" s="5" t="inlineStr">
         <is>
-          <t>Siguin altepemej</t>
+          <t>Tikitkiliskej tepostlapoualli ipan kaltlamachtiloyan kiijtosneki tiktlapoaj melauak ojmej iga pipiltontij, ogachi kanin amo asiaya.</t>
         </is>
       </c>
       <c r="F249" s="4" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="D250" s="4" t="inlineStr">
         <is>
-          <t>Equipos por Municipio</t>
+          <t>, director de Agenda Digital de la ATDEM, durante una entrega en Jojutla.</t>
         </is>
       </c>
       <c r="E250" s="5" t="inlineStr">
         <is>
-          <t>Tepostlapoualli iga altepetl</t>
+          <t>, tlayekanki ipan Agenda Digital ATDEM, kuak kitemakak ipan Jojutla.</t>
         </is>
       </c>
       <c r="F250" s="4" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="D251" s="4" t="inlineStr">
         <is>
-          <t>{n} eq. · {n} esc.</t>
+          <t>Escuelas por nivel educativo</t>
         </is>
       </c>
       <c r="E251" s="5" t="inlineStr">
         <is>
-          <t>{n} tep. · {n} kal.</t>
+          <t>Kaltlamachtiloyan iga temachtilistle</t>
         </is>
       </c>
       <c r="F251" s="4" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="D252" s="4" t="inlineStr">
         <is>
-          <t>Escuelas</t>
+          <t>¿Dónde están las aulas?</t>
         </is>
       </c>
       <c r="E252" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan</t>
+          <t>¿Kanin katej tlamachtiloyan?</t>
         </is>
       </c>
       <c r="F252" s="4" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="D253" s="4" t="inlineStr">
         <is>
-          <t>Escuela</t>
+          <t>Todos los municipios</t>
         </is>
       </c>
       <c r="E253" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan</t>
+          <t>Nochi altepemej</t>
         </is>
       </c>
       <c r="F253" s="4" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="D254" s="4" t="inlineStr">
         <is>
-          <t>Equipos</t>
+          <t>Escuelas equipadas</t>
         </is>
       </c>
       <c r="E254" s="5" t="inlineStr">
         <is>
-          <t>Tepostlapoualmej</t>
+          <t>Kaltlamachtiloyan tlen kipiaj tepostlapoualli</t>
         </is>
       </c>
       <c r="F254" s="4" t="inlineStr">
@@ -8425,17 +8425,17 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
         <is>
-          <t>Ver {d} en el mapa</t>
+          <t>Computadoras</t>
         </is>
       </c>
       <c r="E255" s="5" t="inlineStr">
         <is>
-          <t>Xikita {d} ipan tlalamatl</t>
+          <t>Tepostlapoualmej</t>
         </is>
       </c>
       <c r="F255" s="4" t="inlineStr">
@@ -8461,12 +8461,12 @@
       </c>
       <c r="D256" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, "Proyecto Escuelas entrega Computadoras" (hoja Concentrado). Ubicación según el enlace de Google Maps capturado por escuela.</t>
+          <t>Escuelas dentro de un polígono</t>
         </is>
       </c>
       <c r="E256" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, "Proyecto Escuelas entrega Computadoras" (hoja Concentrado). Kanin katej iga ojtle Google Maps tlen motlalij iga nochi kaltlamachtiloyan.</t>
+          <t>Kaltlamachtiloyan ipan se polígono</t>
         </is>
       </c>
       <c r="F256" s="4" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="B257" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C257" s="4" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="D257" s="4" t="inlineStr">
         <is>
-          <t>Conectividad pública · Agencia de Transformación Digital</t>
+          <t>Mapa de Aulas</t>
         </is>
       </c>
       <c r="E257" s="5" t="inlineStr">
         <is>
-          <t>Matlatl tlapojtok · Agencia de Transformación Digital</t>
+          <t>Tlalamatl iga tlamachtiloyan</t>
         </is>
       </c>
       <c r="F257" s="4" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="B258" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C258" s="4" t="inlineStr">
@@ -8523,12 +8523,12 @@
       </c>
       <c r="D258" s="4" t="inlineStr">
         <is>
-          <t>Red de Wi-Fi pública, gratuita y abierta impulsada por la Agencia de Transformación Digital del Gobierno del Estado de Morelos (ATDEM). Busca reducir la brecha digital y que la ciudadanía pueda comunicarse sin costo, consultar la programación cultural, realizar trámites y acceder a las plataformas digitales institucionales.</t>
+          <t>El tamaño del círculo indica el número de computadoras. Haz clic en una escuela para ver su detalle.</t>
         </is>
       </c>
       <c r="E258" s="5" t="inlineStr">
         <is>
-          <t>Matlatl Wi-Fi tlen nochi ueli kitekiutiskej, amo iga tomin uan tlapojtok, tlen kichiua Agencia de Transformación Digital ipan Kaltlayekana ipan Morelos (ATDEM). Guinegui ma moyekchiua tlen amo kipiaj internet uan ma tlatlaga ueliskej monotsaskej amo iga tomin, kitaskej iljuimej, kichiuaskej trámites uan kalakiskej ipan plataformas digitales iga Kaltlayekana.</t>
+          <t>Kenin ueyi yaualtik kinextia keski tepostlapoualli kipia. Xikpacho se kaltlamachtiloyan iga tikitas nochi.</t>
         </is>
       </c>
       <c r="F258" s="4" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="B259" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C259" s="4" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="D259" s="4" t="inlineStr">
         <is>
-          <t>Internet gratuito y abierto</t>
+          <t>Computadoras por aula</t>
         </is>
       </c>
       <c r="E259" s="5" t="inlineStr">
         <is>
-          <t>Internet amo iga tomin uan tlapojtok</t>
+          <t>Tepostlapoualli ipan nochi tlamachtiloyan</t>
         </is>
       </c>
       <c r="F259" s="4" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="B260" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C260" s="4" t="inlineStr">
@@ -8585,12 +8585,12 @@
       </c>
       <c r="D260" s="4" t="inlineStr">
         <is>
-          <t>Conexión Wi-Fi sin costo para la ciudadanía en espacios públicos y oficinas de gobierno.</t>
+          <t>Municipio con aula</t>
         </is>
       </c>
       <c r="E260" s="5" t="inlineStr">
         <is>
-          <t>Matlatl Wi-Fi amo iga tomin iga tlatlaga kanin nochi monechikouaj uan ipan teguichiualoyan iga Kaltlayekana.</t>
+          <t>Altepetl iga tlamachtiloyan</t>
         </is>
       </c>
       <c r="F260" s="4" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="B261" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C261" s="4" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="D261" s="4" t="inlineStr">
         <is>
-          <t>Reducir la brecha digital</t>
+          <t>Otros municipios</t>
         </is>
       </c>
       <c r="E261" s="5" t="inlineStr">
         <is>
-          <t>Moyekchiuas tlen amo kipiaj internet</t>
+          <t>Siguin altepemej</t>
         </is>
       </c>
       <c r="F261" s="4" t="inlineStr">
@@ -8637,7 +8637,7 @@
       </c>
       <c r="B262" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C262" s="4" t="inlineStr">
@@ -8647,12 +8647,12 @@
       </c>
       <c r="D262" s="4" t="inlineStr">
         <is>
-          <t>Comunicarse sin costo, consultar programación cultural y realizar trámites en plataformas digitales institucionales.</t>
+          <t>Equipos por Municipio</t>
         </is>
       </c>
       <c r="E262" s="5" t="inlineStr">
         <is>
-          <t>Monotsaskej amo iga tomin, kitaskej iljuimej uan kichiuaskej trámites ipan plataformas digitales iga Kaltlayekana.</t>
+          <t>Tepostlapoualli iga altepetl</t>
         </is>
       </c>
       <c r="F262" s="4" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="B263" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C263" s="4" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="D263" s="4" t="inlineStr">
         <is>
-          <t>Puntos de conexión</t>
+          <t>{n} eq. · {n} esc.</t>
         </is>
       </c>
       <c r="E263" s="5" t="inlineStr">
         <is>
-          <t>Kanin mosaloua</t>
+          <t>{n} tep. · {n} kal.</t>
         </is>
       </c>
       <c r="F263" s="4" t="inlineStr">
@@ -8699,7 +8699,7 @@
       </c>
       <c r="B264" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C264" s="4" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="D264" s="4" t="inlineStr">
         <is>
-          <t>Plazas públicas y espacios de alta concurrencia, como la Plaza de Armas Emiliano Zapata (Zócalo de Cuernavaca).</t>
+          <t>Escuelas</t>
         </is>
       </c>
       <c r="E264" s="5" t="inlineStr">
         <is>
-          <t>Plazas uan kanin miak tlatlaga monechikouaj, ken Plaza de Armas Emiliano Zapata (Zócalo de Cuernavaca).</t>
+          <t>Kaltlamachtiloyan</t>
         </is>
       </c>
       <c r="F264" s="4" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="B265" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C265" s="4" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="D265" s="4" t="inlineStr">
         <is>
-          <t>Eventos especiales, como el Festival Internacional Cervantino en Cuernavaca.</t>
+          <t>Escuela</t>
         </is>
       </c>
       <c r="E265" s="5" t="inlineStr">
         <is>
-          <t>Iljuimej, ken Festival Internacional Cervantino ipan Cuernavaca.</t>
+          <t>Kaltlamachtiloyan</t>
         </is>
       </c>
       <c r="F265" s="4" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="B266" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C266" s="4" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="D266" s="4" t="inlineStr">
         <is>
-          <t>Dependencias estatales, ayudantías municipales y escuelas.</t>
+          <t>Equipos</t>
         </is>
       </c>
       <c r="E266" s="5" t="inlineStr">
         <is>
-          <t>Teguichiualoyan iga Kaltlayekana, ayudantías ipan altepemej uan kaltlamachtiloyan.</t>
+          <t>Tepostlapoualmej</t>
         </is>
       </c>
       <c r="F266" s="4" t="inlineStr">
@@ -8792,22 +8792,22 @@
       </c>
       <c r="B267" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
         <is>
-          <t>Dependencias con red</t>
+          <t>Ver {d} en el mapa</t>
         </is>
       </c>
       <c r="E267" s="5" t="inlineStr">
         <is>
-          <t>Teguichiualoyan iga matlatl</t>
+          <t>Xikita {d} ipan tlalamatl</t>
         </is>
       </c>
       <c r="F267" s="4" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="B268" s="4" t="inlineStr">
         <is>
-          <t>Red La tierra que nos une</t>
+          <t>Aulas Tecnológicas</t>
         </is>
       </c>
       <c r="C268" s="4" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="D268" s="4" t="inlineStr">
         <is>
-          <t>Secretarías y órganos</t>
+          <t>Fuente: ATDEM, "Proyecto Escuelas entrega Computadoras" (hoja Concentrado). Ubicación según el enlace de Google Maps capturado por escuela.</t>
         </is>
       </c>
       <c r="E268" s="5" t="inlineStr">
         <is>
-          <t>Secretarías uan teguichiualoyan</t>
+          <t>Kanin eua: ATDEM, "Proyecto Escuelas entrega Computadoras" (hoja Concentrado). Kanin katej iga ojtle Google Maps tlen motlalij iga nochi kaltlamachtiloyan.</t>
         </is>
       </c>
       <c r="F268" s="4" t="inlineStr">
@@ -8864,12 +8864,12 @@
       </c>
       <c r="D269" s="4" t="inlineStr">
         <is>
-          <t>Sedes conectadas</t>
+          <t>Conectividad pública · Agencia de Transformación Digital</t>
         </is>
       </c>
       <c r="E269" s="5" t="inlineStr">
         <is>
-          <t>Kalmej tlen mosalojtokej</t>
+          <t>Matlatl tlapojtok · Agencia de Transformación Digital</t>
         </is>
       </c>
       <c r="F269" s="4" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="D270" s="4" t="inlineStr">
         <is>
-          <t>Puntos de acceso</t>
+          <t>Red de Wi-Fi pública, gratuita y abierta impulsada por la Agencia de Transformación Digital del Gobierno del Estado de Morelos (ATDEM). Busca reducir la brecha digital y que la ciudadanía pueda comunicarse sin costo, consultar la programación cultural, realizar trámites y acceder a las plataformas digitales institucionales.</t>
         </is>
       </c>
       <c r="E270" s="5" t="inlineStr">
         <is>
-          <t>Kanin mosaloua</t>
+          <t>Matlatl Wi-Fi tlen nochi ueli kitekiutiskej, amo iga tomin uan tlapojtok, tlen kichiua Agencia de Transformación Digital ipan Kaltlayekana ipan Morelos (ATDEM). Guinegui ma moyekchiua tlen amo kipiaj internet uan ma tlatlaga ueliskej monotsaskej amo iga tomin, kitaskej iljuimej, kichiuaskej trámites uan kalakiskej ipan plataformas digitales iga Kaltlayekana.</t>
         </is>
       </c>
       <c r="F270" s="4" t="inlineStr">
@@ -8926,12 +8926,12 @@
       </c>
       <c r="D271" s="4" t="inlineStr">
         <is>
-          <t>Mapa de la red</t>
+          <t>Internet gratuito y abierto</t>
         </is>
       </c>
       <c r="E271" s="5" t="inlineStr">
         <is>
-          <t>Tlalamatl iga matlatl</t>
+          <t>Internet amo iga tomin uan tlapojtok</t>
         </is>
       </c>
       <c r="F271" s="4" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="D272" s="4" t="inlineStr">
         <is>
-          <t>Sede con red (el tamaño indica cuántas dependencias)</t>
+          <t>Conexión Wi-Fi sin costo para la ciudadanía en espacios públicos y oficinas de gobierno.</t>
         </is>
       </c>
       <c r="E272" s="5" t="inlineStr">
         <is>
-          <t>Kalle iga matlatl (kenin ueyi kinextia keski teguichiualoyan)</t>
+          <t>Matlatl Wi-Fi amo iga tomin iga tlatlaga kanin nochi monechikouaj uan ipan teguichiualoyan iga Kaltlayekana.</t>
         </is>
       </c>
       <c r="F272" s="4" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="D273" s="4" t="inlineStr">
         <is>
-          <t>Dependencias por secretaría</t>
+          <t>Reducir la brecha digital</t>
         </is>
       </c>
       <c r="E273" s="5" t="inlineStr">
         <is>
-          <t>Teguichiualoyan iga secretaría</t>
+          <t>Moyekchiuas tlen amo kipiaj internet</t>
         </is>
       </c>
       <c r="F273" s="4" t="inlineStr">
@@ -9019,12 +9019,12 @@
       </c>
       <c r="D274" s="4" t="inlineStr">
         <is>
-          <t>{n} puntos de acceso</t>
+          <t>Comunicarse sin costo, consultar programación cultural y realizar trámites en plataformas digitales institucionales.</t>
         </is>
       </c>
       <c r="E274" s="5" t="inlineStr">
         <is>
-          <t>{n} kanin mosaloua</t>
+          <t>Monotsaskej amo iga tomin, kitaskej iljuimej uan kichiuaskej trámites ipan plataformas digitales iga Kaltlayekana.</t>
         </is>
       </c>
       <c r="F274" s="4" t="inlineStr">
@@ -9050,16 +9050,20 @@
       </c>
       <c r="D275" s="4" t="inlineStr">
         <is>
-          <t>Jefatura de la Oficina de la Gubernatura</t>
-        </is>
-      </c>
-      <c r="E275" s="4" t="n"/>
-      <c r="F275" s="4" t="n"/>
-      <c r="G275" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Puntos de conexión</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="inlineStr">
+        <is>
+          <t>Kanin mosaloua</t>
+        </is>
+      </c>
+      <c r="F275" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G275" s="4" t="n"/>
     </row>
     <row r="276">
       <c r="A276" s="4" t="n">
@@ -9077,12 +9081,12 @@
       </c>
       <c r="D276" s="4" t="inlineStr">
         <is>
-          <t>{n} punto de acceso</t>
+          <t>Plazas públicas y espacios de alta concurrencia, como la Plaza de Armas Emiliano Zapata (Zócalo de Cuernavaca).</t>
         </is>
       </c>
       <c r="E276" s="5" t="inlineStr">
         <is>
-          <t>{n} kanin mosaloua</t>
+          <t>Plazas uan kanin miak tlatlaga monechikouaj, ken Plaza de Armas Emiliano Zapata (Zócalo de Cuernavaca).</t>
         </is>
       </c>
       <c r="F276" s="4" t="inlineStr">
@@ -9108,12 +9112,12 @@
       </c>
       <c r="D277" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, "Agentes_dependencias La Tierra Que Nos Une" (dependencias con red La tierra que nos une). Puntos de acceso según el registro de la ATDEM; algunas dependencias no tienen el dato capturado.</t>
+          <t>Eventos especiales, como el Festival Internacional Cervantino en Cuernavaca.</t>
         </is>
       </c>
       <c r="E277" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, "Agentes_dependencias La Tierra Que Nos Une" (teguichiualoyan iga matlatl Nin tlale tech sepaneloa). Kanin mosaloua ken kijkuiloj ATDEM; siguin teguichiualoyan amo kipiaj nin tlapoualli.</t>
+          <t>Iljuimej, ken Festival Internacional Cervantino ipan Cuernavaca.</t>
         </is>
       </c>
       <c r="F277" s="4" t="inlineStr">
@@ -9129,7 +9133,7 @@
       </c>
       <c r="B278" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C278" s="4" t="inlineStr">
@@ -9139,12 +9143,12 @@
       </c>
       <c r="D278" s="4" t="inlineStr">
         <is>
-          <t>Conectividad · Agencia de Transformación Digital</t>
+          <t>Dependencias estatales, ayudantías municipales y escuelas.</t>
         </is>
       </c>
       <c r="E278" s="5" t="inlineStr">
         <is>
-          <t>Mosaloua · Agencia de Transformación Digital</t>
+          <t>Teguichiualoyan iga Kaltlayekana, ayudantías ipan altepemej uan kaltlamachtiloyan.</t>
         </is>
       </c>
       <c r="F278" s="4" t="inlineStr">
@@ -9160,7 +9164,7 @@
       </c>
       <c r="B279" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C279" s="4" t="inlineStr">
@@ -9170,12 +9174,12 @@
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>Sitios y torres de telecomunicaciones de la red estatal (sitios REEM) que dan servicio a dependencias del Gobierno del Estado, planteles educativos, unidades de salud e instalaciones de seguridad en Morelos.</t>
+          <t>Dependencias con red</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>Sitios uan tepostlaketsalmej iga uejka tlanonotsalistle ipan imatlau Kaltlayekana (sitios REEM) tlen kinpaleuiaj teguichiualoyan iga Kaltlayekana, kaltlamachtiloyan, pajtiloyan uan kanin tlajpiaj ipan Morelos.</t>
+          <t>Teguichiualoyan iga matlatl</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
@@ -9191,7 +9195,7 @@
       </c>
       <c r="B280" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C280" s="4" t="inlineStr">
@@ -9201,12 +9205,12 @@
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>Por seguridad de la infraestructura, la información se presenta agregada por municipio y sector. No se publica la ubicación exacta ni el nombre de los sitios.</t>
+          <t>Secretarías y órganos</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>Iga tlajpialistle, tlamachilistle monextia sepan iga altepetl uan teguitl. Amo monextia kanin melauak katej nin intogayo sitios.</t>
+          <t>Secretarías uan teguichiualoyan</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
@@ -9222,7 +9226,7 @@
       </c>
       <c r="B281" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C281" s="4" t="inlineStr">
@@ -9232,12 +9236,12 @@
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>Sitios de telecomunicaciones</t>
+          <t>Sedes conectadas</t>
         </is>
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
-          <t>Sitios iga uejka tlanonotsalistle</t>
+          <t>Kalmej tlen mosalojtokej</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
@@ -9253,7 +9257,7 @@
       </c>
       <c r="B282" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C282" s="4" t="inlineStr">
@@ -9263,12 +9267,12 @@
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>Municipios con sitios</t>
+          <t>Puntos de acceso</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>Altepemej iga sitios</t>
+          <t>Kanin mosaloua</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
@@ -9284,7 +9288,7 @@
       </c>
       <c r="B283" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C283" s="4" t="inlineStr">
@@ -9294,12 +9298,12 @@
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>Sectores atendidos</t>
+          <t>Mapa de la red</t>
         </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
-          <t>Teguimej tlen kinpaleuiaj</t>
+          <t>Tlalamatl iga matlatl</t>
         </is>
       </c>
       <c r="F283" s="4" t="inlineStr">
@@ -9315,7 +9319,7 @@
       </c>
       <c r="B284" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C284" s="4" t="inlineStr">
@@ -9325,12 +9329,12 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Mayor concentración ({n} sitios)</t>
+          <t>Sede con red (el tamaño indica cuántas dependencias)</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>Kanin ogachi miak ({n} sitios)</t>
+          <t>Kalle iga matlatl (kenin ueyi kinextia keski teguichiualoyan)</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
@@ -9346,7 +9350,7 @@
       </c>
       <c r="B285" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C285" s="4" t="inlineStr">
@@ -9356,12 +9360,12 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>Sitios por municipio</t>
+          <t>Dependencias por secretaría</t>
         </is>
       </c>
       <c r="E285" s="5" t="inlineStr">
         <is>
-          <t>Sitios iga altepetl</t>
+          <t>Teguichiualoyan iga secretaría</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
@@ -9377,7 +9381,7 @@
       </c>
       <c r="B286" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C286" s="4" t="inlineStr">
@@ -9387,12 +9391,12 @@
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>Pasa el cursor sobre un municipio para ver el desglose por sector.</t>
+          <t>{n} puntos de acceso</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>Xikpano tepostlapacholi ipan se altepetl iga tikitas tlen kipia iga teguitl.</t>
+          <t>{n} kanin mosaloua</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
@@ -9408,7 +9412,7 @@
       </c>
       <c r="B287" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C287" s="4" t="inlineStr">
@@ -9418,20 +9422,16 @@
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>{n} o más</t>
-        </is>
-      </c>
-      <c r="E287" s="5" t="inlineStr">
-        <is>
-          <t>{n} o ogachi</t>
-        </is>
-      </c>
-      <c r="F287" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G287" s="4" t="n"/>
+          <t>Jefatura de la Oficina de la Gubernatura</t>
+        </is>
+      </c>
+      <c r="E287" s="4" t="n"/>
+      <c r="F287" s="4" t="n"/>
+      <c r="G287" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="4" t="n">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="B288" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C288" s="4" t="inlineStr">
@@ -9449,12 +9449,12 @@
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>Sin sitios</t>
+          <t>{n} punto de acceso</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>Amo kipia sitios</t>
+          <t>{n} kanin mosaloua</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="B289" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C289" s="4" t="inlineStr">
@@ -9480,12 +9480,12 @@
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>Sitios por sector</t>
+          <t>Fuente: ATDEM, "Agentes_dependencias La Tierra Que Nos Une" (dependencias con red La tierra que nos une). Puntos de acceso según el registro de la ATDEM; algunas dependencias no tienen el dato capturado.</t>
         </is>
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>Sitios iga teguitl</t>
+          <t>Kanin eua: ATDEM, "Agentes_dependencias La Tierra Que Nos Une" (teguichiualoyan iga matlatl Nin tlale tech sepaneloa). Kanin mosaloua ken kijkuiloj ATDEM; siguin teguichiualoyan amo kipiaj nin tlapoualli.</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
@@ -9511,12 +9511,12 @@
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>Gobierno del Estado</t>
+          <t>Conectividad · Agencia de Transformación Digital</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>Kaltlayekana</t>
+          <t>Mosaloua · Agencia de Transformación Digital</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
@@ -9542,12 +9542,12 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Sitios y torres de telecomunicaciones de la red estatal (sitios REEM) que dan servicio a dependencias del Gobierno del Estado, planteles educativos, unidades de salud e instalaciones de seguridad en Morelos.</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>Pajtilistle</t>
+          <t>Sitios uan tepostlaketsalmej iga uejka tlanonotsalistle ipan imatlau Kaltlayekana (sitios REEM) tlen kinpaleuiaj teguichiualoyan iga Kaltlayekana, kaltlamachtiloyan, pajtiloyan uan kanin tlajpiaj ipan Morelos.</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
@@ -9573,12 +9573,12 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>Seguridad y Protección Ciudadana</t>
+          <t>Por seguridad de la infraestructura, la información se presenta agregada por municipio y sector. No se publica la ubicación exacta ni el nombre de los sitios.</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>Tlajpialistle uan Tlapaleuilistle iga Tlatlaga</t>
+          <t>Iga tlajpialistle, tlamachilistle monextia sepan iga altepetl uan teguitl. Amo monextia kanin melauak katej nin intogayo sitios.</t>
         </is>
       </c>
       <c r="F292" s="4" t="inlineStr">
@@ -9604,12 +9604,12 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>Municipios con infraestructura</t>
+          <t>Sitios de telecomunicaciones</t>
         </is>
       </c>
       <c r="E293" s="5" t="inlineStr">
         <is>
-          <t>Altepemej iga tepostlaketsalmej</t>
+          <t>Sitios iga uejka tlanonotsalistle</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>Sectores</t>
+          <t>Municipios con sitios</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>Teguimej</t>
+          <t>Altepemej iga sitios</t>
         </is>
       </c>
       <c r="F294" s="4" t="inlineStr">
@@ -9666,12 +9666,12 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>Sitios</t>
+          <t>Sectores atendidos</t>
         </is>
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>Sitios</t>
+          <t>Teguimej tlen kinpaleuiaj</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
@@ -9697,12 +9697,12 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>Gobierno del Estado · {n}</t>
+          <t>Mayor concentración ({n} sitios)</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>Kaltlayekana · {n}</t>
+          <t>Kanin ogachi miak ({n} sitios)</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
@@ -9728,12 +9728,12 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>Salud · {n}</t>
+          <t>Sitios por municipio</t>
         </is>
       </c>
       <c r="E297" s="5" t="inlineStr">
         <is>
-          <t>Pajtilistle · {n}</t>
+          <t>Sitios iga altepetl</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
@@ -9759,12 +9759,12 @@
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>Educación · {n}</t>
+          <t>Pasa el cursor sobre un municipio para ver el desglose por sector.</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
         <is>
-          <t>Temachtilistle · {n}</t>
+          <t>Xikpano tepostlapacholi ipan se altepetl iga tikitas tlen kipia iga teguitl.</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>Seguridad y Protección Ciudadana · {n}</t>
+          <t>{n} o más</t>
         </is>
       </c>
       <c r="E299" s="5" t="inlineStr">
         <is>
-          <t>Tlajpialistle uan Tlapaleuilistle iga Tlatlaga · {n}</t>
+          <t>{n} o ogachi</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, registro de sitios REEM. Municipio asignado con los límites municipales del INE.</t>
+          <t>Sin sitios</t>
         </is>
       </c>
       <c r="E300" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, sitios REEM. Altepetl motlalij iga itlalxelol altepemej tlen INE.</t>
+          <t>Amo kipia sitios</t>
         </is>
       </c>
       <c r="F300" s="4" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
@@ -9852,12 +9852,12 @@
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>Territorios de Paz y Buen Vivir · Transparencia</t>
+          <t>Sitios por sector</t>
         </is>
       </c>
       <c r="E301" s="5" t="inlineStr">
         <is>
-          <t>Territorios de Paz y Buen Vivir · Tlen nochi ueli kitaskej</t>
+          <t>Sitios iga teguitl</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>Descarga las bases de datos que alimentan este tablero. Cada conjunto está disponible en CSV, para abrirlo en Excel o cualquier herramienta de análisis, y en KML, para verlo en Google Earth o Google My Maps.</t>
+          <t>Gobierno del Estado</t>
         </is>
       </c>
       <c r="E302" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga tlapoualli tlen kitekiutia nin tablero. Nochi kipia CSV, iga tiktlapos ipan Excel o siguin programa, uan KML, iga tikitas ipan Google Earth o Google My Maps.</t>
+          <t>Kaltlayekana</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
@@ -9904,7 +9904,7 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>{n} conjuntos de datos</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="E303" s="5" t="inlineStr">
         <is>
-          <t>{n} tlapoualamatl</t>
+          <t>Pajtilistle</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
@@ -9945,12 +9945,12 @@
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>CSV · UTF-{n}, separado por comas</t>
+          <t>Seguridad y Protección Ciudadana</t>
         </is>
       </c>
       <c r="E304" s="5" t="inlineStr">
         <is>
-          <t>CSV · UTF-{n}, xeloltok iga comas</t>
+          <t>Tlajpialistle uan Tlapaleuilistle iga Tlatlaga</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>KML · una sola capa</t>
+          <t>Municipios con infraestructura</t>
         </is>
       </c>
       <c r="E305" s="5" t="inlineStr">
         <is>
-          <t>KML · san se tlapachtli</t>
+          <t>Altepemej iga tepostlaketsalmej</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
@@ -10007,12 +10007,12 @@
       </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>Localidades · Propuesta Actual</t>
+          <t>Sectores</t>
         </is>
       </c>
       <c r="E306" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin · Tlen axan</t>
+          <t>Teguimej</t>
         </is>
       </c>
       <c r="F306" s="4" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
@@ -10038,12 +10038,12 @@
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>{n} registros · {n} campos</t>
+          <t>Sitios</t>
         </is>
       </c>
       <c r="E307" s="5" t="inlineStr">
         <is>
-          <t>{n} tlajkuilolli · {n} tlamachilistle</t>
+          <t>Sitios</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr">
@@ -10059,7 +10059,7 @@
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
@@ -10069,12 +10069,12 @@
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>Las localidades de los {n} polígonos vigentes con sus indicadores de población, vivienda, salud, educación, economía y marginación.</t>
+          <t>Gobierno del Estado · {n}</t>
         </is>
       </c>
       <c r="E308" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin tlen {n} polígono tlen axan iga itlapoual tlatlaga, kalmej, pajtilistle, temachtilistle, tomin uan iknoyotl.</t>
+          <t>Kaltlayekana · {n}</t>
         </is>
       </c>
       <c r="F308" s="4" t="inlineStr">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
@@ -10100,12 +10100,12 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>Fuente: INEGI, Censo {n} (ITER Morelos) y Lista de Comunidades TPBV {n}</t>
+          <t>Salud · {n}</t>
         </is>
       </c>
       <c r="E309" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: INEGI, Censo {n} (ITER Morelos) uan Lista de Comunidades TPBV {n}</t>
+          <t>Pajtilistle · {n}</t>
         </is>
       </c>
       <c r="F309" s="4" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>Ver campos</t>
+          <t>Educación · {n}</t>
         </is>
       </c>
       <c r="E310" s="5" t="inlineStr">
         <is>
-          <t>Xikita tlen kipia</t>
+          <t>Temachtilistle · {n}</t>
         </is>
       </c>
       <c r="F310" s="4" t="inlineStr">
@@ -10152,22 +10152,22 @@
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>Descargar Localidades · Propuesta Actual en CSV</t>
+          <t>Seguridad y Protección Ciudadana · {n}</t>
         </is>
       </c>
       <c r="E311" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Altepetsitsin · Tlen axan ipan CSV</t>
+          <t>Tlajpialistle uan Tlapaleuilistle iga Tlatlaga · {n}</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
@@ -10183,22 +10183,22 @@
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>Descargar Localidades · Propuesta Actual en KML</t>
+          <t>Fuente: ATDEM, registro de sitios REEM. Municipio asignado con los límites municipales del INE.</t>
         </is>
       </c>
       <c r="E312" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Altepetsitsin · Tlen axan ipan KML</t>
+          <t>Kanin eua: ATDEM, sitios REEM. Altepetl motlalij iga itlalxelol altepemej tlen INE.</t>
         </is>
       </c>
       <c r="F312" s="4" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>Polígonos · Propuesta Actual</t>
+          <t>Territorios de Paz y Buen Vivir · Transparencia</t>
         </is>
       </c>
       <c r="E313" s="5" t="inlineStr">
         <is>
-          <t>Polígono · Tlen axan</t>
+          <t>Territorios de Paz y Buen Vivir · Tlen nochi ueli kitaskej</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>Contorno de los {n} polígonos vigentes de Territorios de Paz y Buen Vivir, con número de localidades y población.</t>
+          <t>Descarga las bases de datos que alimentan este tablero. Cada conjunto está disponible en CSV, para abrirlo en Excel o cualquier herramienta de análisis, y en KML, para verlo en Google Earth o Google My Maps.</t>
         </is>
       </c>
       <c r="E314" s="5" t="inlineStr">
         <is>
-          <t>Itlalxelol {n} polígono tlen axan ipan Territorios de Paz y Buen Vivir, iga keski altepetsitsin uan tlatlaga.</t>
+          <t>Xikuiga tlapoualli tlen kitekiutia nin tablero. Nochi kipia CSV, iga tiktlapos ipan Excel o siguin programa, uan KML, iga tikitas ipan Google Earth o Google My Maps.</t>
         </is>
       </c>
       <c r="F314" s="4" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>Fuente: TPBV {n}.geojson</t>
+          <t>{n} conjuntos de datos</t>
         </is>
       </c>
       <c r="E315" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: TPBV {n}.geojson</t>
+          <t>{n} tlapoualamatl</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
@@ -10312,17 +10312,17 @@
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
         <is>
-          <t>Descargar Polígonos · Propuesta Actual en CSV</t>
+          <t>CSV · UTF-{n}, separado por comas</t>
         </is>
       </c>
       <c r="E316" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Polígono · Tlen axan ipan CSV</t>
+          <t>CSV · UTF-{n}, xeloltok iga comas</t>
         </is>
       </c>
       <c r="F316" s="4" t="inlineStr">
@@ -10343,17 +10343,17 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>Descargar Polígonos · Propuesta Actual en KML</t>
+          <t>KML · una sola capa</t>
         </is>
       </c>
       <c r="E317" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Polígono · Tlen axan ipan KML</t>
+          <t>KML · san se tlapachtli</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="D318" s="4" t="inlineStr">
         <is>
-          <t>Escuelas donde ATDEM instaló aulas de cómputo: CCT, nivel, computadoras, fecha de instalación y polígono TPBV.</t>
+          <t>Localidades · Propuesta Actual</t>
         </is>
       </c>
       <c r="E318" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan kanin ATDEM kitlalij tepostlapoualli: CCT, temachtilistle, tepostlapoualmej, kemanian motlalij uan polígono TPBV.</t>
+          <t>Altepetsitsin · Tlen axan</t>
         </is>
       </c>
       <c r="F318" s="4" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, Proyecto Escuelas entrega Computadoras</t>
+          <t>{n} registros · {n} campos</t>
         </is>
       </c>
       <c r="E319" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, Proyecto Escuelas entrega Computadoras</t>
+          <t>{n} tlajkuilolli · {n} tlamachilistle</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
@@ -10436,17 +10436,17 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>Descargar Aulas Tecnológicas en CSV</t>
+          <t>Las localidades de los {n} polígonos vigentes con sus indicadores de población, vivienda, salud, educación, economía y marginación.</t>
         </is>
       </c>
       <c r="E320" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Tlamachtiloyan iga tepostlapoualli ipan CSV</t>
+          <t>Altepetsitsin tlen {n} polígono tlen axan iga itlapoual tlatlaga, kalmej, pajtilistle, temachtilistle, tomin uan iknoyotl.</t>
         </is>
       </c>
       <c r="F320" s="4" t="inlineStr">
@@ -10467,17 +10467,17 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>Descargar Aulas Tecnológicas en KML</t>
+          <t>Fuente: INEGI, Censo {n} (ITER Morelos) y Lista de Comunidades TPBV {n}</t>
         </is>
       </c>
       <c r="E321" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Tlamachtiloyan iga tepostlapoualli ipan KML</t>
+          <t>Kanin eua: INEGI, Censo {n} (ITER Morelos) uan Lista de Comunidades TPBV {n}</t>
         </is>
       </c>
       <c r="F321" s="4" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>Dependencias estatales con la red Wi-Fi pública de la ATDEM: secretaría, sede, coordenadas y puntos de acceso.</t>
+          <t>Ver campos</t>
         </is>
       </c>
       <c r="E322" s="5" t="inlineStr">
         <is>
-          <t>Teguichiualoyan iga Kaltlayekana tlen kipiaj matlatl Wi-Fi tlen ATDEM: secretaría, kalle, kanin katej uan kanin mosaloua.</t>
+          <t>Xikita tlen kipia</t>
         </is>
       </c>
       <c r="F322" s="4" t="inlineStr">
@@ -10529,17 +10529,17 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, Agentes_dependencias La Tierra Que Nos Une</t>
+          <t>Descargar Localidades · Propuesta Actual en CSV</t>
         </is>
       </c>
       <c r="E323" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, Agentes_dependencias La Tierra Que Nos Une</t>
+          <t>Xikuiga Altepetsitsin · Tlen axan ipan CSV</t>
         </is>
       </c>
       <c r="F323" s="4" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="D324" s="4" t="inlineStr">
         <is>
-          <t>Descargar Red La tierra que nos une en CSV</t>
+          <t>Descargar Localidades · Propuesta Actual en KML</t>
         </is>
       </c>
       <c r="E324" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Matlatl Nin tlale tech sepaneloa ipan CSV</t>
+          <t>Xikuiga Altepetsitsin · Tlen axan ipan KML</t>
         </is>
       </c>
       <c r="F324" s="4" t="inlineStr">
@@ -10591,17 +10591,17 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>Descargar Red La tierra que nos une en KML</t>
+          <t>Polígonos · Propuesta Actual</t>
         </is>
       </c>
       <c r="E325" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Matlatl Nin tlale tech sepaneloa ipan KML</t>
+          <t>Polígono · Tlen axan</t>
         </is>
       </c>
       <c r="F325" s="4" t="inlineStr">
@@ -10627,12 +10627,12 @@
       </c>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>Límites municipales de Morelos</t>
+          <t>Contorno de los {n} polígonos vigentes de Territorios de Paz y Buen Vivir, con número de localidades y población.</t>
         </is>
       </c>
       <c r="E326" s="5" t="inlineStr">
         <is>
-          <t>Itlalxelol altepemej ipan Morelos</t>
+          <t>Itlalxelol {n} polígono tlen axan ipan Territorios de Paz y Buen Vivir, iga keski altepetsitsin uan tlatlaga.</t>
         </is>
       </c>
       <c r="F326" s="4" t="inlineStr">
@@ -10658,12 +10658,12 @@
       </c>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>Contorno de los {n} municipios del estado, con clave geoestadística (CVEGEO) y nombre.</t>
+          <t>Fuente: TPBV {n}.geojson</t>
         </is>
       </c>
       <c r="E327" s="5" t="inlineStr">
         <is>
-          <t>Itlalxelol {n} altepemej, iga iclave geoestadística (CVEGEO) uan itoga.</t>
+          <t>Kanin eua: TPBV {n}.geojson</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
@@ -10684,17 +10684,17 @@
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
         <is>
-          <t>Fuente: INE, límites municipales</t>
+          <t>Descargar Polígonos · Propuesta Actual en CSV</t>
         </is>
       </c>
       <c r="E328" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: INE, itlalxelol altepemej</t>
+          <t>Xikuiga Polígono · Tlen axan ipan CSV</t>
         </is>
       </c>
       <c r="F328" s="4" t="inlineStr">
@@ -10720,12 +10720,12 @@
       </c>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>Descargar Límites municipales de Morelos en CSV</t>
+          <t>Descargar Polígonos · Propuesta Actual en KML</t>
         </is>
       </c>
       <c r="E329" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Itlalxelol altepemej ipan Morelos ipan CSV</t>
+          <t>Xikuiga Polígono · Tlen axan ipan KML</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
@@ -10746,17 +10746,17 @@
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
         <is>
-          <t>Descargar Límites municipales de Morelos en KML</t>
+          <t>Escuelas donde ATDEM instaló aulas de cómputo: CCT, nivel, computadoras, fecha de instalación y polígono TPBV.</t>
         </is>
       </c>
       <c r="E330" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Itlalxelol altepemej ipan Morelos ipan KML</t>
+          <t>Kaltlamachtiloyan kanin ATDEM kitlalij tepostlapoualli: CCT, temachtilistle, tepostlapoualmej, kemanian motlalij uan polígono TPBV.</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
@@ -10782,12 +10782,12 @@
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>Los archivos se generan en tu navegador con la misma información que muestra el tablero. Para Google My Maps importa el KML en una capa nueva y usa "Aplicar estilo por columna de datos" para colorear por municipio, polígono u otro campo.</t>
+          <t>Fuente: ATDEM, Proyecto Escuelas entrega Computadoras</t>
         </is>
       </c>
       <c r="E331" s="5" t="inlineStr">
         <is>
-          <t>Nin amatl mochiua ipan motepostlapoual iga nochi tlamachilistle tlen kinextia nin tablero. Iga Google My Maps, xikalaki KML ipan se yankuik tlapachtli uan xiktekiuti "Aplicar estilo por columna de datos" iga tiktlapaluis iga altepetl, polígono o siguin.</t>
+          <t>Kanin eua: ATDEM, Proyecto Escuelas entrega Computadoras</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
@@ -10803,22 +10803,22 @@
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>Inicio (buscador de comunidades)</t>
+          <t>Datos Abiertos</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D332" s="4" t="inlineStr">
         <is>
-          <t>No encontramos «{d}» entre las {n} comunidades del programa. Revisa cómo está escrito o busca por municipio.</t>
+          <t>Descargar Aulas Tecnológicas en CSV</t>
         </is>
       </c>
       <c r="E332" s="5" t="inlineStr">
         <is>
-          <t>Amo otikajsike «{d}» ipan {n} altepetsitsin tlen nin tlapaleuilistle. Xiktlachili kenin otiktlajkuilo o xiktemo iga altepetl.</t>
+          <t>Xikuiga Tlamachtiloyan iga tepostlapoualli ipan CSV</t>
         </is>
       </c>
       <c r="F332" s="4" t="inlineStr">
@@ -10834,22 +10834,22 @@
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>Inicio (buscador de comunidades)</t>
+          <t>Datos Abiertos</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>{d} tiene {n} comunidad en el programa.</t>
+          <t>Descargar Aulas Tecnológicas en KML</t>
         </is>
       </c>
       <c r="E333" s="5" t="inlineStr">
         <is>
-          <t>{d} kipia {n} altepetsin ipan nin tlapaleuilistle.</t>
+          <t>Xikuiga Tlamachtiloyan iga tepostlapoualli ipan KML</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>Inicio (buscador de comunidades)</t>
+          <t>Datos Abiertos</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
@@ -10875,12 +10875,12 @@
       </c>
       <c r="D334" s="4" t="inlineStr">
         <is>
-          <t>Y {n} comunidad más. Escribe más letras para afinar la búsqueda.</t>
+          <t>Dependencias estatales con la red Wi-Fi pública de la ATDEM: secretaría, sede, coordenadas y puntos de acceso.</t>
         </is>
       </c>
       <c r="E334" s="5" t="inlineStr">
         <is>
-          <t>Uan ogachi {n} altepetsin. Xiktlajkuilo ogachi tlajkuilolli iga tiktemos kuale.</t>
+          <t>Teguichiualoyan iga Kaltlayekana tlen kipiaj matlatl Wi-Fi tlen ATDEM: secretaría, kalle, kanin katej uan kanin mosaloua.</t>
         </is>
       </c>
       <c r="F334" s="4" t="inlineStr">
@@ -10896,33 +10896,405 @@
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C335" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D335" s="4" t="inlineStr">
+        <is>
+          <t>Fuente: ATDEM, Agentes_dependencias La Tierra Que Nos Une</t>
+        </is>
+      </c>
+      <c r="E335" s="5" t="inlineStr">
+        <is>
+          <t>Kanin eua: ATDEM, Agentes_dependencias La Tierra Que Nos Une</t>
+        </is>
+      </c>
+      <c r="F335" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G335" s="4" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="4" t="n">
+        <v>335</v>
+      </c>
+      <c r="B336" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C336" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D336" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Red La tierra que nos une en CSV</t>
+        </is>
+      </c>
+      <c r="E336" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Matlatl Nin tlale tech sepaneloa ipan CSV</t>
+        </is>
+      </c>
+      <c r="F336" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G336" s="4" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="4" t="n">
+        <v>336</v>
+      </c>
+      <c r="B337" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C337" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D337" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Red La tierra que nos une en KML</t>
+        </is>
+      </c>
+      <c r="E337" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Matlatl Nin tlale tech sepaneloa ipan KML</t>
+        </is>
+      </c>
+      <c r="F337" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G337" s="4" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="4" t="n">
+        <v>337</v>
+      </c>
+      <c r="B338" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C338" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D338" s="4" t="inlineStr">
+        <is>
+          <t>Límites municipales de Morelos</t>
+        </is>
+      </c>
+      <c r="E338" s="5" t="inlineStr">
+        <is>
+          <t>Itlalxelol altepemej ipan Morelos</t>
+        </is>
+      </c>
+      <c r="F338" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G338" s="4" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="4" t="n">
+        <v>338</v>
+      </c>
+      <c r="B339" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C339" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D339" s="4" t="inlineStr">
+        <is>
+          <t>Contorno de los {n} municipios del estado, con clave geoestadística (CVEGEO) y nombre.</t>
+        </is>
+      </c>
+      <c r="E339" s="5" t="inlineStr">
+        <is>
+          <t>Itlalxelol {n} altepemej, iga iclave geoestadística (CVEGEO) uan itoga.</t>
+        </is>
+      </c>
+      <c r="F339" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G339" s="4" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="4" t="n">
+        <v>339</v>
+      </c>
+      <c r="B340" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D340" s="4" t="inlineStr">
+        <is>
+          <t>Fuente: INE, límites municipales</t>
+        </is>
+      </c>
+      <c r="E340" s="5" t="inlineStr">
+        <is>
+          <t>Kanin eua: INE, itlalxelol altepemej</t>
+        </is>
+      </c>
+      <c r="F340" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G340" s="4" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="4" t="n">
+        <v>340</v>
+      </c>
+      <c r="B341" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D341" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Límites municipales de Morelos en CSV</t>
+        </is>
+      </c>
+      <c r="E341" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Itlalxelol altepemej ipan Morelos ipan CSV</t>
+        </is>
+      </c>
+      <c r="F341" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G341" s="4" t="n"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="4" t="n">
+        <v>341</v>
+      </c>
+      <c r="B342" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D342" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Límites municipales de Morelos en KML</t>
+        </is>
+      </c>
+      <c r="E342" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Itlalxelol altepemej ipan Morelos ipan KML</t>
+        </is>
+      </c>
+      <c r="F342" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G342" s="4" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="4" t="n">
+        <v>342</v>
+      </c>
+      <c r="B343" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C343" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D343" s="4" t="inlineStr">
+        <is>
+          <t>Los archivos se generan en tu navegador con la misma información que muestra el tablero. Para Google My Maps importa el KML en una capa nueva y usa "Aplicar estilo por columna de datos" para colorear por municipio, polígono u otro campo.</t>
+        </is>
+      </c>
+      <c r="E343" s="5" t="inlineStr">
+        <is>
+          <t>Nin amatl mochiua ipan motepostlapoual iga nochi tlamachilistle tlen kinextia nin tablero. Iga Google My Maps, xikalaki KML ipan se yankuik tlapachtli uan xiktekiuti "Aplicar estilo por columna de datos" iga tiktlapaluis iga altepetl, polígono o siguin.</t>
+        </is>
+      </c>
+      <c r="F343" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G343" s="4" t="n"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="4" t="n">
+        <v>343</v>
+      </c>
+      <c r="B344" s="4" t="inlineStr">
+        <is>
+          <t>Inicio (buscador de comunidades)</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D344" s="4" t="inlineStr">
+        <is>
+          <t>No encontramos «{d}» entre las {n} comunidades del programa. Revisa cómo está escrito o busca por municipio.</t>
+        </is>
+      </c>
+      <c r="E344" s="5" t="inlineStr">
+        <is>
+          <t>Amo otikajsike «{d}» ipan {n} altepetsitsin tlen nin tlapaleuilistle. Xiktlachili kenin otiktlajkuilo o xiktemo iga altepetl.</t>
+        </is>
+      </c>
+      <c r="F344" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G344" s="4" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="4" t="n">
+        <v>344</v>
+      </c>
+      <c r="B345" s="4" t="inlineStr">
+        <is>
+          <t>Inicio (buscador de comunidades)</t>
+        </is>
+      </c>
+      <c r="C345" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D345" s="4" t="inlineStr">
+        <is>
+          <t>{d} tiene {n} comunidad en el programa.</t>
+        </is>
+      </c>
+      <c r="E345" s="5" t="inlineStr">
+        <is>
+          <t>{d} kipia {n} altepetsin ipan nin tlapaleuilistle.</t>
+        </is>
+      </c>
+      <c r="F345" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G345" s="4" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="4" t="n">
+        <v>345</v>
+      </c>
+      <c r="B346" s="4" t="inlineStr">
+        <is>
+          <t>Inicio (buscador de comunidades)</t>
+        </is>
+      </c>
+      <c r="C346" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D346" s="4" t="inlineStr">
+        <is>
+          <t>Y {n} comunidad más. Escribe más letras para afinar la búsqueda.</t>
+        </is>
+      </c>
+      <c r="E346" s="5" t="inlineStr">
+        <is>
+          <t>Uan ogachi {n} altepetsin. Xiktlajkuilo ogachi tlajkuilolli iga tiktemos kuale.</t>
+        </is>
+      </c>
+      <c r="F346" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G346" s="4" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="4" t="n">
+        <v>346</v>
+      </c>
+      <c r="B347" s="4" t="inlineStr">
+        <is>
           <t>Encabezado y menú</t>
         </is>
       </c>
-      <c r="C335" s="4" t="inlineStr">
+      <c r="C347" s="4" t="inlineStr">
         <is>
           <t>atributo</t>
         </is>
       </c>
-      <c r="D335" s="4" t="inlineStr">
+      <c r="D347" s="4" t="inlineStr">
         <is>
           <t>Territorios de Paz y Buen Vivir · Gobierno de Morelos</t>
         </is>
       </c>
-      <c r="E335" s="5" t="inlineStr">
+      <c r="E347" s="5" t="inlineStr">
         <is>
           <t>Territorios de Paz y Buen Vivir · Kaltlayekana ipan Morelos</t>
         </is>
       </c>
-      <c r="F335" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G335" s="4" t="n"/>
+      <c r="F347" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G347" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G335"/>
+  <autoFilter ref="A1:G347"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/traducciones/Traduccion_nahuatl_tablero.xlsx
+++ b/traducciones/Traduccion_nahuatl_tablero.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glosario" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$G$347</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Textos'!$A$1:$G$378</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G347"/>
+  <dimension ref="A1:G378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3963,12 +3963,12 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Mapa de las dependencias estatales que ya cuentan con la red Wi-Fi pública y gratuita de la ATDEM: sedes, secretarías y puntos de acceso.</t>
+          <t>Mapa de la red Wi-Fi pública y gratuita de la ATDEM en oficinas de gobierno y en comunidades: sedes, puntos de acceso y avance de instalación.</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Tlalamatl iga teguichiualoyan iga Kaltlayekana tlen ya kipiaj matlatl Wi-Fi tlapojtok uan amo iga tomin tlen ATDEM: kalmej, secretarías uan kanin mosaloua.</t>
+          <t>Tlalamatl iga matlatl Wi-Fi tlapojtok uan amo iga tomin tlen ATDEM ipan teguichiualoyan iga Kaltlayekana uan ipan altepetsitsin: kalmej, kanin mosaloua uan kenin motlalijtiga.</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -9174,12 +9174,12 @@
       </c>
       <c r="D279" s="4" t="inlineStr">
         <is>
-          <t>Dependencias con red</t>
+          <t>{n} de agosto de {n} · Comunidades prioritarias</t>
         </is>
       </c>
       <c r="E279" s="5" t="inlineStr">
         <is>
-          <t>Teguichiualoyan iga matlatl</t>
+          <t>{n} agosto, {n} xiuitl · Altepetsitsin tlen achtopa</t>
         </is>
       </c>
       <c r="F279" s="4" t="inlineStr">
@@ -9205,12 +9205,12 @@
       </c>
       <c r="D280" s="4" t="inlineStr">
         <is>
-          <t>Secretarías y órganos</t>
+          <t>Internet gratuito en comunidades prioritarias</t>
         </is>
       </c>
       <c r="E280" s="5" t="inlineStr">
         <is>
-          <t>Secretarías uan teguichiualoyan</t>
+          <t>Internet amo iga tomin ipan altepetsitsin tlen achtopa</t>
         </is>
       </c>
       <c r="F280" s="4" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="D281" s="4" t="inlineStr">
         <is>
-          <t>Sedes conectadas</t>
+          <t>La ATDEM amplía la red «La tierra que nos une» a zonas históricamente vulnerables. El servicio opera al cien por ciento en El Zapote ({d}) y en Villa Nicolás Zapata ({d}), con puntos Wi-Fi en plazas principales, centros comunitarios y planteles educativos, y personal técnico realiza estudios de factibilidad en {d} y otras localidades de Territorios de Paz y Buen Vivir.</t>
         </is>
       </c>
       <c r="E281" s="5" t="inlineStr">
         <is>
-          <t>Kalmej tlen mosalojtokej</t>
+          <t>ATDEM kiueyichiua matlatl «Nin tlale tech sepaneloa» ipan altepetsitsin tlen miak xiuitl amo kipiayaj. Matlatl ya nochi teguiti ipan El Zapote ({d}) uan ipan Villa Nicolás Zapata ({d}), iga Wi-Fi ipan plazas, kalmej tlen altepetsin uan kaltlamachtiloyan, uan tlatlaga tlen kimatij kitemoaj kenin uelis motlalis ipan {d} uan siguin altepetsitsin tlen Territorios de Paz y Buen Vivir.</t>
         </is>
       </c>
       <c r="F281" s="4" t="inlineStr">
@@ -9267,12 +9267,12 @@
       </c>
       <c r="D282" s="4" t="inlineStr">
         <is>
-          <t>Puntos de acceso</t>
+          <t>comunidades con red instalada</t>
         </is>
       </c>
       <c r="E282" s="5" t="inlineStr">
         <is>
-          <t>Kanin mosaloua</t>
+          <t>altepetsitsin tlen ya kipiaj matlatl</t>
         </is>
       </c>
       <c r="F282" s="4" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="D283" s="4" t="inlineStr">
         <is>
-          <t>Mapa de la red</t>
+          <t>comunidades en proceso de instalación</t>
         </is>
       </c>
       <c r="E283" s="5" t="inlineStr">
         <is>
-          <t>Tlalamatl iga matlatl</t>
+          <t>altepetsitsin kanin matlatl motlalijtiga</t>
         </is>
       </c>
       <c r="F283" s="4" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="D284" s="4" t="inlineStr">
         <is>
-          <t>Sede con red (el tamaño indica cuántas dependencias)</t>
+          <t>“El internet no puede seguir siendo un privilegio de pocos; es una herramienta de equidad social.”</t>
         </is>
       </c>
       <c r="E284" s="5" t="inlineStr">
         <is>
-          <t>Kalle iga matlatl (kenin ueyi kinextia keski teguichiualoyan)</t>
+          <t>“Internet amo ueli san sansiguin kipiaske; ika internet nochi sepan tiuejueyij.”</t>
         </is>
       </c>
       <c r="F284" s="4" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="D285" s="4" t="inlineStr">
         <is>
-          <t>Dependencias por secretaría</t>
+          <t>Samuel Rivera Muciño, titular de la ATDEM</t>
         </is>
       </c>
       <c r="E285" s="5" t="inlineStr">
         <is>
-          <t>Teguichiualoyan iga secretaría</t>
+          <t>Samuel Rivera Muciño, tlayekanki ipan ATDEM</t>
         </is>
       </c>
       <c r="F285" s="4" t="inlineStr">
@@ -9386,17 +9386,17 @@
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
         <is>
-          <t>{n} puntos de acceso</t>
+          <t>Fotos de la red en comunidades prioritarias</t>
         </is>
       </c>
       <c r="E286" s="5" t="inlineStr">
         <is>
-          <t>{n} kanin mosaloua</t>
+          <t>Ixkopinkayomej tlen matlatl ipan altepetsitsin tlen achtopa</t>
         </is>
       </c>
       <c r="F286" s="4" t="inlineStr">
@@ -9417,21 +9417,25 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
         <is>
-          <t>Jefatura de la Oficina de la Gubernatura</t>
-        </is>
-      </c>
-      <c r="E287" s="4" t="n"/>
-      <c r="F287" s="4" t="n"/>
-      <c r="G287" s="4" t="inlineStr">
-        <is>
-          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
-        </is>
-      </c>
+          <t>Personal técnico de la ATDEM durante un recorrido de campo.</t>
+        </is>
+      </c>
+      <c r="E287" s="5" t="inlineStr">
+        <is>
+          <t>Tlatlaga tlen ATDEM kuak nejnemij ipan tlale.</t>
+        </is>
+      </c>
+      <c r="F287" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G287" s="4" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="4" t="n">
@@ -9444,17 +9448,17 @@
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
         <is>
-          <t>{n} punto de acceso</t>
+          <t>Visita de la ATDEM a un centro comunitario.</t>
         </is>
       </c>
       <c r="E288" s="5" t="inlineStr">
         <is>
-          <t>{n} kanin mosaloua</t>
+          <t>ATDEM kipaxaloua se kalle tlen altepetsin.</t>
         </is>
       </c>
       <c r="F288" s="4" t="inlineStr">
@@ -9475,17 +9479,17 @@
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, "Agentes_dependencias La Tierra Que Nos Une" (dependencias con red La tierra que nos une). Puntos de acceso según el registro de la ATDEM; algunas dependencias no tienen el dato capturado.</t>
+          <t>Infraestructura de telecomunicaciones para llevar la red a las comunidades.</t>
         </is>
       </c>
       <c r="E289" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, "Agentes_dependencias La Tierra Que Nos Une" (teguichiualoyan iga matlatl Nin tlale tech sepaneloa). Kanin mosaloua ken kijkuiloj ATDEM; siguin teguichiualoyan amo kipiaj nin tlapoualli.</t>
+          <t>Tepostlaketsalli iga kuiguiliske matlatl altepetsitsin.</t>
         </is>
       </c>
       <c r="F289" s="4" t="inlineStr">
@@ -9501,22 +9505,22 @@
       </c>
       <c r="B290" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>atributo</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
         <is>
-          <t>Conectividad · Agencia de Transformación Digital</t>
+          <t>Estudios de factibilidad tecnológica en zonas prioritarias del estado.</t>
         </is>
       </c>
       <c r="E290" s="5" t="inlineStr">
         <is>
-          <t>Mosaloua · Agencia de Transformación Digital</t>
+          <t>Kitemoaj kenin uelis motlalis matlatl ipan altepetsitsin tlen achtopa.</t>
         </is>
       </c>
       <c r="F290" s="4" t="inlineStr">
@@ -9532,7 +9536,7 @@
       </c>
       <c r="B291" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C291" s="4" t="inlineStr">
@@ -9542,12 +9546,12 @@
       </c>
       <c r="D291" s="4" t="inlineStr">
         <is>
-          <t>Sitios y torres de telecomunicaciones de la red estatal (sitios REEM) que dan servicio a dependencias del Gobierno del Estado, planteles educativos, unidades de salud e instalaciones de seguridad en Morelos.</t>
+          <t>Dependencias con red</t>
         </is>
       </c>
       <c r="E291" s="5" t="inlineStr">
         <is>
-          <t>Sitios uan tepostlaketsalmej iga uejka tlanonotsalistle ipan imatlau Kaltlayekana (sitios REEM) tlen kinpaleuiaj teguichiualoyan iga Kaltlayekana, kaltlamachtiloyan, pajtiloyan uan kanin tlajpiaj ipan Morelos.</t>
+          <t>Teguichiualoyan iga matlatl</t>
         </is>
       </c>
       <c r="F291" s="4" t="inlineStr">
@@ -9563,7 +9567,7 @@
       </c>
       <c r="B292" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C292" s="4" t="inlineStr">
@@ -9573,12 +9577,12 @@
       </c>
       <c r="D292" s="4" t="inlineStr">
         <is>
-          <t>Por seguridad de la infraestructura, la información se presenta agregada por municipio y sector. No se publica la ubicación exacta ni el nombre de los sitios.</t>
+          <t>Secretarías y órganos</t>
         </is>
       </c>
       <c r="E292" s="5" t="inlineStr">
         <is>
-          <t>Iga tlajpialistle, tlamachilistle monextia sepan iga altepetl uan teguitl. Amo monextia kanin melauak katej nin intogayo sitios.</t>
+          <t>Secretarías uan teguichiualoyan</t>
         </is>
       </c>
       <c r="F292" s="4" t="inlineStr">
@@ -9594,7 +9598,7 @@
       </c>
       <c r="B293" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C293" s="4" t="inlineStr">
@@ -9604,12 +9608,12 @@
       </c>
       <c r="D293" s="4" t="inlineStr">
         <is>
-          <t>Sitios de telecomunicaciones</t>
+          <t>Sedes conectadas</t>
         </is>
       </c>
       <c r="E293" s="5" t="inlineStr">
         <is>
-          <t>Sitios iga uejka tlanonotsalistle</t>
+          <t>Kalmej tlen mosalojtokej</t>
         </is>
       </c>
       <c r="F293" s="4" t="inlineStr">
@@ -9625,7 +9629,7 @@
       </c>
       <c r="B294" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C294" s="4" t="inlineStr">
@@ -9635,12 +9639,12 @@
       </c>
       <c r="D294" s="4" t="inlineStr">
         <is>
-          <t>Municipios con sitios</t>
+          <t>Puntos de acceso</t>
         </is>
       </c>
       <c r="E294" s="5" t="inlineStr">
         <is>
-          <t>Altepemej iga sitios</t>
+          <t>Kanin mosaloua</t>
         </is>
       </c>
       <c r="F294" s="4" t="inlineStr">
@@ -9656,7 +9660,7 @@
       </c>
       <c r="B295" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C295" s="4" t="inlineStr">
@@ -9666,12 +9670,12 @@
       </c>
       <c r="D295" s="4" t="inlineStr">
         <is>
-          <t>Sectores atendidos</t>
+          <t>WiFi gratuito en comunidades</t>
         </is>
       </c>
       <c r="E295" s="5" t="inlineStr">
         <is>
-          <t>Teguimej tlen kinpaleuiaj</t>
+          <t>WiFi amo iga tomin ipan altepetsitsin</t>
         </is>
       </c>
       <c r="F295" s="4" t="inlineStr">
@@ -9687,7 +9691,7 @@
       </c>
       <c r="B296" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C296" s="4" t="inlineStr">
@@ -9697,12 +9701,12 @@
       </c>
       <c r="D296" s="4" t="inlineStr">
         <is>
-          <t>Mayor concentración ({n} sitios)</t>
+          <t>Comunidades</t>
         </is>
       </c>
       <c r="E296" s="5" t="inlineStr">
         <is>
-          <t>Kanin ogachi miak ({n} sitios)</t>
+          <t>Altepetsitsin</t>
         </is>
       </c>
       <c r="F296" s="4" t="inlineStr">
@@ -9718,7 +9722,7 @@
       </c>
       <c r="B297" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C297" s="4" t="inlineStr">
@@ -9728,12 +9732,12 @@
       </c>
       <c r="D297" s="4" t="inlineStr">
         <is>
-          <t>Sitios por municipio</t>
+          <t>Con red instalada</t>
         </is>
       </c>
       <c r="E297" s="5" t="inlineStr">
         <is>
-          <t>Sitios iga altepetl</t>
+          <t>Ya kipiaj matlatl</t>
         </is>
       </c>
       <c r="F297" s="4" t="inlineStr">
@@ -9749,7 +9753,7 @@
       </c>
       <c r="B298" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C298" s="4" t="inlineStr">
@@ -9759,12 +9763,12 @@
       </c>
       <c r="D298" s="4" t="inlineStr">
         <is>
-          <t>Pasa el cursor sobre un municipio para ver el desglose por sector.</t>
+          <t>En proceso de instalación</t>
         </is>
       </c>
       <c r="E298" s="5" t="inlineStr">
         <is>
-          <t>Xikpano tepostlapacholi ipan se altepetl iga tikitas tlen kipia iga teguitl.</t>
+          <t>Matlatl motlalijtiga</t>
         </is>
       </c>
       <c r="F298" s="4" t="inlineStr">
@@ -9780,7 +9784,7 @@
       </c>
       <c r="B299" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C299" s="4" t="inlineStr">
@@ -9790,12 +9794,12 @@
       </c>
       <c r="D299" s="4" t="inlineStr">
         <is>
-          <t>{n} o más</t>
+          <t>En comunidades TPBV</t>
         </is>
       </c>
       <c r="E299" s="5" t="inlineStr">
         <is>
-          <t>{n} o ogachi</t>
+          <t>Ipan altepetsitsin TPBV</t>
         </is>
       </c>
       <c r="F299" s="4" t="inlineStr">
@@ -9811,7 +9815,7 @@
       </c>
       <c r="B300" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C300" s="4" t="inlineStr">
@@ -9821,12 +9825,12 @@
       </c>
       <c r="D300" s="4" t="inlineStr">
         <is>
-          <t>Sin sitios</t>
+          <t>Mapa de la red</t>
         </is>
       </c>
       <c r="E300" s="5" t="inlineStr">
         <is>
-          <t>Amo kipia sitios</t>
+          <t>Tlalamatl iga matlatl</t>
         </is>
       </c>
       <c r="F300" s="4" t="inlineStr">
@@ -9842,7 +9846,7 @@
       </c>
       <c r="B301" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C301" s="4" t="inlineStr">
@@ -9852,12 +9856,12 @@
       </c>
       <c r="D301" s="4" t="inlineStr">
         <is>
-          <t>Sitios por sector</t>
+          <t>Oficina de gobierno (el tamaño indica cuántas dependencias)</t>
         </is>
       </c>
       <c r="E301" s="5" t="inlineStr">
         <is>
-          <t>Sitios iga teguitl</t>
+          <t>Teguichiualoyan iga Kaltlayekana (kenin ueyi kinextia keski teguichiualoyan)</t>
         </is>
       </c>
       <c r="F301" s="4" t="inlineStr">
@@ -9873,7 +9877,7 @@
       </c>
       <c r="B302" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C302" s="4" t="inlineStr">
@@ -9883,12 +9887,12 @@
       </c>
       <c r="D302" s="4" t="inlineStr">
         <is>
-          <t>Gobierno del Estado</t>
+          <t>Comunidad: instalado</t>
         </is>
       </c>
       <c r="E302" s="5" t="inlineStr">
         <is>
-          <t>Kaltlayekana</t>
+          <t>Altepetsin: motlalij</t>
         </is>
       </c>
       <c r="F302" s="4" t="inlineStr">
@@ -9904,7 +9908,7 @@
       </c>
       <c r="B303" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C303" s="4" t="inlineStr">
@@ -9914,12 +9918,12 @@
       </c>
       <c r="D303" s="4" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Comunidad: en proceso</t>
         </is>
       </c>
       <c r="E303" s="5" t="inlineStr">
         <is>
-          <t>Pajtilistle</t>
+          <t>Altepetsin: motlalijtiga</t>
         </is>
       </c>
       <c r="F303" s="4" t="inlineStr">
@@ -9935,7 +9939,7 @@
       </c>
       <c r="B304" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C304" s="4" t="inlineStr">
@@ -9945,12 +9949,12 @@
       </c>
       <c r="D304" s="4" t="inlineStr">
         <is>
-          <t>Seguridad y Protección Ciudadana</t>
+          <t>Instalado</t>
         </is>
       </c>
       <c r="E304" s="5" t="inlineStr">
         <is>
-          <t>Tlajpialistle uan Tlapaleuilistle iga Tlatlaga</t>
+          <t>Motlalij</t>
         </is>
       </c>
       <c r="F304" s="4" t="inlineStr">
@@ -9966,7 +9970,7 @@
       </c>
       <c r="B305" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C305" s="4" t="inlineStr">
@@ -9976,12 +9980,12 @@
       </c>
       <c r="D305" s="4" t="inlineStr">
         <is>
-          <t>Municipios con infraestructura</t>
+          <t>{d} · Comunidad TPBV</t>
         </is>
       </c>
       <c r="E305" s="5" t="inlineStr">
         <is>
-          <t>Altepemej iga tepostlaketsalmej</t>
+          <t>{d} · Altepetsin TPBV</t>
         </is>
       </c>
       <c r="F305" s="4" t="inlineStr">
@@ -9997,7 +10001,7 @@
       </c>
       <c r="B306" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C306" s="4" t="inlineStr">
@@ -10007,12 +10011,12 @@
       </c>
       <c r="D306" s="4" t="inlineStr">
         <is>
-          <t>Sectores</t>
+          <t>En proceso</t>
         </is>
       </c>
       <c r="E306" s="5" t="inlineStr">
         <is>
-          <t>Teguimej</t>
+          <t>Motlalijtiga</t>
         </is>
       </c>
       <c r="F306" s="4" t="inlineStr">
@@ -10028,7 +10032,7 @@
       </c>
       <c r="B307" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C307" s="4" t="inlineStr">
@@ -10038,12 +10042,12 @@
       </c>
       <c r="D307" s="4" t="inlineStr">
         <is>
-          <t>Sitios</t>
+          <t>Disponibilidad de WiFi gratuito en oficinas de gobierno</t>
         </is>
       </c>
       <c r="E307" s="5" t="inlineStr">
         <is>
-          <t>Sitios</t>
+          <t>Kanin onka WiFi amo iga tomin ipan teguichiualoyan iga Kaltlayekana</t>
         </is>
       </c>
       <c r="F307" s="4" t="inlineStr">
@@ -10059,7 +10063,7 @@
       </c>
       <c r="B308" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C308" s="4" t="inlineStr">
@@ -10069,12 +10073,12 @@
       </c>
       <c r="D308" s="4" t="inlineStr">
         <is>
-          <t>Gobierno del Estado · {n}</t>
+          <t>{n} puntos de acceso</t>
         </is>
       </c>
       <c r="E308" s="5" t="inlineStr">
         <is>
-          <t>Kaltlayekana · {n}</t>
+          <t>{n} kanin mosaloua</t>
         </is>
       </c>
       <c r="F308" s="4" t="inlineStr">
@@ -10090,7 +10094,7 @@
       </c>
       <c r="B309" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C309" s="4" t="inlineStr">
@@ -10100,20 +10104,16 @@
       </c>
       <c r="D309" s="4" t="inlineStr">
         <is>
-          <t>Salud · {n}</t>
-        </is>
-      </c>
-      <c r="E309" s="5" t="inlineStr">
-        <is>
-          <t>Pajtilistle · {n}</t>
-        </is>
-      </c>
-      <c r="F309" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G309" s="4" t="n"/>
+          <t>Jefatura de la Oficina de la Gubernatura</t>
+        </is>
+      </c>
+      <c r="E309" s="4" t="n"/>
+      <c r="F309" s="4" t="n"/>
+      <c r="G309" s="4" t="inlineStr">
+        <is>
+          <t>Nombre propio o préstamo: se deja en español (confirmar).</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="4" t="n">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="B310" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C310" s="4" t="inlineStr">
@@ -10131,12 +10131,12 @@
       </c>
       <c r="D310" s="4" t="inlineStr">
         <is>
-          <t>Educación · {n}</t>
+          <t>{n} punto de acceso</t>
         </is>
       </c>
       <c r="E310" s="5" t="inlineStr">
         <is>
-          <t>Temachtilistle · {n}</t>
+          <t>{n} kanin mosaloua</t>
         </is>
       </c>
       <c r="F310" s="4" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="B311" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C311" s="4" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="D311" s="4" t="inlineStr">
         <is>
-          <t>Seguridad y Protección Ciudadana · {n}</t>
+          <t>Fuente: ATDEM, "Agentes_dependencias La Tierra Que Nos Une" (dependencias con red La tierra que nos une) y registro de instalaciones en comunidades. Puntos de acceso según el registro de la ATDEM; algunas dependencias no tienen el dato capturado.</t>
         </is>
       </c>
       <c r="E311" s="5" t="inlineStr">
         <is>
-          <t>Tlajpialistle uan Tlapaleuilistle iga Tlatlaga · {n}</t>
+          <t>Kanin eua: ATDEM, "Agentes_dependencias La Tierra Que Nos Une" (teguichiualoyan iga matlatl Nin tlale tech sepaneloa) uan itlajkuilol tlen motlalij ipan altepetsitsin. Kanin mosaloua ken kijkuiloj ATDEM; siguin teguichiualoyan amo kipiaj nin tlapoualli.</t>
         </is>
       </c>
       <c r="F311" s="4" t="inlineStr">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="B312" s="4" t="inlineStr">
         <is>
-          <t>Infraestructura de Telecomunicaciones</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C312" s="4" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="D312" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, registro de sitios REEM. Municipio asignado con los límites municipales del INE.</t>
+          <t>WiFi gratuito: instalado</t>
         </is>
       </c>
       <c r="E312" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, sitios REEM. Altepetl motlalij iga itlalxelol altepemej tlen INE.</t>
+          <t>WiFi amo iga tomin: motlalij</t>
         </is>
       </c>
       <c r="F312" s="4" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="B313" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C313" s="4" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="D313" s="4" t="inlineStr">
         <is>
-          <t>Territorios de Paz y Buen Vivir · Transparencia</t>
+          <t>Comunidad de Territorios de Paz y Buen Vivir · Polígono {d}</t>
         </is>
       </c>
       <c r="E313" s="5" t="inlineStr">
         <is>
-          <t>Territorios de Paz y Buen Vivir · Tlen nochi ueli kitaskej</t>
+          <t>Altepetsin ipan Territorios de Paz y Buen Vivir · Polígono {d}</t>
         </is>
       </c>
       <c r="F313" s="4" t="inlineStr">
@@ -10245,7 +10245,7 @@
       </c>
       <c r="B314" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C314" s="4" t="inlineStr">
@@ -10255,12 +10255,12 @@
       </c>
       <c r="D314" s="4" t="inlineStr">
         <is>
-          <t>Descarga las bases de datos que alimentan este tablero. Cada conjunto está disponible en CSV, para abrirlo en Excel o cualquier herramienta de análisis, y en KML, para verlo en Google Earth o Google My Maps.</t>
+          <t>Ubicación aproximada de la localidad</t>
         </is>
       </c>
       <c r="E314" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga tlapoualli tlen kitekiutia nin tablero. Nochi kipia CSV, iga tiktlapos ipan Excel o siguin programa, uan KML, iga tikitas ipan Google Earth o Google My Maps.</t>
+          <t>Kanin katej altepetsin (amo melauak)</t>
         </is>
       </c>
       <c r="F314" s="4" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="B315" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Red La tierra que nos une</t>
         </is>
       </c>
       <c r="C315" s="4" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="D315" s="4" t="inlineStr">
         <is>
-          <t>{n} conjuntos de datos</t>
+          <t>WiFi gratuito: en proceso</t>
         </is>
       </c>
       <c r="E315" s="5" t="inlineStr">
         <is>
-          <t>{n} tlapoualamatl</t>
+          <t>WiFi amo iga tomin: motlalijtiga</t>
         </is>
       </c>
       <c r="F315" s="4" t="inlineStr">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="B316" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C316" s="4" t="inlineStr">
@@ -10317,12 +10317,12 @@
       </c>
       <c r="D316" s="4" t="inlineStr">
         <is>
-          <t>CSV · UTF-{n}, separado por comas</t>
+          <t>Conectividad · Agencia de Transformación Digital</t>
         </is>
       </c>
       <c r="E316" s="5" t="inlineStr">
         <is>
-          <t>CSV · UTF-{n}, xeloltok iga comas</t>
+          <t>Mosaloua · Agencia de Transformación Digital</t>
         </is>
       </c>
       <c r="F316" s="4" t="inlineStr">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="B317" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C317" s="4" t="inlineStr">
@@ -10348,12 +10348,12 @@
       </c>
       <c r="D317" s="4" t="inlineStr">
         <is>
-          <t>KML · una sola capa</t>
+          <t>Sitios y torres de telecomunicaciones de la red estatal (sitios REEM) que dan servicio a dependencias del Gobierno del Estado, planteles educativos, unidades de salud e instalaciones de seguridad en Morelos.</t>
         </is>
       </c>
       <c r="E317" s="5" t="inlineStr">
         <is>
-          <t>KML · san se tlapachtli</t>
+          <t>Sitios uan tepostlaketsalmej iga uejka tlanonotsalistle ipan imatlau Kaltlayekana (sitios REEM) tlen kinpaleuiaj teguichiualoyan iga Kaltlayekana, kaltlamachtiloyan, pajtiloyan uan kanin tlajpiaj ipan Morelos.</t>
         </is>
       </c>
       <c r="F317" s="4" t="inlineStr">
@@ -10369,7 +10369,7 @@
       </c>
       <c r="B318" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C318" s="4" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="D318" s="4" t="inlineStr">
         <is>
-          <t>Localidades · Propuesta Actual</t>
+          <t>Por seguridad de la infraestructura, la información se presenta agregada por municipio y sector. No se publica la ubicación exacta ni el nombre de los sitios.</t>
         </is>
       </c>
       <c r="E318" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin · Tlen axan</t>
+          <t>Iga tlajpialistle, tlamachilistle monextia sepan iga altepetl uan teguitl. Amo monextia kanin melauak katej nin intogayo sitios.</t>
         </is>
       </c>
       <c r="F318" s="4" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="B319" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C319" s="4" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="D319" s="4" t="inlineStr">
         <is>
-          <t>{n} registros · {n} campos</t>
+          <t>Sitios de telecomunicaciones</t>
         </is>
       </c>
       <c r="E319" s="5" t="inlineStr">
         <is>
-          <t>{n} tlajkuilolli · {n} tlamachilistle</t>
+          <t>Sitios iga uejka tlanonotsalistle</t>
         </is>
       </c>
       <c r="F319" s="4" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="B320" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C320" s="4" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="D320" s="4" t="inlineStr">
         <is>
-          <t>Las localidades de los {n} polígonos vigentes con sus indicadores de población, vivienda, salud, educación, economía y marginación.</t>
+          <t>Municipios con sitios</t>
         </is>
       </c>
       <c r="E320" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin tlen {n} polígono tlen axan iga itlapoual tlatlaga, kalmej, pajtilistle, temachtilistle, tomin uan iknoyotl.</t>
+          <t>Altepemej iga sitios</t>
         </is>
       </c>
       <c r="F320" s="4" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B321" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C321" s="4" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="D321" s="4" t="inlineStr">
         <is>
-          <t>Fuente: INEGI, Censo {n} (ITER Morelos) y Lista de Comunidades TPBV {n}</t>
+          <t>Sectores atendidos</t>
         </is>
       </c>
       <c r="E321" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: INEGI, Censo {n} (ITER Morelos) uan Lista de Comunidades TPBV {n}</t>
+          <t>Teguimej tlen kinpaleuiaj</t>
         </is>
       </c>
       <c r="F321" s="4" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="B322" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C322" s="4" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="D322" s="4" t="inlineStr">
         <is>
-          <t>Ver campos</t>
+          <t>Mayor concentración ({n} sitios)</t>
         </is>
       </c>
       <c r="E322" s="5" t="inlineStr">
         <is>
-          <t>Xikita tlen kipia</t>
+          <t>Kanin ogachi miak ({n} sitios)</t>
         </is>
       </c>
       <c r="F322" s="4" t="inlineStr">
@@ -10524,22 +10524,22 @@
       </c>
       <c r="B323" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
         <is>
-          <t>Descargar Localidades · Propuesta Actual en CSV</t>
+          <t>Sitios por municipio</t>
         </is>
       </c>
       <c r="E323" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Altepetsitsin · Tlen axan ipan CSV</t>
+          <t>Sitios iga altepetl</t>
         </is>
       </c>
       <c r="F323" s="4" t="inlineStr">
@@ -10555,22 +10555,22 @@
       </c>
       <c r="B324" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
         <is>
-          <t>Descargar Localidades · Propuesta Actual en KML</t>
+          <t>Pasa el cursor sobre un municipio para ver el desglose por sector.</t>
         </is>
       </c>
       <c r="E324" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Altepetsitsin · Tlen axan ipan KML</t>
+          <t>Xikpano tepostlapacholi ipan se altepetl iga tikitas tlen kipia iga teguitl.</t>
         </is>
       </c>
       <c r="F324" s="4" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="B325" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C325" s="4" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="D325" s="4" t="inlineStr">
         <is>
-          <t>Polígonos · Propuesta Actual</t>
+          <t>{n} o más</t>
         </is>
       </c>
       <c r="E325" s="5" t="inlineStr">
         <is>
-          <t>Polígono · Tlen axan</t>
+          <t>{n} o ogachi</t>
         </is>
       </c>
       <c r="F325" s="4" t="inlineStr">
@@ -10617,7 +10617,7 @@
       </c>
       <c r="B326" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C326" s="4" t="inlineStr">
@@ -10627,12 +10627,12 @@
       </c>
       <c r="D326" s="4" t="inlineStr">
         <is>
-          <t>Contorno de los {n} polígonos vigentes de Territorios de Paz y Buen Vivir, con número de localidades y población.</t>
+          <t>Sin sitios</t>
         </is>
       </c>
       <c r="E326" s="5" t="inlineStr">
         <is>
-          <t>Itlalxelol {n} polígono tlen axan ipan Territorios de Paz y Buen Vivir, iga keski altepetsitsin uan tlatlaga.</t>
+          <t>Amo kipia sitios</t>
         </is>
       </c>
       <c r="F326" s="4" t="inlineStr">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="B327" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C327" s="4" t="inlineStr">
@@ -10658,12 +10658,12 @@
       </c>
       <c r="D327" s="4" t="inlineStr">
         <is>
-          <t>Fuente: TPBV {n}.geojson</t>
+          <t>Sitios por sector</t>
         </is>
       </c>
       <c r="E327" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: TPBV {n}.geojson</t>
+          <t>Sitios iga teguitl</t>
         </is>
       </c>
       <c r="F327" s="4" t="inlineStr">
@@ -10679,22 +10679,22 @@
       </c>
       <c r="B328" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
         <is>
-          <t>Descargar Polígonos · Propuesta Actual en CSV</t>
+          <t>Gobierno del Estado</t>
         </is>
       </c>
       <c r="E328" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Polígono · Tlen axan ipan CSV</t>
+          <t>Kaltlayekana</t>
         </is>
       </c>
       <c r="F328" s="4" t="inlineStr">
@@ -10710,22 +10710,22 @@
       </c>
       <c r="B329" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
         <is>
-          <t>Descargar Polígonos · Propuesta Actual en KML</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="E329" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Polígono · Tlen axan ipan KML</t>
+          <t>Pajtilistle</t>
         </is>
       </c>
       <c r="F329" s="4" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="B330" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C330" s="4" t="inlineStr">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="D330" s="4" t="inlineStr">
         <is>
-          <t>Escuelas donde ATDEM instaló aulas de cómputo: CCT, nivel, computadoras, fecha de instalación y polígono TPBV.</t>
+          <t>Seguridad y Protección Ciudadana</t>
         </is>
       </c>
       <c r="E330" s="5" t="inlineStr">
         <is>
-          <t>Kaltlamachtiloyan kanin ATDEM kitlalij tepostlapoualli: CCT, temachtilistle, tepostlapoualmej, kemanian motlalij uan polígono TPBV.</t>
+          <t>Tlajpialistle uan Tlapaleuilistle iga Tlatlaga</t>
         </is>
       </c>
       <c r="F330" s="4" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="B331" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C331" s="4" t="inlineStr">
@@ -10782,12 +10782,12 @@
       </c>
       <c r="D331" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, Proyecto Escuelas entrega Computadoras</t>
+          <t>Municipios con infraestructura</t>
         </is>
       </c>
       <c r="E331" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, Proyecto Escuelas entrega Computadoras</t>
+          <t>Altepemej iga tepostlaketsalmej</t>
         </is>
       </c>
       <c r="F331" s="4" t="inlineStr">
@@ -10803,22 +10803,22 @@
       </c>
       <c r="B332" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D332" s="4" t="inlineStr">
         <is>
-          <t>Descargar Aulas Tecnológicas en CSV</t>
+          <t>Sectores</t>
         </is>
       </c>
       <c r="E332" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Tlamachtiloyan iga tepostlapoualli ipan CSV</t>
+          <t>Teguimej</t>
         </is>
       </c>
       <c r="F332" s="4" t="inlineStr">
@@ -10834,22 +10834,22 @@
       </c>
       <c r="B333" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
         <is>
-          <t>Descargar Aulas Tecnológicas en KML</t>
+          <t>Sitios</t>
         </is>
       </c>
       <c r="E333" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Tlamachtiloyan iga tepostlapoualli ipan KML</t>
+          <t>Sitios</t>
         </is>
       </c>
       <c r="F333" s="4" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="B334" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C334" s="4" t="inlineStr">
@@ -10875,12 +10875,12 @@
       </c>
       <c r="D334" s="4" t="inlineStr">
         <is>
-          <t>Dependencias estatales con la red Wi-Fi pública de la ATDEM: secretaría, sede, coordenadas y puntos de acceso.</t>
+          <t>Gobierno del Estado · {n}</t>
         </is>
       </c>
       <c r="E334" s="5" t="inlineStr">
         <is>
-          <t>Teguichiualoyan iga Kaltlayekana tlen kipiaj matlatl Wi-Fi tlen ATDEM: secretaría, kalle, kanin katej uan kanin mosaloua.</t>
+          <t>Kaltlayekana · {n}</t>
         </is>
       </c>
       <c r="F334" s="4" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="B335" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C335" s="4" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="D335" s="4" t="inlineStr">
         <is>
-          <t>Fuente: ATDEM, Agentes_dependencias La Tierra Que Nos Une</t>
+          <t>Salud · {n}</t>
         </is>
       </c>
       <c r="E335" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: ATDEM, Agentes_dependencias La Tierra Que Nos Une</t>
+          <t>Pajtilistle · {n}</t>
         </is>
       </c>
       <c r="F335" s="4" t="inlineStr">
@@ -10927,22 +10927,22 @@
       </c>
       <c r="B336" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D336" s="4" t="inlineStr">
         <is>
-          <t>Descargar Red La tierra que nos une en CSV</t>
+          <t>Educación · {n}</t>
         </is>
       </c>
       <c r="E336" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Matlatl Nin tlale tech sepaneloa ipan CSV</t>
+          <t>Temachtilistle · {n}</t>
         </is>
       </c>
       <c r="F336" s="4" t="inlineStr">
@@ -10958,22 +10958,22 @@
       </c>
       <c r="B337" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
         <is>
-          <t>Descargar Red La tierra que nos une en KML</t>
+          <t>Seguridad y Protección Ciudadana · {n}</t>
         </is>
       </c>
       <c r="E337" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Matlatl Nin tlale tech sepaneloa ipan KML</t>
+          <t>Tlajpialistle uan Tlapaleuilistle iga Tlatlaga · {n}</t>
         </is>
       </c>
       <c r="F337" s="4" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="B338" s="4" t="inlineStr">
         <is>
-          <t>Datos Abiertos</t>
+          <t>Infraestructura de Telecomunicaciones</t>
         </is>
       </c>
       <c r="C338" s="4" t="inlineStr">
@@ -10999,12 +10999,12 @@
       </c>
       <c r="D338" s="4" t="inlineStr">
         <is>
-          <t>Límites municipales de Morelos</t>
+          <t>Fuente: ATDEM, registro de sitios REEM. Municipio asignado con los límites municipales del INE.</t>
         </is>
       </c>
       <c r="E338" s="5" t="inlineStr">
         <is>
-          <t>Itlalxelol altepemej ipan Morelos</t>
+          <t>Kanin eua: ATDEM, sitios REEM. Altepetl motlalij iga itlalxelol altepemej tlen INE.</t>
         </is>
       </c>
       <c r="F338" s="4" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="D339" s="4" t="inlineStr">
         <is>
-          <t>Contorno de los {n} municipios del estado, con clave geoestadística (CVEGEO) y nombre.</t>
+          <t>Territorios de Paz y Buen Vivir · Transparencia</t>
         </is>
       </c>
       <c r="E339" s="5" t="inlineStr">
         <is>
-          <t>Itlalxelol {n} altepemej, iga iclave geoestadística (CVEGEO) uan itoga.</t>
+          <t>Territorios de Paz y Buen Vivir · Tlen nochi ueli kitaskej</t>
         </is>
       </c>
       <c r="F339" s="4" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="D340" s="4" t="inlineStr">
         <is>
-          <t>Fuente: INE, límites municipales</t>
+          <t>Descarga las bases de datos que alimentan este tablero. Cada conjunto está disponible en CSV, para abrirlo en Excel o cualquier herramienta de análisis, y en KML, para verlo en Google Earth o Google My Maps.</t>
         </is>
       </c>
       <c r="E340" s="5" t="inlineStr">
         <is>
-          <t>Kanin eua: INE, itlalxelol altepemej</t>
+          <t>Xikuiga tlapoualli tlen kitekiutia nin tablero. Nochi kipia CSV, iga tiktlapos ipan Excel o siguin programa, uan KML, iga tikitas ipan Google Earth o Google My Maps.</t>
         </is>
       </c>
       <c r="F340" s="4" t="inlineStr">
@@ -11087,17 +11087,17 @@
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>Descargar Límites municipales de Morelos en CSV</t>
+          <t>{n} conjuntos de datos</t>
         </is>
       </c>
       <c r="E341" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Itlalxelol altepemej ipan Morelos ipan CSV</t>
+          <t>{n} tlapoualamatl</t>
         </is>
       </c>
       <c r="F341" s="4" t="inlineStr">
@@ -11118,17 +11118,17 @@
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>atributo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="D342" s="4" t="inlineStr">
         <is>
-          <t>Descargar Límites municipales de Morelos en KML</t>
+          <t>CSV · UTF-{n}, separado por comas</t>
         </is>
       </c>
       <c r="E342" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Itlalxelol altepemej ipan Morelos ipan KML</t>
+          <t>CSV · UTF-{n}, xeloltok iga comas</t>
         </is>
       </c>
       <c r="F342" s="4" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="D343" s="4" t="inlineStr">
         <is>
-          <t>Los archivos se generan en tu navegador con la misma información que muestra el tablero. Para Google My Maps importa el KML en una capa nueva y usa "Aplicar estilo por columna de datos" para colorear por municipio, polígono u otro campo.</t>
+          <t>KML · una sola capa</t>
         </is>
       </c>
       <c r="E343" s="5" t="inlineStr">
         <is>
-          <t>Nin amatl mochiua ipan motepostlapoual iga nochi tlamachilistle tlen kinextia nin tablero. Iga Google My Maps, xikalaki KML ipan se yankuik tlapachtli uan xiktekiuti "Aplicar estilo por columna de datos" iga tiktlapaluis iga altepetl, polígono o siguin.</t>
+          <t>KML · san se tlapachtli</t>
         </is>
       </c>
       <c r="F343" s="4" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="B344" s="4" t="inlineStr">
         <is>
-          <t>Inicio (buscador de comunidades)</t>
+          <t>Datos Abiertos</t>
         </is>
       </c>
       <c r="C344" s="4" t="inlineStr">
@@ -11185,12 +11185,12 @@
       </c>
       <c r="D344" s="4" t="inlineStr">
         <is>
-          <t>No encontramos «{d}» entre las {n} comunidades del programa. Revisa cómo está escrito o busca por municipio.</t>
+          <t>Localidades · Propuesta Actual</t>
         </is>
       </c>
       <c r="E344" s="5" t="inlineStr">
         <is>
-          <t>Amo otikajsike «{d}» ipan {n} altepetsitsin tlen nin tlapaleuilistle. Xiktlachili kenin otiktlajkuilo o xiktemo iga altepetl.</t>
+          <t>Altepetsitsin · Tlen axan</t>
         </is>
       </c>
       <c r="F344" s="4" t="inlineStr">
@@ -11206,7 +11206,7 @@
       </c>
       <c r="B345" s="4" t="inlineStr">
         <is>
-          <t>Inicio (buscador de comunidades)</t>
+          <t>Datos Abiertos</t>
         </is>
       </c>
       <c r="C345" s="4" t="inlineStr">
@@ -11216,12 +11216,12 @@
       </c>
       <c r="D345" s="4" t="inlineStr">
         <is>
-          <t>{d} tiene {n} comunidad en el programa.</t>
+          <t>{n} registros · {n} campos</t>
         </is>
       </c>
       <c r="E345" s="5" t="inlineStr">
         <is>
-          <t>{d} kipia {n} altepetsin ipan nin tlapaleuilistle.</t>
+          <t>{n} tlajkuilolli · {n} tlamachilistle</t>
         </is>
       </c>
       <c r="F345" s="4" t="inlineStr">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="B346" s="4" t="inlineStr">
         <is>
-          <t>Inicio (buscador de comunidades)</t>
+          <t>Datos Abiertos</t>
         </is>
       </c>
       <c r="C346" s="4" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="D346" s="4" t="inlineStr">
         <is>
-          <t>Y {n} comunidad más. Escribe más letras para afinar la búsqueda.</t>
+          <t>Las localidades de los {n} polígonos vigentes con sus indicadores de población, vivienda, salud, educación, economía y marginación.</t>
         </is>
       </c>
       <c r="E346" s="5" t="inlineStr">
         <is>
-          <t>Uan ogachi {n} altepetsin. Xiktlajkuilo ogachi tlajkuilolli iga tiktemos kuale.</t>
+          <t>Altepetsitsin tlen {n} polígono tlen axan iga itlapoual tlatlaga, kalmej, pajtilistle, temachtilistle, tomin uan iknoyotl.</t>
         </is>
       </c>
       <c r="F346" s="4" t="inlineStr">
@@ -11268,33 +11268,994 @@
       </c>
       <c r="B347" s="4" t="inlineStr">
         <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C347" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D347" s="4" t="inlineStr">
+        <is>
+          <t>Fuente: INEGI, Censo {n} (ITER Morelos) y Lista de Comunidades TPBV {n}</t>
+        </is>
+      </c>
+      <c r="E347" s="5" t="inlineStr">
+        <is>
+          <t>Kanin eua: INEGI, Censo {n} (ITER Morelos) uan Lista de Comunidades TPBV {n}</t>
+        </is>
+      </c>
+      <c r="F347" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G347" s="4" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="4" t="n">
+        <v>347</v>
+      </c>
+      <c r="B348" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C348" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D348" s="4" t="inlineStr">
+        <is>
+          <t>Ver campos</t>
+        </is>
+      </c>
+      <c r="E348" s="5" t="inlineStr">
+        <is>
+          <t>Xikita tlen kipia</t>
+        </is>
+      </c>
+      <c r="F348" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G348" s="4" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="4" t="n">
+        <v>348</v>
+      </c>
+      <c r="B349" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C349" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D349" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Localidades · Propuesta Actual en CSV</t>
+        </is>
+      </c>
+      <c r="E349" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Altepetsitsin · Tlen axan ipan CSV</t>
+        </is>
+      </c>
+      <c r="F349" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G349" s="4" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="4" t="n">
+        <v>349</v>
+      </c>
+      <c r="B350" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C350" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D350" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Localidades · Propuesta Actual en KML</t>
+        </is>
+      </c>
+      <c r="E350" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Altepetsitsin · Tlen axan ipan KML</t>
+        </is>
+      </c>
+      <c r="F350" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G350" s="4" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="4" t="n">
+        <v>350</v>
+      </c>
+      <c r="B351" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C351" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D351" s="4" t="inlineStr">
+        <is>
+          <t>Polígonos · Propuesta Actual</t>
+        </is>
+      </c>
+      <c r="E351" s="5" t="inlineStr">
+        <is>
+          <t>Polígono · Tlen axan</t>
+        </is>
+      </c>
+      <c r="F351" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G351" s="4" t="n"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="4" t="n">
+        <v>351</v>
+      </c>
+      <c r="B352" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C352" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D352" s="4" t="inlineStr">
+        <is>
+          <t>Contorno de los {n} polígonos vigentes de Territorios de Paz y Buen Vivir, con número de localidades y población.</t>
+        </is>
+      </c>
+      <c r="E352" s="5" t="inlineStr">
+        <is>
+          <t>Itlalxelol {n} polígono tlen axan ipan Territorios de Paz y Buen Vivir, iga keski altepetsitsin uan tlatlaga.</t>
+        </is>
+      </c>
+      <c r="F352" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G352" s="4" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="4" t="n">
+        <v>352</v>
+      </c>
+      <c r="B353" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C353" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D353" s="4" t="inlineStr">
+        <is>
+          <t>Fuente: TPBV {n}.geojson</t>
+        </is>
+      </c>
+      <c r="E353" s="5" t="inlineStr">
+        <is>
+          <t>Kanin eua: TPBV {n}.geojson</t>
+        </is>
+      </c>
+      <c r="F353" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G353" s="4" t="n"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="4" t="n">
+        <v>353</v>
+      </c>
+      <c r="B354" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C354" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D354" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Polígonos · Propuesta Actual en CSV</t>
+        </is>
+      </c>
+      <c r="E354" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Polígono · Tlen axan ipan CSV</t>
+        </is>
+      </c>
+      <c r="F354" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G354" s="4" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="4" t="n">
+        <v>354</v>
+      </c>
+      <c r="B355" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C355" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D355" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Polígonos · Propuesta Actual en KML</t>
+        </is>
+      </c>
+      <c r="E355" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Polígono · Tlen axan ipan KML</t>
+        </is>
+      </c>
+      <c r="F355" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G355" s="4" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="4" t="n">
+        <v>355</v>
+      </c>
+      <c r="B356" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C356" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D356" s="4" t="inlineStr">
+        <is>
+          <t>Escuelas donde ATDEM instaló aulas de cómputo: CCT, nivel, computadoras, fecha de instalación y polígono TPBV.</t>
+        </is>
+      </c>
+      <c r="E356" s="5" t="inlineStr">
+        <is>
+          <t>Kaltlamachtiloyan kanin ATDEM kitlalij tepostlapoualli: CCT, temachtilistle, tepostlapoualmej, kemanian motlalij uan polígono TPBV.</t>
+        </is>
+      </c>
+      <c r="F356" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G356" s="4" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="4" t="n">
+        <v>356</v>
+      </c>
+      <c r="B357" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C357" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D357" s="4" t="inlineStr">
+        <is>
+          <t>Fuente: ATDEM, Proyecto Escuelas entrega Computadoras</t>
+        </is>
+      </c>
+      <c r="E357" s="5" t="inlineStr">
+        <is>
+          <t>Kanin eua: ATDEM, Proyecto Escuelas entrega Computadoras</t>
+        </is>
+      </c>
+      <c r="F357" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G357" s="4" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="4" t="n">
+        <v>357</v>
+      </c>
+      <c r="B358" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C358" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D358" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Aulas Tecnológicas en CSV</t>
+        </is>
+      </c>
+      <c r="E358" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Tlamachtiloyan iga tepostlapoualli ipan CSV</t>
+        </is>
+      </c>
+      <c r="F358" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G358" s="4" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="4" t="n">
+        <v>358</v>
+      </c>
+      <c r="B359" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C359" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D359" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Aulas Tecnológicas en KML</t>
+        </is>
+      </c>
+      <c r="E359" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Tlamachtiloyan iga tepostlapoualli ipan KML</t>
+        </is>
+      </c>
+      <c r="F359" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G359" s="4" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="4" t="n">
+        <v>359</v>
+      </c>
+      <c r="B360" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C360" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D360" s="4" t="inlineStr">
+        <is>
+          <t>Dependencias estatales con la red Wi-Fi pública de la ATDEM: secretaría, sede, coordenadas y puntos de acceso.</t>
+        </is>
+      </c>
+      <c r="E360" s="5" t="inlineStr">
+        <is>
+          <t>Teguichiualoyan iga Kaltlayekana tlen kipiaj matlatl Wi-Fi tlen ATDEM: secretaría, kalle, kanin katej uan kanin mosaloua.</t>
+        </is>
+      </c>
+      <c r="F360" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G360" s="4" t="n"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="4" t="n">
+        <v>360</v>
+      </c>
+      <c r="B361" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C361" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D361" s="4" t="inlineStr">
+        <is>
+          <t>Fuente: ATDEM, Agentes_dependencias La Tierra Que Nos Une</t>
+        </is>
+      </c>
+      <c r="E361" s="5" t="inlineStr">
+        <is>
+          <t>Kanin eua: ATDEM, Agentes_dependencias La Tierra Que Nos Une</t>
+        </is>
+      </c>
+      <c r="F361" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G361" s="4" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="4" t="n">
+        <v>361</v>
+      </c>
+      <c r="B362" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C362" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D362" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Red La tierra que nos une en CSV</t>
+        </is>
+      </c>
+      <c r="E362" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Matlatl Nin tlale tech sepaneloa ipan CSV</t>
+        </is>
+      </c>
+      <c r="F362" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G362" s="4" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="4" t="n">
+        <v>362</v>
+      </c>
+      <c r="B363" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C363" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D363" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Red La tierra que nos une en KML</t>
+        </is>
+      </c>
+      <c r="E363" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Matlatl Nin tlale tech sepaneloa ipan KML</t>
+        </is>
+      </c>
+      <c r="F363" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G363" s="4" t="n"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="4" t="n">
+        <v>363</v>
+      </c>
+      <c r="B364" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C364" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D364" s="4" t="inlineStr">
+        <is>
+          <t>Red La tierra que nos une · Comunidades</t>
+        </is>
+      </c>
+      <c r="E364" s="5" t="inlineStr">
+        <is>
+          <t>Matlatl Nin tlale tech sepaneloa · Altepetsitsin</t>
+        </is>
+      </c>
+      <c r="F364" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G364" s="4" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="4" t="n">
+        <v>364</v>
+      </c>
+      <c r="B365" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C365" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D365" s="4" t="inlineStr">
+        <is>
+          <t>Comunidades con WiFi gratuito de la ATDEM instalado o en proceso: localidad, municipio, coordenadas, estatus y polígono TPBV.</t>
+        </is>
+      </c>
+      <c r="E365" s="5" t="inlineStr">
+        <is>
+          <t>Altepetsitsin iga WiFi amo iga tomin tlen ATDEM tlen motlalij o motlalijtiga: altepetsin, altepetl, kanin katej, kenin katej uan polígono TPBV.</t>
+        </is>
+      </c>
+      <c r="F365" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G365" s="4" t="n"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="4" t="n">
+        <v>365</v>
+      </c>
+      <c r="B366" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C366" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D366" s="4" t="inlineStr">
+        <is>
+          <t>Fuente: ATDEM, registro de instalaciones en comunidades</t>
+        </is>
+      </c>
+      <c r="E366" s="5" t="inlineStr">
+        <is>
+          <t>Kanin eua: ATDEM, itlajkuilol tlen motlalij ipan altepetsitsin</t>
+        </is>
+      </c>
+      <c r="F366" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G366" s="4" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="4" t="n">
+        <v>366</v>
+      </c>
+      <c r="B367" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C367" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D367" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Red La tierra que nos une · Comunidades en CSV</t>
+        </is>
+      </c>
+      <c r="E367" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Matlatl Nin tlale tech sepaneloa · Altepetsitsin ipan CSV</t>
+        </is>
+      </c>
+      <c r="F367" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G367" s="4" t="n"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="4" t="n">
+        <v>367</v>
+      </c>
+      <c r="B368" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C368" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D368" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Red La tierra que nos une · Comunidades en KML</t>
+        </is>
+      </c>
+      <c r="E368" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Matlatl Nin tlale tech sepaneloa · Altepetsitsin ipan KML</t>
+        </is>
+      </c>
+      <c r="F368" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G368" s="4" t="n"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="4" t="n">
+        <v>368</v>
+      </c>
+      <c r="B369" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C369" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D369" s="4" t="inlineStr">
+        <is>
+          <t>Límites municipales de Morelos</t>
+        </is>
+      </c>
+      <c r="E369" s="5" t="inlineStr">
+        <is>
+          <t>Itlalxelol altepemej ipan Morelos</t>
+        </is>
+      </c>
+      <c r="F369" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G369" s="4" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="4" t="n">
+        <v>369</v>
+      </c>
+      <c r="B370" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C370" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D370" s="4" t="inlineStr">
+        <is>
+          <t>Contorno de los {n} municipios del estado, con clave geoestadística (CVEGEO) y nombre.</t>
+        </is>
+      </c>
+      <c r="E370" s="5" t="inlineStr">
+        <is>
+          <t>Itlalxelol {n} altepemej, iga iclave geoestadística (CVEGEO) uan itoga.</t>
+        </is>
+      </c>
+      <c r="F370" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G370" s="4" t="n"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="4" t="n">
+        <v>370</v>
+      </c>
+      <c r="B371" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C371" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D371" s="4" t="inlineStr">
+        <is>
+          <t>Fuente: INE, límites municipales</t>
+        </is>
+      </c>
+      <c r="E371" s="5" t="inlineStr">
+        <is>
+          <t>Kanin eua: INE, itlalxelol altepemej</t>
+        </is>
+      </c>
+      <c r="F371" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G371" s="4" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="4" t="n">
+        <v>371</v>
+      </c>
+      <c r="B372" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C372" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D372" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Límites municipales de Morelos en CSV</t>
+        </is>
+      </c>
+      <c r="E372" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Itlalxelol altepemej ipan Morelos ipan CSV</t>
+        </is>
+      </c>
+      <c r="F372" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G372" s="4" t="n"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="4" t="n">
+        <v>372</v>
+      </c>
+      <c r="B373" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C373" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D373" s="4" t="inlineStr">
+        <is>
+          <t>Descargar Límites municipales de Morelos en KML</t>
+        </is>
+      </c>
+      <c r="E373" s="5" t="inlineStr">
+        <is>
+          <t>Xikuiga Itlalxelol altepemej ipan Morelos ipan KML</t>
+        </is>
+      </c>
+      <c r="F373" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G373" s="4" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="4" t="n">
+        <v>373</v>
+      </c>
+      <c r="B374" s="4" t="inlineStr">
+        <is>
+          <t>Datos Abiertos</t>
+        </is>
+      </c>
+      <c r="C374" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D374" s="4" t="inlineStr">
+        <is>
+          <t>Los archivos se generan en tu navegador con la misma información que muestra el tablero. Para Google My Maps importa el KML en una capa nueva y usa "Aplicar estilo por columna de datos" para colorear por municipio, polígono u otro campo.</t>
+        </is>
+      </c>
+      <c r="E374" s="5" t="inlineStr">
+        <is>
+          <t>Nin amatl mochiua ipan motepostlapoual iga nochi tlamachilistle tlen kinextia nin tablero. Iga Google My Maps, xikalaki KML ipan se yankuik tlapachtli uan xiktekiuti "Aplicar estilo por columna de datos" iga tiktlapaluis iga altepetl, polígono o siguin.</t>
+        </is>
+      </c>
+      <c r="F374" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G374" s="4" t="n"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="4" t="n">
+        <v>374</v>
+      </c>
+      <c r="B375" s="4" t="inlineStr">
+        <is>
+          <t>Inicio (buscador de comunidades)</t>
+        </is>
+      </c>
+      <c r="C375" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D375" s="4" t="inlineStr">
+        <is>
+          <t>No encontramos «{d}» entre las {n} comunidades del programa. Revisa cómo está escrito o busca por municipio.</t>
+        </is>
+      </c>
+      <c r="E375" s="5" t="inlineStr">
+        <is>
+          <t>Amo otikajsike «{d}» ipan {n} altepetsitsin tlen nin tlapaleuilistle. Xiktlachili kenin otiktlajkuilo o xiktemo iga altepetl.</t>
+        </is>
+      </c>
+      <c r="F375" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G375" s="4" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="4" t="n">
+        <v>375</v>
+      </c>
+      <c r="B376" s="4" t="inlineStr">
+        <is>
+          <t>Inicio (buscador de comunidades)</t>
+        </is>
+      </c>
+      <c r="C376" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D376" s="4" t="inlineStr">
+        <is>
+          <t>{d} tiene {n} comunidad en el programa.</t>
+        </is>
+      </c>
+      <c r="E376" s="5" t="inlineStr">
+        <is>
+          <t>{d} kipia {n} altepetsin ipan nin tlapaleuilistle.</t>
+        </is>
+      </c>
+      <c r="F376" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G376" s="4" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="4" t="n">
+        <v>376</v>
+      </c>
+      <c r="B377" s="4" t="inlineStr">
+        <is>
+          <t>Inicio (buscador de comunidades)</t>
+        </is>
+      </c>
+      <c r="C377" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D377" s="4" t="inlineStr">
+        <is>
+          <t>Y {n} comunidad más. Escribe más letras para afinar la búsqueda.</t>
+        </is>
+      </c>
+      <c r="E377" s="5" t="inlineStr">
+        <is>
+          <t>Uan ogachi {n} altepetsin. Xiktlajkuilo ogachi tlajkuilolli iga tiktemos kuale.</t>
+        </is>
+      </c>
+      <c r="F377" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G377" s="4" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="4" t="n">
+        <v>377</v>
+      </c>
+      <c r="B378" s="4" t="inlineStr">
+        <is>
           <t>Encabezado y menú</t>
         </is>
       </c>
-      <c r="C347" s="4" t="inlineStr">
+      <c r="C378" s="4" t="inlineStr">
         <is>
           <t>atributo</t>
         </is>
       </c>
-      <c r="D347" s="4" t="inlineStr">
+      <c r="D378" s="4" t="inlineStr">
         <is>
           <t>Territorios de Paz y Buen Vivir · Gobierno de Morelos</t>
         </is>
       </c>
-      <c r="E347" s="5" t="inlineStr">
+      <c r="E378" s="5" t="inlineStr">
         <is>
           <t>Territorios de Paz y Buen Vivir · Kaltlayekana ipan Morelos</t>
         </is>
       </c>
-      <c r="F347" s="4" t="inlineStr">
-        <is>
-          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
-        </is>
-      </c>
-      <c r="G347" s="4" t="n"/>
+      <c r="F378" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G378" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G347"/>
+  <autoFilter ref="A1:G378"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/traducciones/Traduccion_nahuatl_tablero.xlsx
+++ b/traducciones/Traduccion_nahuatl_tablero.xlsx
@@ -11185,12 +11185,12 @@
       </c>
       <c r="D344" s="4" t="inlineStr">
         <is>
-          <t>Localidades · Propuesta Actual</t>
+          <t>Localidades TPBV {n}</t>
         </is>
       </c>
       <c r="E344" s="5" t="inlineStr">
         <is>
-          <t>Altepetsitsin · Tlen axan</t>
+          <t>Altepetsitsin TPBV {n}</t>
         </is>
       </c>
       <c r="F344" s="4" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="D349" s="4" t="inlineStr">
         <is>
-          <t>Descargar Localidades · Propuesta Actual en CSV</t>
+          <t>Descargar Localidades TPBV {n} en CSV</t>
         </is>
       </c>
       <c r="E349" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Altepetsitsin · Tlen axan ipan CSV</t>
+          <t>Xikuiga Altepetsitsin TPBV {n} ipan CSV</t>
         </is>
       </c>
       <c r="F349" s="4" t="inlineStr">
@@ -11371,12 +11371,12 @@
       </c>
       <c r="D350" s="4" t="inlineStr">
         <is>
-          <t>Descargar Localidades · Propuesta Actual en KML</t>
+          <t>Descargar Localidades TPBV {n} en KML</t>
         </is>
       </c>
       <c r="E350" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Altepetsitsin · Tlen axan ipan KML</t>
+          <t>Xikuiga Altepetsitsin TPBV {n} ipan KML</t>
         </is>
       </c>
       <c r="F350" s="4" t="inlineStr">
@@ -11402,12 +11402,12 @@
       </c>
       <c r="D351" s="4" t="inlineStr">
         <is>
-          <t>Polígonos · Propuesta Actual</t>
+          <t>Polígonos TPBV {n}</t>
         </is>
       </c>
       <c r="E351" s="5" t="inlineStr">
         <is>
-          <t>Polígono · Tlen axan</t>
+          <t>Polígono TPBV {n}</t>
         </is>
       </c>
       <c r="F351" s="4" t="inlineStr">
@@ -11495,12 +11495,12 @@
       </c>
       <c r="D354" s="4" t="inlineStr">
         <is>
-          <t>Descargar Polígonos · Propuesta Actual en CSV</t>
+          <t>Descargar Polígonos TPBV {n} en CSV</t>
         </is>
       </c>
       <c r="E354" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Polígono · Tlen axan ipan CSV</t>
+          <t>Xikuiga Polígono TPBV {n} ipan CSV</t>
         </is>
       </c>
       <c r="F354" s="4" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>Descargar Polígonos · Propuesta Actual en KML</t>
+          <t>Descargar Polígonos TPBV {n} en KML</t>
         </is>
       </c>
       <c r="E355" s="5" t="inlineStr">
         <is>
-          <t>Xikuiga Polígono · Tlen axan ipan KML</t>
+          <t>Xikuiga Polígono TPBV {n} ipan KML</t>
         </is>
       </c>
       <c r="F355" s="4" t="inlineStr">

--- a/traducciones/Traduccion_nahuatl_tablero.xlsx
+++ b/traducciones/Traduccion_nahuatl_tablero.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G378"/>
+  <dimension ref="A1:G381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12253,6 +12253,111 @@
         </is>
       </c>
       <c r="G378" s="4" t="n"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="4" t="n">
+        <v>378</v>
+      </c>
+      <c r="B379" s="4" t="inlineStr">
+        <is>
+          <t>General (lectores de pantalla)</t>
+        </is>
+      </c>
+      <c r="C379" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D379" s="4" t="inlineStr">
+        <is>
+          <t>(se abre en una pestaña nueva)</t>
+        </is>
+      </c>
+      <c r="E379" s="5" t="inlineStr">
+        <is>
+          <t>(motlapoua ipan okse amatl)</t>
+        </is>
+      </c>
+      <c r="F379" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G379" s="4" t="inlineStr">
+        <is>
+          <t>Aviso para lectores de pantalla en enlaces que abren pestaña nueva</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="4" t="n">
+        <v>379</v>
+      </c>
+      <c r="B380" s="4" t="inlineStr">
+        <is>
+          <t>Análisis Demográfico</t>
+        </is>
+      </c>
+      <c r="C380" s="4" t="inlineStr">
+        <is>
+          <t>atributo</t>
+        </is>
+      </c>
+      <c r="D380" s="4" t="inlineStr">
+        <is>
+          <t>Ruta de navegación</t>
+        </is>
+      </c>
+      <c r="E380" s="5" t="inlineStr">
+        <is>
+          <t>Ojtle kanin tinemi</t>
+        </is>
+      </c>
+      <c r="F380" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G380" s="4" t="inlineStr">
+        <is>
+          <t>Ruta (breadcrumbs) de Análisis, para lectores de pantalla</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="4" t="n">
+        <v>380</v>
+      </c>
+      <c r="B381" s="4" t="inlineStr">
+        <is>
+          <t>Análisis Demográfico</t>
+        </is>
+      </c>
+      <c r="C381" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D381" s="4" t="inlineStr">
+        <is>
+          <t>Comparación de {n} polígonos</t>
+        </is>
+      </c>
+      <c r="E381" s="5" t="inlineStr">
+        <is>
+          <t>Tikinneneuilia {n} polígono</t>
+        </is>
+      </c>
+      <c r="F381" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G381" s="4" t="inlineStr">
+        <is>
+          <t>Último nivel de la ruta al comparar polígonos</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G378"/>

--- a/traducciones/Traduccion_nahuatl_tablero.xlsx
+++ b/traducciones/Traduccion_nahuatl_tablero.xlsx
@@ -570,7 +570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G381"/>
+  <dimension ref="A1:G383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12356,6 +12356,76 @@
       <c r="G381" s="4" t="inlineStr">
         <is>
           <t>Último nivel de la ruta al comparar polígonos</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="4" t="n">
+        <v>381</v>
+      </c>
+      <c r="B382" s="4" t="inlineStr">
+        <is>
+          <t>Inicio</t>
+        </is>
+      </c>
+      <c r="C382" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D382" s="4" t="inlineStr">
+        <is>
+          <t>Mapa del WiFi gratuito de la ATDEM en comunidades: dónde ya está instalado y dónde está en proceso.</t>
+        </is>
+      </c>
+      <c r="E382" s="5" t="inlineStr">
+        <is>
+          <t>Itlalamauj WiFi amo iga tomin tlen ATDEM ipan altepetsitsin: kanin ya motlalij uan kanin motlalijtiga.</t>
+        </is>
+      </c>
+      <c r="F382" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G382" s="4" t="inlineStr">
+        <is>
+          <t>Tarjeta de Red en Inicio (sin oficinas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="4" t="n">
+        <v>382</v>
+      </c>
+      <c r="B383" s="4" t="inlineStr">
+        <is>
+          <t>Red La tierra que nos une</t>
+        </is>
+      </c>
+      <c r="C383" s="4" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="D383" s="4" t="inlineStr">
+        <is>
+          <t>Fuente: ATDEM, registro de instalaciones de WiFi gratuito en comunidades.</t>
+        </is>
+      </c>
+      <c r="E383" s="5" t="inlineStr">
+        <is>
+          <t>Kanin eua: ATDEM, itlajkuilol tlen WiFi amo iga tomin tlen motlalij ipan altepetsitsin.</t>
+        </is>
+      </c>
+      <c r="F383" s="4" t="inlineStr">
+        <is>
+          <t>Borrador automático, ajustado a Hueyapan (revisar)</t>
+        </is>
+      </c>
+      <c r="G383" s="4" t="inlineStr">
+        <is>
+          <t>Fuente de Red (sin oficinas)</t>
         </is>
       </c>
     </row>
